--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68EA380-13DD-4777-92DD-DC4E4894C1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE53E99-B784-4E44-A82E-4185F997F386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="113">
   <si>
     <t>TỔ CHỨC BIÊN CHẾ, TRANG BỊ HƯỚNG CHỦ YẾU</t>
   </si>
@@ -378,9 +378,6 @@
     <t>Hướng PN chủ yếu</t>
   </si>
   <si>
-    <t>Cối 82mm</t>
-  </si>
-  <si>
     <t>Hướng PN thứ yếu</t>
   </si>
   <si>
@@ -388,9 +385,6 @@
   </si>
   <si>
     <t>Lực lượng còn lại</t>
-  </si>
-  <si>
-    <t>Cối 100mm</t>
   </si>
   <si>
     <t>14.00 N-4</t>
@@ -835,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -942,17 +936,11 @@
     <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
+    <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1032,6 +1020,21 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1041,23 +1044,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1377,76 +1365,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42"/>
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="40"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="45"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46" t="s">
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1455,8 +1443,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1472,7 +1460,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="46"/>
+      <c r="H5" s="44"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1806,76 +1794,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="40"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="45"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46" t="s">
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1884,8 +1872,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1901,7 +1889,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="46"/>
+      <c r="H5" s="44"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2382,32 +2370,32 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="47" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="47" t="s">
+      <c r="I1" s="45" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
       <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
@@ -2420,8 +2408,8 @@
       <c r="G2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
@@ -2685,30 +2673,30 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="56" t="s">
+      <c r="C1" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="61" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="63"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="61"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="55"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="26" t="s">
         <v>65</v>
       </c>
@@ -2811,76 +2799,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="40"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="45"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46" t="s">
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2889,8 +2877,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2906,7 +2894,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="46"/>
+      <c r="H5" s="44"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -3387,88 +3375,88 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64" t="s">
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64" t="s">
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="64"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="D2" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="64" t="s">
+      <c r="H2" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="64" t="s">
+      <c r="J2" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="64"/>
-      <c r="L2" s="65" t="s">
+      <c r="K2" s="62"/>
+      <c r="L2" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="65"/>
+      <c r="M2" s="63"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
       <c r="J4" s="29" t="s">
         <v>79</v>
       </c>
@@ -3505,47 +3493,48 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9BFD24-F416-4E13-BF3D-CA2831AC61D2}">
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="7" max="7" width="4.7265625" customWidth="1"/>
+    <col min="9" max="9" width="9.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.5" customHeight="1" thickBot="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="72" t="s">
+      <c r="C1" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="72" t="s">
+      <c r="D1" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="72" t="s">
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="68"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="71"/>
     </row>
     <row r="2" spans="1:13" ht="30.5" thickBot="1">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
       <c r="E2" s="30" t="s">
         <v>86</v>
       </c>
@@ -3558,7 +3547,7 @@
       <c r="H2" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="73"/>
+      <c r="I2" s="68"/>
       <c r="J2" s="30" t="s">
         <v>89</v>
       </c>
@@ -3573,7 +3562,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="64" t="s">
         <v>93</v>
       </c>
       <c r="B3" s="31" t="s">
@@ -3582,26 +3571,20 @@
       <c r="C3" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="33">
-        <v>9</v>
-      </c>
-      <c r="E3" s="33">
-        <v>9</v>
-      </c>
-      <c r="F3" s="33">
-        <v>9</v>
-      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
       <c r="G3" s="33">
-        <f>E3/D3</f>
-        <v>1</v>
+        <f>IFERROR(E3/D3,0)</f>
+        <v>0</v>
       </c>
       <c r="H3" s="33">
-        <f>F3/E3</f>
-        <v>1</v>
+        <f>IFERROR(F3/E3,0)</f>
+        <v>0</v>
       </c>
       <c r="I3" s="33">
         <f>D3</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J3" s="33">
         <f>D3-E3</f>
@@ -3612,33 +3595,27 @@
       <c r="M3" s="31"/>
     </row>
     <row r="4" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A4" s="70"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="34" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="35">
-        <v>4</v>
-      </c>
-      <c r="E4" s="33">
-        <v>4</v>
-      </c>
-      <c r="F4" s="33">
-        <v>4</v>
-      </c>
+      <c r="D4" s="35"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
       <c r="G4" s="33">
-        <f t="shared" ref="G4:H47" si="0">E4/D4</f>
-        <v>1</v>
+        <f t="shared" ref="G4:G57" si="0">IFERROR(E4/D4,0)</f>
+        <v>0</v>
       </c>
       <c r="H4" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IFERROR(F4/E4,0)</f>
+        <v>0</v>
       </c>
       <c r="I4" s="33">
         <f t="shared" ref="I4:I47" si="1">D4</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4" s="33">
         <f t="shared" ref="J4:J47" si="2">D4-E4</f>
@@ -3649,33 +3626,27 @@
       <c r="M4" s="31"/>
     </row>
     <row r="5" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A5" s="70"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="34" t="s">
         <v>96</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="35">
-        <v>4</v>
-      </c>
-      <c r="E5" s="33">
-        <v>4</v>
-      </c>
-      <c r="F5" s="33">
-        <v>4</v>
-      </c>
+      <c r="D5" s="35"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
       <c r="G5" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ref="H4:H57" si="3">IFERROR(F5/E5,0)</f>
+        <v>0</v>
       </c>
       <c r="I5" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5" s="33">
         <f>D5-E5</f>
@@ -3686,33 +3657,27 @@
       <c r="M5" s="31"/>
     </row>
     <row r="6" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A6" s="70"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="34" t="s">
         <v>97</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="35">
-        <v>8</v>
-      </c>
-      <c r="E6" s="33">
-        <v>8</v>
-      </c>
-      <c r="F6" s="33">
-        <v>8</v>
-      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
       <c r="G6" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I6" s="33">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J6" s="33">
         <f t="shared" si="2"/>
@@ -3723,33 +3688,27 @@
       <c r="M6" s="31"/>
     </row>
     <row r="7" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A7" s="70"/>
+      <c r="A7" s="65"/>
       <c r="B7" s="34" t="s">
         <v>98</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="35">
-        <v>9</v>
-      </c>
-      <c r="E7" s="33">
-        <v>9</v>
-      </c>
-      <c r="F7" s="33">
-        <v>9</v>
-      </c>
+      <c r="D7" s="35"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
       <c r="G7" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I7" s="33">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J7" s="33">
         <f t="shared" si="2"/>
@@ -3760,76 +3719,64 @@
       <c r="M7" s="31"/>
     </row>
     <row r="8" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A8" s="70"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="34" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="35">
-        <v>72</v>
-      </c>
-      <c r="E8" s="33">
-        <v>72</v>
-      </c>
-      <c r="F8" s="33">
-        <v>71</v>
-      </c>
+      <c r="D8" s="35"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
       <c r="G8" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="36">
-        <f t="shared" si="0"/>
-        <v>0.98611111111111116</v>
+        <v>0</v>
+      </c>
+      <c r="H8" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I8" s="33">
         <f t="shared" si="1"/>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="J8" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K8" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="M8" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="L8" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="9" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A9" s="70"/>
+      <c r="A9" s="65"/>
       <c r="B9" s="34" t="s">
         <v>100</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="35">
-        <v>8</v>
-      </c>
-      <c r="E9" s="33">
-        <v>8</v>
-      </c>
-      <c r="F9" s="33">
-        <v>8</v>
-      </c>
+      <c r="D9" s="35"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
       <c r="G9" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I9" s="33">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J9" s="33">
         <f t="shared" si="2"/>
@@ -3840,33 +3787,27 @@
       <c r="M9" s="31"/>
     </row>
     <row r="10" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A10" s="70"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="34" t="s">
         <v>101</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="35">
-        <v>36</v>
-      </c>
-      <c r="E10" s="33">
-        <v>36</v>
-      </c>
-      <c r="F10" s="33">
-        <v>36</v>
-      </c>
+      <c r="D10" s="35"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
       <c r="G10" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I10" s="33">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J10" s="33">
         <f t="shared" si="2"/>
@@ -3877,76 +3818,64 @@
       <c r="M10" s="31"/>
     </row>
     <row r="11" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A11" s="70"/>
+      <c r="A11" s="65"/>
       <c r="B11" s="34" t="s">
         <v>102</v>
       </c>
       <c r="C11" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="35">
-        <v>486</v>
-      </c>
-      <c r="E11" s="33">
-        <v>486</v>
-      </c>
-      <c r="F11" s="33">
-        <v>474</v>
-      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
       <c r="G11" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H11" s="36">
-        <f t="shared" si="0"/>
-        <v>0.97530864197530864</v>
+        <v>0</v>
+      </c>
+      <c r="H11" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I11" s="33">
         <f t="shared" si="1"/>
-        <v>486</v>
+        <v>0</v>
       </c>
       <c r="J11" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K11" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="M11" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="L11" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="12" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A12" s="70"/>
+      <c r="A12" s="65"/>
       <c r="B12" s="34" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="35">
-        <v>42</v>
-      </c>
-      <c r="E12" s="33">
-        <v>42</v>
-      </c>
-      <c r="F12" s="33">
-        <v>42</v>
-      </c>
+      <c r="D12" s="35"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I12" s="33">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J12" s="33">
         <f t="shared" si="2"/>
@@ -3957,33 +3886,27 @@
       <c r="M12" s="31"/>
     </row>
     <row r="13" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A13" s="71"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="34" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="74">
-        <v>2403</v>
-      </c>
-      <c r="E13" s="37">
-        <v>2403</v>
-      </c>
-      <c r="F13" s="37">
-        <v>2403</v>
-      </c>
+      <c r="D13" s="37"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
       <c r="G13" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I13" s="33">
         <f t="shared" si="1"/>
-        <v>2403</v>
+        <v>0</v>
       </c>
       <c r="J13" s="33">
         <f t="shared" si="2"/>
@@ -3994,7 +3917,7 @@
       <c r="M13" s="31"/>
     </row>
     <row r="14" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="64" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="31" t="s">
@@ -4003,26 +3926,20 @@
       <c r="C14" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="33">
-        <v>3</v>
-      </c>
-      <c r="E14" s="33">
-        <v>3</v>
-      </c>
-      <c r="F14" s="33">
-        <v>3</v>
-      </c>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
       <c r="G14" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I14" s="33">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="33">
         <f t="shared" si="2"/>
@@ -4033,33 +3950,27 @@
       <c r="M14" s="31"/>
     </row>
     <row r="15" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A15" s="70"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="34" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C15" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="35">
-        <v>3</v>
-      </c>
-      <c r="E15" s="33">
-        <v>3</v>
-      </c>
-      <c r="F15" s="33">
-        <v>3</v>
-      </c>
+      <c r="D15" s="35"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
       <c r="G15" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I15" s="33">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="33">
         <f t="shared" si="2"/>
@@ -4070,33 +3981,27 @@
       <c r="M15" s="31"/>
     </row>
     <row r="16" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A16" s="70"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="35">
-        <v>4</v>
-      </c>
-      <c r="E16" s="33">
-        <v>4</v>
-      </c>
-      <c r="F16" s="33">
-        <v>4</v>
-      </c>
+      <c r="D16" s="35"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I16" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" s="33">
         <f t="shared" si="2"/>
@@ -4107,33 +4012,27 @@
       <c r="M16" s="31"/>
     </row>
     <row r="17" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A17" s="70"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="35">
-        <v>3</v>
-      </c>
-      <c r="E17" s="33">
-        <v>3</v>
-      </c>
-      <c r="F17" s="33">
-        <v>3</v>
-      </c>
+      <c r="D17" s="35"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
       <c r="G17" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I17" s="33">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" s="33">
         <f t="shared" si="2"/>
@@ -4143,77 +4042,65 @@
       <c r="L17" s="31"/>
       <c r="M17" s="31"/>
     </row>
-    <row r="18" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A18" s="70"/>
+    <row r="18" spans="1:13" ht="19" customHeight="1" thickBot="1">
+      <c r="A18" s="65"/>
       <c r="B18" s="34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C18" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="35">
-        <v>30</v>
-      </c>
-      <c r="E18" s="33">
-        <v>30</v>
-      </c>
-      <c r="F18" s="33">
-        <v>29</v>
-      </c>
+      <c r="D18" s="35"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
       <c r="G18" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="36">
-        <f t="shared" si="0"/>
-        <v>0.96666666666666667</v>
+        <v>0</v>
+      </c>
+      <c r="H18" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I18" s="33">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J18" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K18" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="M18" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="L18" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="M18" s="31" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="19" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A19" s="70"/>
+      <c r="A19" s="65"/>
       <c r="B19" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="35">
-        <v>4</v>
-      </c>
-      <c r="E19" s="33">
-        <v>4</v>
-      </c>
-      <c r="F19" s="33">
-        <v>4</v>
-      </c>
+      <c r="D19" s="35"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
       <c r="G19" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I19" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J19" s="33">
         <f t="shared" si="2"/>
@@ -4224,33 +4111,27 @@
       <c r="M19" s="31"/>
     </row>
     <row r="20" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A20" s="70"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="35">
-        <v>18</v>
-      </c>
-      <c r="E20" s="33">
-        <v>18</v>
-      </c>
-      <c r="F20" s="33">
-        <v>18</v>
-      </c>
+      <c r="D20" s="35"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
       <c r="G20" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I20" s="33">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J20" s="33">
         <f t="shared" si="2"/>
@@ -4261,76 +4142,64 @@
       <c r="M20" s="31"/>
     </row>
     <row r="21" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A21" s="70"/>
+      <c r="A21" s="65"/>
       <c r="B21" s="34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="35">
-        <v>161</v>
-      </c>
-      <c r="E21" s="33">
-        <v>161</v>
-      </c>
-      <c r="F21" s="33">
-        <v>155</v>
-      </c>
+      <c r="D21" s="35"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H21" s="36">
-        <f t="shared" si="0"/>
-        <v>0.96273291925465843</v>
+        <v>0</v>
+      </c>
+      <c r="H21" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I21" s="33">
         <f t="shared" si="1"/>
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="J21" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K21" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="M21" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="L21" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="M21" s="31" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="22" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A22" s="70"/>
+      <c r="A22" s="65"/>
       <c r="B22" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="35">
-        <v>12</v>
-      </c>
-      <c r="E22" s="33">
-        <v>12</v>
-      </c>
-      <c r="F22" s="33">
-        <v>12</v>
-      </c>
+      <c r="D22" s="35"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I22" s="33">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J22" s="33">
         <f t="shared" si="2"/>
@@ -4340,34 +4209,28 @@
       <c r="L22" s="31"/>
       <c r="M22" s="31"/>
     </row>
-    <row r="23" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A23" s="71"/>
+    <row r="23" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A23" s="65"/>
       <c r="B23" s="34" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="35">
-        <v>846</v>
-      </c>
-      <c r="E23" s="33">
-        <v>846</v>
-      </c>
-      <c r="F23" s="33">
-        <v>846</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D23" s="35"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I23" s="33">
         <f t="shared" si="1"/>
-        <v>846</v>
+        <v>0</v>
       </c>
       <c r="J23" s="33">
         <f t="shared" si="2"/>
@@ -4377,36 +4240,28 @@
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
     </row>
-    <row r="24" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A24" s="69" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>94</v>
+    <row r="24" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A24" s="66"/>
+      <c r="B24" s="34" t="s">
+        <v>5</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="33">
-        <v>3</v>
-      </c>
-      <c r="E24" s="33">
-        <v>3</v>
-      </c>
-      <c r="F24" s="33">
-        <v>3</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
       <c r="G24" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I24" s="33">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="33">
         <f t="shared" si="2"/>
@@ -4416,34 +4271,30 @@
       <c r="L24" s="31"/>
       <c r="M24" s="31"/>
     </row>
-    <row r="25" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A25" s="70"/>
-      <c r="B25" s="38" t="s">
+    <row r="25" spans="1:13" ht="21" customHeight="1" thickBot="1">
+      <c r="A25" s="64" t="s">
         <v>106</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>94</v>
       </c>
       <c r="C25" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="33">
-        <v>1</v>
-      </c>
-      <c r="E25" s="33">
-        <v>1</v>
-      </c>
-      <c r="F25" s="33">
-        <v>1</v>
-      </c>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
       <c r="G25" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I25" s="33">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="33">
         <f t="shared" si="2"/>
@@ -4454,33 +4305,27 @@
       <c r="M25" s="31"/>
     </row>
     <row r="26" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A26" s="70"/>
-      <c r="B26" s="39" t="s">
-        <v>97</v>
+      <c r="A26" s="65"/>
+      <c r="B26" s="34" t="s">
+        <v>95</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="35">
-        <v>2</v>
-      </c>
-      <c r="E26" s="33">
-        <v>2</v>
-      </c>
-      <c r="F26" s="33">
-        <v>2</v>
-      </c>
+      <c r="D26" s="35"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I26" s="33">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="33">
         <f t="shared" si="2"/>
@@ -4491,33 +4336,27 @@
       <c r="M26" s="31"/>
     </row>
     <row r="27" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A27" s="70"/>
-      <c r="B27" s="39" t="s">
-        <v>98</v>
+      <c r="A27" s="65"/>
+      <c r="B27" s="34" t="s">
+        <v>96</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="35">
-        <v>3</v>
-      </c>
-      <c r="E27" s="33">
-        <v>3</v>
-      </c>
-      <c r="F27" s="33">
-        <v>3</v>
-      </c>
+      <c r="D27" s="35"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
       <c r="G27" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I27" s="33">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J27" s="33">
         <f t="shared" si="2"/>
@@ -4528,33 +4367,27 @@
       <c r="M27" s="31"/>
     </row>
     <row r="28" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A28" s="70"/>
-      <c r="B28" s="39" t="s">
-        <v>99</v>
+      <c r="A28" s="65"/>
+      <c r="B28" s="34" t="s">
+        <v>97</v>
       </c>
       <c r="C28" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="35">
-        <v>18</v>
-      </c>
-      <c r="E28" s="33">
-        <v>18</v>
-      </c>
-      <c r="F28" s="33">
-        <v>18</v>
-      </c>
+      <c r="D28" s="35"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
       <c r="G28" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I28" s="33">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J28" s="33">
         <f t="shared" si="2"/>
@@ -4565,33 +4398,27 @@
       <c r="M28" s="31"/>
     </row>
     <row r="29" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A29" s="70"/>
-      <c r="B29" s="39" t="s">
-        <v>100</v>
+      <c r="A29" s="65"/>
+      <c r="B29" s="34" t="s">
+        <v>98</v>
       </c>
       <c r="C29" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="35">
-        <v>2</v>
-      </c>
-      <c r="E29" s="33">
-        <v>2</v>
-      </c>
-      <c r="F29" s="33">
-        <v>2</v>
-      </c>
+      <c r="D29" s="35"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
       <c r="G29" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I29" s="33">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" s="33">
         <f t="shared" si="2"/>
@@ -4602,33 +4429,27 @@
       <c r="M29" s="31"/>
     </row>
     <row r="30" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A30" s="70"/>
-      <c r="B30" s="39" t="s">
-        <v>101</v>
+      <c r="A30" s="65"/>
+      <c r="B30" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="35">
-        <v>9</v>
-      </c>
-      <c r="E30" s="33">
-        <v>9</v>
-      </c>
-      <c r="F30" s="33">
-        <v>9</v>
-      </c>
+      <c r="D30" s="35"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I30" s="33">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J30" s="33">
         <f t="shared" si="2"/>
@@ -4639,76 +4460,64 @@
       <c r="M30" s="31"/>
     </row>
     <row r="31" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A31" s="70"/>
-      <c r="B31" s="39" t="s">
-        <v>102</v>
+      <c r="A31" s="65"/>
+      <c r="B31" s="34" t="s">
+        <v>100</v>
       </c>
       <c r="C31" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="35">
-        <v>96</v>
-      </c>
-      <c r="E31" s="33">
-        <v>96</v>
-      </c>
-      <c r="F31" s="33">
-        <v>92</v>
-      </c>
+      <c r="D31" s="35"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
       <c r="G31" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H31" s="36">
-        <f t="shared" si="0"/>
-        <v>0.95833333333333337</v>
+        <v>0</v>
+      </c>
+      <c r="H31" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I31" s="33">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="J31" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K31" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="L31" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="M31" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="L31" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="M31" s="31" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="32" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A32" s="70"/>
-      <c r="B32" s="39" t="s">
-        <v>103</v>
+      <c r="A32" s="65"/>
+      <c r="B32" s="34" t="s">
+        <v>101</v>
       </c>
       <c r="C32" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="35">
-        <v>4</v>
-      </c>
-      <c r="E32" s="33">
-        <v>4</v>
-      </c>
-      <c r="F32" s="33">
-        <v>4</v>
-      </c>
+      <c r="D32" s="35"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
       <c r="G32" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I32" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J32" s="33">
         <f t="shared" si="2"/>
@@ -4719,33 +4528,27 @@
       <c r="M32" s="31"/>
     </row>
     <row r="33" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A33" s="71"/>
-      <c r="B33" s="39" t="s">
-        <v>5</v>
+      <c r="A33" s="65"/>
+      <c r="B33" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="C33" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="35">
-        <v>514</v>
-      </c>
-      <c r="E33" s="33">
-        <v>514</v>
-      </c>
-      <c r="F33" s="33">
-        <v>514</v>
-      </c>
+      <c r="D33" s="35"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
       <c r="G33" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I33" s="33">
         <f t="shared" si="1"/>
-        <v>514</v>
+        <v>0</v>
       </c>
       <c r="J33" s="33">
         <f t="shared" si="2"/>
@@ -4756,35 +4559,27 @@
       <c r="M33" s="31"/>
     </row>
     <row r="34" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A34" s="69" t="s">
-        <v>108</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>97</v>
+      <c r="A34" s="65"/>
+      <c r="B34" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="C34" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="33">
-        <v>2</v>
-      </c>
-      <c r="E34" s="33">
-        <v>2</v>
-      </c>
-      <c r="F34" s="33">
-        <v>2</v>
-      </c>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
       <c r="G34" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I34" s="33">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="33">
         <f t="shared" si="2"/>
@@ -4795,33 +4590,27 @@
       <c r="M34" s="31"/>
     </row>
     <row r="35" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A35" s="70"/>
+      <c r="A35" s="66"/>
       <c r="B35" s="34" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="C35" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="35">
-        <v>18</v>
-      </c>
-      <c r="E35" s="33">
-        <v>18</v>
-      </c>
-      <c r="F35" s="33">
-        <v>18</v>
-      </c>
+      <c r="D35" s="35"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
       <c r="G35" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I35" s="33">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J35" s="33">
         <f t="shared" si="2"/>
@@ -4831,34 +4620,30 @@
       <c r="L35" s="31"/>
       <c r="M35" s="31"/>
     </row>
-    <row r="36" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A36" s="70"/>
-      <c r="B36" s="34" t="s">
-        <v>100</v>
+    <row r="36" spans="1:13" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A36" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>94</v>
       </c>
       <c r="C36" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="35">
-        <v>2</v>
-      </c>
-      <c r="E36" s="33">
-        <v>2</v>
-      </c>
-      <c r="F36" s="33">
-        <v>2</v>
-      </c>
+      <c r="D36" s="35"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
       <c r="G36" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I36" s="33">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="33">
         <f t="shared" si="2"/>
@@ -4869,33 +4654,27 @@
       <c r="M36" s="31"/>
     </row>
     <row r="37" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A37" s="70"/>
+      <c r="A37" s="65"/>
       <c r="B37" s="34" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C37" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="35">
-        <v>9</v>
-      </c>
-      <c r="E37" s="33">
-        <v>9</v>
-      </c>
-      <c r="F37" s="33">
-        <v>9</v>
-      </c>
+      <c r="D37" s="35"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
       <c r="G37" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I37" s="33">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J37" s="33">
         <f t="shared" si="2"/>
@@ -4906,33 +4685,27 @@
       <c r="M37" s="31"/>
     </row>
     <row r="38" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A38" s="70"/>
+      <c r="A38" s="65"/>
       <c r="B38" s="34" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C38" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="35">
-        <v>69</v>
-      </c>
-      <c r="E38" s="33">
-        <v>69</v>
-      </c>
-      <c r="F38" s="33">
-        <v>67</v>
-      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
       <c r="G38" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H38" s="36">
-        <f t="shared" si="0"/>
-        <v>0.97101449275362317</v>
+        <v>0</v>
+      </c>
+      <c r="H38" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I38" s="33">
         <f t="shared" si="1"/>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="J38" s="33">
         <f t="shared" si="2"/>
@@ -4943,33 +4716,27 @@
       <c r="M38" s="31"/>
     </row>
     <row r="39" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A39" s="70"/>
+      <c r="A39" s="65"/>
       <c r="B39" s="34" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C39" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="35">
-        <v>4</v>
-      </c>
-      <c r="E39" s="33">
-        <v>4</v>
-      </c>
-      <c r="F39" s="33">
-        <v>4</v>
-      </c>
+      <c r="D39" s="35"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
       <c r="G39" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I39" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J39" s="33">
         <f t="shared" si="2"/>
@@ -4980,33 +4747,27 @@
       <c r="M39" s="31"/>
     </row>
     <row r="40" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A40" s="71"/>
+      <c r="A40" s="65"/>
       <c r="B40" s="34" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" s="35">
-        <v>350</v>
-      </c>
-      <c r="E40" s="33">
-        <v>350</v>
-      </c>
-      <c r="F40" s="33">
-        <v>350</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D40" s="35"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
       <c r="G40" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I40" s="33">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="J40" s="33">
         <f t="shared" si="2"/>
@@ -5017,35 +4778,27 @@
       <c r="M40" s="31"/>
     </row>
     <row r="41" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A41" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>94</v>
+      <c r="A41" s="65"/>
+      <c r="B41" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="C41" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="33">
-        <v>3</v>
-      </c>
-      <c r="E41" s="33">
-        <v>3</v>
-      </c>
-      <c r="F41" s="33">
-        <v>3</v>
-      </c>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
       <c r="G41" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I41" s="33">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" s="33">
         <f t="shared" si="2"/>
@@ -5054,37 +4807,31 @@
       <c r="K41" s="31"/>
       <c r="L41" s="31"/>
       <c r="M41" s="31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A42" s="70"/>
+      <c r="A42" s="65"/>
       <c r="B42" s="34" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C42" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="35">
-        <v>4</v>
-      </c>
-      <c r="E42" s="33">
-        <v>4</v>
-      </c>
-      <c r="F42" s="33">
-        <v>4</v>
-      </c>
+      <c r="D42" s="35"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
       <c r="G42" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I42" s="33">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J42" s="33">
         <f t="shared" si="2"/>
@@ -5095,33 +4842,27 @@
       <c r="M42" s="31"/>
     </row>
     <row r="43" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A43" s="70"/>
+      <c r="A43" s="65"/>
       <c r="B43" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C43" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="35">
-        <v>3</v>
-      </c>
-      <c r="E43" s="33">
-        <v>3</v>
-      </c>
-      <c r="F43" s="33">
-        <v>3</v>
-      </c>
+      <c r="D43" s="35"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
       <c r="G43" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I43" s="33">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J43" s="33">
         <f t="shared" si="2"/>
@@ -5132,33 +4873,27 @@
       <c r="M43" s="31"/>
     </row>
     <row r="44" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A44" s="70"/>
+      <c r="A44" s="65"/>
       <c r="B44" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C44" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D44" s="35">
-        <v>6</v>
-      </c>
-      <c r="E44" s="33">
-        <v>6</v>
-      </c>
-      <c r="F44" s="33">
-        <v>6</v>
-      </c>
+      <c r="D44" s="35"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
       <c r="G44" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I44" s="33">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J44" s="33">
         <f t="shared" si="2"/>
@@ -5169,33 +4904,27 @@
       <c r="M44" s="31"/>
     </row>
     <row r="45" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A45" s="70"/>
+      <c r="A45" s="65"/>
       <c r="B45" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="35">
-        <v>160</v>
-      </c>
-      <c r="E45" s="33">
-        <v>160</v>
-      </c>
-      <c r="F45" s="33">
-        <v>160</v>
-      </c>
+      <c r="D45" s="35"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
       <c r="G45" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I45" s="33">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="J45" s="33">
         <f t="shared" si="2"/>
@@ -5206,33 +4935,27 @@
       <c r="M45" s="31"/>
     </row>
     <row r="46" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A46" s="70"/>
+      <c r="A46" s="65"/>
       <c r="B46" s="34" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="35">
-        <v>22</v>
-      </c>
-      <c r="E46" s="33">
-        <v>22</v>
-      </c>
-      <c r="F46" s="33">
-        <v>22</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D46" s="35"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
       <c r="G46" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I46" s="33">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J46" s="33">
         <f t="shared" si="2"/>
@@ -5243,33 +4966,29 @@
       <c r="M46" s="31"/>
     </row>
     <row r="47" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A47" s="71"/>
-      <c r="B47" s="34" t="s">
-        <v>5</v>
+      <c r="A47" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>94</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" s="35">
-        <v>693</v>
-      </c>
-      <c r="E47" s="33">
-        <v>693</v>
-      </c>
-      <c r="F47" s="33">
-        <v>693</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D47" s="35"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
       <c r="G47" s="33">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I47" s="33">
         <f t="shared" si="1"/>
-        <v>693</v>
+        <v>0</v>
       </c>
       <c r="J47" s="33">
         <f t="shared" si="2"/>
@@ -5279,20 +4998,330 @@
       <c r="L47" s="31"/>
       <c r="M47" s="31"/>
     </row>
+    <row r="48" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A48" s="72"/>
+      <c r="B48" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="35"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="33">
+        <f t="shared" ref="I48:I57" si="4">D48</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="33">
+        <f t="shared" ref="J48:J57" si="5">D48-E48</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31"/>
+    </row>
+    <row r="49" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A49" s="72"/>
+      <c r="B49" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="35"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+    </row>
+    <row r="50" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A50" s="72"/>
+      <c r="B50" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" s="35"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="31"/>
+      <c r="L50" s="31"/>
+      <c r="M50" s="31"/>
+    </row>
+    <row r="51" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A51" s="72"/>
+      <c r="B51" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="35"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
+      <c r="M51" s="31"/>
+    </row>
+    <row r="52" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A52" s="72"/>
+      <c r="B52" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="35"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+    </row>
+    <row r="53" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A53" s="72"/>
+      <c r="B53" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="35"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
+      <c r="M53" s="31"/>
+    </row>
+    <row r="54" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A54" s="72"/>
+      <c r="B54" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="35"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+    </row>
+    <row r="55" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A55" s="72"/>
+      <c r="B55" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55" s="35"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+    </row>
+    <row r="56" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A56" s="72"/>
+      <c r="B56" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="35"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="31"/>
+      <c r="L56" s="31"/>
+      <c r="M56" s="31"/>
+    </row>
+    <row r="57" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A57" s="72"/>
+      <c r="B57" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57" s="35"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H57" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="33">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="33">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="31"/>
+      <c r="L57" s="31"/>
+      <c r="M57" s="31"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A3:A13"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A14:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A46"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A3:A13"/>
-    <mergeCell ref="A14:A23"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A47:A57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE53E99-B784-4E44-A82E-4185F997F386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74659D99-1B8D-49EA-8BDE-700D4EB0781C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="115">
   <si>
     <t>TỔ CHỨC BIÊN CHẾ, TRANG BỊ HƯỚNG CHỦ YẾU</t>
   </si>
@@ -397,6 +397,12 @@
   </si>
   <si>
     <t>  </t>
+  </si>
+  <si>
+    <t>Cối 82mm</t>
+  </si>
+  <si>
+    <t>Cối 100mm</t>
   </si>
 </sst>
 </file>
@@ -829,7 +835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1026,15 +1032,15 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1044,8 +1050,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="2" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1396,7 +1408,7 @@
       <c r="L2" s="42"/>
       <c r="M2" s="43"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="14" customHeight="1">
       <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
@@ -3493,25 +3505,24 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9BFD24-F416-4E13-BF3D-CA2831AC61D2}">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="7" max="7" width="4.7265625" customWidth="1"/>
-    <col min="9" max="9" width="9.6328125" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" customWidth="1"/>
+    <col min="3" max="3" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.5" customHeight="1" thickBot="1">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:13" ht="15.5" thickBot="1">
+      <c r="A1" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="67" t="s">
+      <c r="C1" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="66" t="s">
         <v>83</v>
       </c>
       <c r="E1" s="69" t="s">
@@ -3520,7 +3531,7 @@
       <c r="F1" s="70"/>
       <c r="G1" s="70"/>
       <c r="H1" s="71"/>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="66" t="s">
         <v>84</v>
       </c>
       <c r="J1" s="69" t="s">
@@ -3531,10 +3542,10 @@
       <c r="M1" s="71"/>
     </row>
     <row r="2" spans="1:13" ht="30.5" thickBot="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
       <c r="E2" s="30" t="s">
         <v>86</v>
       </c>
@@ -3547,7 +3558,7 @@
       <c r="H2" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="68"/>
+      <c r="I2" s="67"/>
       <c r="J2" s="30" t="s">
         <v>89</v>
       </c>
@@ -3561,7 +3572,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.5" thickBot="1">
       <c r="A3" s="64" t="s">
         <v>93</v>
       </c>
@@ -3571,20 +3582,26 @@
       <c r="C3" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
+      <c r="D3" s="33">
+        <v>9</v>
+      </c>
+      <c r="E3" s="33">
+        <v>9</v>
+      </c>
+      <c r="F3" s="33">
+        <v>9</v>
+      </c>
       <c r="G3" s="33">
-        <f>IFERROR(E3/D3,0)</f>
-        <v>0</v>
+        <f>E3/D3</f>
+        <v>1</v>
       </c>
       <c r="H3" s="33">
-        <f>IFERROR(F3/E3,0)</f>
-        <v>0</v>
+        <f>F3/E3</f>
+        <v>1</v>
       </c>
       <c r="I3" s="33">
         <f>D3</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J3" s="33">
         <f>D3-E3</f>
@@ -3602,20 +3619,26 @@
       <c r="C4" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
+      <c r="D4" s="35">
+        <v>4</v>
+      </c>
+      <c r="E4" s="33">
+        <v>4</v>
+      </c>
+      <c r="F4" s="33">
+        <v>4</v>
+      </c>
       <c r="G4" s="33">
-        <f t="shared" ref="G4:G57" si="0">IFERROR(E4/D4,0)</f>
-        <v>0</v>
+        <f t="shared" ref="G4:H47" si="0">E4/D4</f>
+        <v>1</v>
       </c>
       <c r="H4" s="33">
-        <f>IFERROR(F4/E4,0)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I4" s="33">
         <f t="shared" ref="I4:I47" si="1">D4</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="33">
         <f t="shared" ref="J4:J47" si="2">D4-E4</f>
@@ -3633,20 +3656,26 @@
       <c r="C5" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
+      <c r="D5" s="35">
+        <v>4</v>
+      </c>
+      <c r="E5" s="33">
+        <v>4</v>
+      </c>
+      <c r="F5" s="33">
+        <v>4</v>
+      </c>
       <c r="G5" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="33">
-        <f t="shared" ref="H4:H57" si="3">IFERROR(F5/E5,0)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I5" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="33">
         <f>D5-E5</f>
@@ -3664,20 +3693,26 @@
       <c r="C6" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
+      <c r="D6" s="35">
+        <v>8</v>
+      </c>
+      <c r="E6" s="33">
+        <v>8</v>
+      </c>
+      <c r="F6" s="33">
+        <v>8</v>
+      </c>
       <c r="G6" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I6" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J6" s="33">
         <f t="shared" si="2"/>
@@ -3695,20 +3730,26 @@
       <c r="C7" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
+      <c r="D7" s="35">
+        <v>9</v>
+      </c>
+      <c r="E7" s="33">
+        <v>9</v>
+      </c>
+      <c r="F7" s="33">
+        <v>9</v>
+      </c>
       <c r="G7" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I7" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J7" s="33">
         <f t="shared" si="2"/>
@@ -3726,20 +3767,26 @@
       <c r="C8" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
+      <c r="D8" s="35">
+        <v>72</v>
+      </c>
+      <c r="E8" s="33">
+        <v>72</v>
+      </c>
+      <c r="F8" s="33">
+        <v>71</v>
+      </c>
       <c r="G8" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H8" s="72">
+        <f t="shared" si="0"/>
+        <v>0.98611111111111116</v>
       </c>
       <c r="I8" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J8" s="33">
         <f t="shared" si="2"/>
@@ -3763,20 +3810,26 @@
       <c r="C9" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
+      <c r="D9" s="35">
+        <v>8</v>
+      </c>
+      <c r="E9" s="33">
+        <v>8</v>
+      </c>
+      <c r="F9" s="33">
+        <v>8</v>
+      </c>
       <c r="G9" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I9" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J9" s="33">
         <f t="shared" si="2"/>
@@ -3794,20 +3847,26 @@
       <c r="C10" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
+      <c r="D10" s="35">
+        <v>36</v>
+      </c>
+      <c r="E10" s="33">
+        <v>36</v>
+      </c>
+      <c r="F10" s="33">
+        <v>36</v>
+      </c>
       <c r="G10" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I10" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J10" s="33">
         <f t="shared" si="2"/>
@@ -3825,20 +3884,26 @@
       <c r="C11" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
+      <c r="D11" s="35">
+        <v>486</v>
+      </c>
+      <c r="E11" s="33">
+        <v>486</v>
+      </c>
+      <c r="F11" s="33">
+        <v>474</v>
+      </c>
       <c r="G11" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H11" s="72">
+        <f t="shared" si="0"/>
+        <v>0.97530864197530864</v>
       </c>
       <c r="I11" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="J11" s="33">
         <f t="shared" si="2"/>
@@ -3862,20 +3927,26 @@
       <c r="C12" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
+      <c r="D12" s="35">
+        <v>42</v>
+      </c>
+      <c r="E12" s="33">
+        <v>42</v>
+      </c>
+      <c r="F12" s="33">
+        <v>42</v>
+      </c>
       <c r="G12" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I12" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J12" s="33">
         <f t="shared" si="2"/>
@@ -3886,27 +3957,33 @@
       <c r="M12" s="31"/>
     </row>
     <row r="13" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A13" s="66"/>
+      <c r="A13" s="68"/>
       <c r="B13" s="34" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
+      <c r="D13" s="37">
+        <v>2403</v>
+      </c>
+      <c r="E13" s="36">
+        <v>2403</v>
+      </c>
+      <c r="F13" s="36">
+        <v>2403</v>
+      </c>
       <c r="G13" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I13" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2403</v>
       </c>
       <c r="J13" s="33">
         <f t="shared" si="2"/>
@@ -3916,7 +3993,7 @@
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
     </row>
-    <row r="14" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.5" thickBot="1">
       <c r="A14" s="64" t="s">
         <v>105</v>
       </c>
@@ -3926,20 +4003,26 @@
       <c r="C14" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
+      <c r="D14" s="33">
+        <v>3</v>
+      </c>
+      <c r="E14" s="33">
+        <v>3</v>
+      </c>
+      <c r="F14" s="33">
+        <v>3</v>
+      </c>
       <c r="G14" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I14" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="33">
         <f t="shared" si="2"/>
@@ -3952,25 +4035,31 @@
     <row r="15" spans="1:13" ht="18.5" thickBot="1">
       <c r="A15" s="65"/>
       <c r="B15" s="34" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C15" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
+      <c r="D15" s="35">
+        <v>3</v>
+      </c>
+      <c r="E15" s="33">
+        <v>3</v>
+      </c>
+      <c r="F15" s="33">
+        <v>3</v>
+      </c>
       <c r="G15" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I15" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="33">
         <f t="shared" si="2"/>
@@ -3983,25 +4072,31 @@
     <row r="16" spans="1:13" ht="18.5" thickBot="1">
       <c r="A16" s="65"/>
       <c r="B16" s="34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C16" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
+      <c r="D16" s="35">
+        <v>4</v>
+      </c>
+      <c r="E16" s="33">
+        <v>4</v>
+      </c>
+      <c r="F16" s="33">
+        <v>4</v>
+      </c>
       <c r="G16" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I16" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J16" s="33">
         <f t="shared" si="2"/>
@@ -4014,25 +4109,31 @@
     <row r="17" spans="1:13" ht="18.5" thickBot="1">
       <c r="A17" s="65"/>
       <c r="B17" s="34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
+      <c r="D17" s="35">
+        <v>3</v>
+      </c>
+      <c r="E17" s="33">
+        <v>3</v>
+      </c>
+      <c r="F17" s="33">
+        <v>3</v>
+      </c>
       <c r="G17" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I17" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="33">
         <f t="shared" si="2"/>
@@ -4042,28 +4143,34 @@
       <c r="L17" s="31"/>
       <c r="M17" s="31"/>
     </row>
-    <row r="18" spans="1:13" ht="19" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="36.5" thickBot="1">
       <c r="A18" s="65"/>
       <c r="B18" s="34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="35"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
+      <c r="D18" s="35">
+        <v>30</v>
+      </c>
+      <c r="E18" s="33">
+        <v>30</v>
+      </c>
+      <c r="F18" s="33">
+        <v>29</v>
+      </c>
       <c r="G18" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H18" s="72">
+        <f t="shared" si="0"/>
+        <v>0.96666666666666667</v>
       </c>
       <c r="I18" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J18" s="33">
         <f t="shared" si="2"/>
@@ -4082,25 +4189,31 @@
     <row r="19" spans="1:13" ht="18.5" thickBot="1">
       <c r="A19" s="65"/>
       <c r="B19" s="34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
+      <c r="D19" s="35">
+        <v>4</v>
+      </c>
+      <c r="E19" s="33">
+        <v>4</v>
+      </c>
+      <c r="F19" s="33">
+        <v>4</v>
+      </c>
       <c r="G19" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I19" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J19" s="33">
         <f t="shared" si="2"/>
@@ -4113,25 +4226,31 @@
     <row r="20" spans="1:13" ht="18.5" thickBot="1">
       <c r="A20" s="65"/>
       <c r="B20" s="34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
+      <c r="D20" s="35">
+        <v>18</v>
+      </c>
+      <c r="E20" s="33">
+        <v>18</v>
+      </c>
+      <c r="F20" s="33">
+        <v>18</v>
+      </c>
       <c r="G20" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I20" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J20" s="33">
         <f t="shared" si="2"/>
@@ -4144,25 +4263,31 @@
     <row r="21" spans="1:13" ht="36.5" thickBot="1">
       <c r="A21" s="65"/>
       <c r="B21" s="34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C21" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
+      <c r="D21" s="35">
+        <v>161</v>
+      </c>
+      <c r="E21" s="33">
+        <v>161</v>
+      </c>
+      <c r="F21" s="33">
+        <v>155</v>
+      </c>
       <c r="G21" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H21" s="72">
+        <f t="shared" si="0"/>
+        <v>0.96273291925465843</v>
       </c>
       <c r="I21" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="J21" s="33">
         <f t="shared" si="2"/>
@@ -4181,25 +4306,31 @@
     <row r="22" spans="1:13" ht="18.5" thickBot="1">
       <c r="A22" s="65"/>
       <c r="B22" s="34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C22" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
+      <c r="D22" s="35">
+        <v>12</v>
+      </c>
+      <c r="E22" s="33">
+        <v>12</v>
+      </c>
+      <c r="F22" s="33">
+        <v>12</v>
+      </c>
       <c r="G22" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I22" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J22" s="33">
         <f t="shared" si="2"/>
@@ -4209,28 +4340,34 @@
       <c r="L22" s="31"/>
       <c r="M22" s="31"/>
     </row>
-    <row r="23" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="65"/>
+    <row r="23" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A23" s="68"/>
       <c r="B23" s="34" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="35"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
+        <v>104</v>
+      </c>
+      <c r="D23" s="35">
+        <v>846</v>
+      </c>
+      <c r="E23" s="33">
+        <v>846</v>
+      </c>
+      <c r="F23" s="33">
+        <v>846</v>
+      </c>
       <c r="G23" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I23" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>846</v>
       </c>
       <c r="J23" s="33">
         <f t="shared" si="2"/>
@@ -4240,28 +4377,36 @@
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
     </row>
-    <row r="24" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A24" s="66"/>
-      <c r="B24" s="34" t="s">
-        <v>5</v>
+    <row r="24" spans="1:13" ht="54.5" thickBot="1">
+      <c r="A24" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="73" t="s">
+        <v>94</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
+        <v>50</v>
+      </c>
+      <c r="D24" s="33">
+        <v>3</v>
+      </c>
+      <c r="E24" s="33">
+        <v>3</v>
+      </c>
+      <c r="F24" s="33">
+        <v>3</v>
+      </c>
       <c r="G24" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I24" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="33">
         <f t="shared" si="2"/>
@@ -4271,30 +4416,34 @@
       <c r="L24" s="31"/>
       <c r="M24" s="31"/>
     </row>
-    <row r="25" spans="1:13" ht="21" customHeight="1" thickBot="1">
-      <c r="A25" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>94</v>
+    <row r="25" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A25" s="65"/>
+      <c r="B25" s="73" t="s">
+        <v>113</v>
       </c>
       <c r="C25" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
+      <c r="D25" s="33">
+        <v>1</v>
+      </c>
+      <c r="E25" s="33">
+        <v>1</v>
+      </c>
+      <c r="F25" s="33">
+        <v>1</v>
+      </c>
       <c r="G25" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I25" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="33">
         <f t="shared" si="2"/>
@@ -4304,28 +4453,34 @@
       <c r="L25" s="31"/>
       <c r="M25" s="31"/>
     </row>
-    <row r="26" spans="1:13" ht="18.5" thickBot="1">
+    <row r="26" spans="1:13" ht="36.5" thickBot="1">
       <c r="A26" s="65"/>
-      <c r="B26" s="34" t="s">
-        <v>95</v>
+      <c r="B26" s="74" t="s">
+        <v>97</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="35"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
+      <c r="D26" s="35">
+        <v>2</v>
+      </c>
+      <c r="E26" s="33">
+        <v>2</v>
+      </c>
+      <c r="F26" s="33">
+        <v>2</v>
+      </c>
       <c r="G26" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I26" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="33">
         <f t="shared" si="2"/>
@@ -4335,28 +4490,34 @@
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
     </row>
-    <row r="27" spans="1:13" ht="18.5" thickBot="1">
+    <row r="27" spans="1:13" ht="36.5" thickBot="1">
       <c r="A27" s="65"/>
-      <c r="B27" s="34" t="s">
-        <v>96</v>
+      <c r="B27" s="74" t="s">
+        <v>98</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="35"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
+      <c r="D27" s="35">
+        <v>3</v>
+      </c>
+      <c r="E27" s="33">
+        <v>3</v>
+      </c>
+      <c r="F27" s="33">
+        <v>3</v>
+      </c>
       <c r="G27" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I27" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" s="33">
         <f t="shared" si="2"/>
@@ -4366,28 +4527,34 @@
       <c r="L27" s="31"/>
       <c r="M27" s="31"/>
     </row>
-    <row r="28" spans="1:13" ht="18.5" thickBot="1">
+    <row r="28" spans="1:13" ht="36.5" thickBot="1">
       <c r="A28" s="65"/>
-      <c r="B28" s="34" t="s">
-        <v>97</v>
+      <c r="B28" s="74" t="s">
+        <v>99</v>
       </c>
       <c r="C28" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="35"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
+      <c r="D28" s="35">
+        <v>18</v>
+      </c>
+      <c r="E28" s="33">
+        <v>18</v>
+      </c>
+      <c r="F28" s="33">
+        <v>18</v>
+      </c>
       <c r="G28" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I28" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J28" s="33">
         <f t="shared" si="2"/>
@@ -4397,28 +4564,34 @@
       <c r="L28" s="31"/>
       <c r="M28" s="31"/>
     </row>
-    <row r="29" spans="1:13" ht="18.5" thickBot="1">
+    <row r="29" spans="1:13" ht="36.5" thickBot="1">
       <c r="A29" s="65"/>
-      <c r="B29" s="34" t="s">
-        <v>98</v>
+      <c r="B29" s="74" t="s">
+        <v>100</v>
       </c>
       <c r="C29" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
+      <c r="D29" s="35">
+        <v>2</v>
+      </c>
+      <c r="E29" s="33">
+        <v>2</v>
+      </c>
+      <c r="F29" s="33">
+        <v>2</v>
+      </c>
       <c r="G29" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I29" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="33">
         <f t="shared" si="2"/>
@@ -4428,28 +4601,34 @@
       <c r="L29" s="31"/>
       <c r="M29" s="31"/>
     </row>
-    <row r="30" spans="1:13" ht="18.5" thickBot="1">
+    <row r="30" spans="1:13" ht="54.5" thickBot="1">
       <c r="A30" s="65"/>
-      <c r="B30" s="34" t="s">
-        <v>99</v>
+      <c r="B30" s="74" t="s">
+        <v>101</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="35"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
+      <c r="D30" s="35">
+        <v>9</v>
+      </c>
+      <c r="E30" s="33">
+        <v>9</v>
+      </c>
+      <c r="F30" s="33">
+        <v>9</v>
+      </c>
       <c r="G30" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I30" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J30" s="33">
         <f t="shared" si="2"/>
@@ -4459,28 +4638,34 @@
       <c r="L30" s="31"/>
       <c r="M30" s="31"/>
     </row>
-    <row r="31" spans="1:13" ht="36.5" thickBot="1">
+    <row r="31" spans="1:13" ht="54.5" thickBot="1">
       <c r="A31" s="65"/>
-      <c r="B31" s="34" t="s">
-        <v>100</v>
+      <c r="B31" s="74" t="s">
+        <v>102</v>
       </c>
       <c r="C31" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
+      <c r="D31" s="35">
+        <v>96</v>
+      </c>
+      <c r="E31" s="33">
+        <v>96</v>
+      </c>
+      <c r="F31" s="33">
+        <v>92</v>
+      </c>
       <c r="G31" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H31" s="72">
+        <f t="shared" si="0"/>
+        <v>0.95833333333333337</v>
       </c>
       <c r="I31" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J31" s="33">
         <f t="shared" si="2"/>
@@ -4496,28 +4681,34 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="18.5" thickBot="1">
+    <row r="32" spans="1:13" ht="36.5" thickBot="1">
       <c r="A32" s="65"/>
-      <c r="B32" s="34" t="s">
-        <v>101</v>
+      <c r="B32" s="74" t="s">
+        <v>103</v>
       </c>
       <c r="C32" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
+      <c r="D32" s="35">
+        <v>4</v>
+      </c>
+      <c r="E32" s="33">
+        <v>4</v>
+      </c>
+      <c r="F32" s="33">
+        <v>4</v>
+      </c>
       <c r="G32" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I32" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J32" s="33">
         <f t="shared" si="2"/>
@@ -4527,28 +4718,34 @@
       <c r="L32" s="31"/>
       <c r="M32" s="31"/>
     </row>
-    <row r="33" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A33" s="65"/>
-      <c r="B33" s="34" t="s">
-        <v>102</v>
+    <row r="33" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A33" s="68"/>
+      <c r="B33" s="74" t="s">
+        <v>5</v>
       </c>
       <c r="C33" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
+      <c r="D33" s="35">
+        <v>514</v>
+      </c>
+      <c r="E33" s="33">
+        <v>514</v>
+      </c>
+      <c r="F33" s="33">
+        <v>514</v>
+      </c>
       <c r="G33" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I33" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="J33" s="33">
         <f t="shared" si="2"/>
@@ -4558,28 +4755,36 @@
       <c r="L33" s="31"/>
       <c r="M33" s="31"/>
     </row>
-    <row r="34" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="34" t="s">
-        <v>103</v>
+    <row r="34" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A34" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>97</v>
       </c>
       <c r="C34" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
+      <c r="D34" s="33">
+        <v>2</v>
+      </c>
+      <c r="E34" s="33">
+        <v>2</v>
+      </c>
+      <c r="F34" s="33">
+        <v>2</v>
+      </c>
       <c r="G34" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I34" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="33">
         <f t="shared" si="2"/>
@@ -4590,27 +4795,33 @@
       <c r="M34" s="31"/>
     </row>
     <row r="35" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A35" s="66"/>
+      <c r="A35" s="65"/>
       <c r="B35" s="34" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="C35" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="35"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
+      <c r="D35" s="35">
+        <v>18</v>
+      </c>
+      <c r="E35" s="33">
+        <v>18</v>
+      </c>
+      <c r="F35" s="33">
+        <v>18</v>
+      </c>
       <c r="G35" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I35" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J35" s="33">
         <f t="shared" si="2"/>
@@ -4620,30 +4831,34 @@
       <c r="L35" s="31"/>
       <c r="M35" s="31"/>
     </row>
-    <row r="36" spans="1:13" ht="26.5" customHeight="1" thickBot="1">
-      <c r="A36" s="64" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>94</v>
+    <row r="36" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A36" s="65"/>
+      <c r="B36" s="34" t="s">
+        <v>100</v>
       </c>
       <c r="C36" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="35"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
+      <c r="D36" s="35">
+        <v>2</v>
+      </c>
+      <c r="E36" s="33">
+        <v>2</v>
+      </c>
+      <c r="F36" s="33">
+        <v>2</v>
+      </c>
       <c r="G36" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I36" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="33">
         <f t="shared" si="2"/>
@@ -4656,25 +4871,31 @@
     <row r="37" spans="1:13" ht="18.5" thickBot="1">
       <c r="A37" s="65"/>
       <c r="B37" s="34" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C37" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="35"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
+      <c r="D37" s="35">
+        <v>9</v>
+      </c>
+      <c r="E37" s="33">
+        <v>9</v>
+      </c>
+      <c r="F37" s="33">
+        <v>9</v>
+      </c>
       <c r="G37" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I37" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J37" s="33">
         <f t="shared" si="2"/>
@@ -4687,25 +4908,31 @@
     <row r="38" spans="1:13" ht="18.5" thickBot="1">
       <c r="A38" s="65"/>
       <c r="B38" s="34" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C38" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="35"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
+      <c r="D38" s="35">
+        <v>69</v>
+      </c>
+      <c r="E38" s="33">
+        <v>69</v>
+      </c>
+      <c r="F38" s="33">
+        <v>67</v>
+      </c>
       <c r="G38" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H38" s="72">
+        <f t="shared" si="0"/>
+        <v>0.97101449275362317</v>
       </c>
       <c r="I38" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="J38" s="33">
         <f t="shared" si="2"/>
@@ -4718,25 +4945,31 @@
     <row r="39" spans="1:13" ht="18.5" thickBot="1">
       <c r="A39" s="65"/>
       <c r="B39" s="34" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C39" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="35"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
+      <c r="D39" s="35">
+        <v>4</v>
+      </c>
+      <c r="E39" s="33">
+        <v>4</v>
+      </c>
+      <c r="F39" s="33">
+        <v>4</v>
+      </c>
       <c r="G39" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I39" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39" s="33">
         <f t="shared" si="2"/>
@@ -4747,27 +4980,33 @@
       <c r="M39" s="31"/>
     </row>
     <row r="40" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A40" s="65"/>
+      <c r="A40" s="68"/>
       <c r="B40" s="34" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="35"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
+        <v>104</v>
+      </c>
+      <c r="D40" s="35">
+        <v>350</v>
+      </c>
+      <c r="E40" s="33">
+        <v>350</v>
+      </c>
+      <c r="F40" s="33">
+        <v>350</v>
+      </c>
       <c r="G40" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I40" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="J40" s="33">
         <f t="shared" si="2"/>
@@ -4777,28 +5016,36 @@
       <c r="L40" s="31"/>
       <c r="M40" s="31"/>
     </row>
-    <row r="41" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A41" s="65"/>
-      <c r="B41" s="34" t="s">
-        <v>99</v>
+    <row r="41" spans="1:13" ht="54.5" thickBot="1">
+      <c r="A41" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>94</v>
       </c>
       <c r="C41" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
+      <c r="D41" s="33">
+        <v>3</v>
+      </c>
+      <c r="E41" s="33">
+        <v>3</v>
+      </c>
+      <c r="F41" s="33">
+        <v>3</v>
+      </c>
       <c r="G41" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I41" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J41" s="33">
         <f t="shared" si="2"/>
@@ -4813,25 +5060,31 @@
     <row r="42" spans="1:13" ht="18.5" thickBot="1">
       <c r="A42" s="65"/>
       <c r="B42" s="34" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C42" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="35"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
+      <c r="D42" s="35">
+        <v>4</v>
+      </c>
+      <c r="E42" s="33">
+        <v>4</v>
+      </c>
+      <c r="F42" s="33">
+        <v>4</v>
+      </c>
       <c r="G42" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I42" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J42" s="33">
         <f t="shared" si="2"/>
@@ -4844,25 +5097,31 @@
     <row r="43" spans="1:13" ht="18.5" thickBot="1">
       <c r="A43" s="65"/>
       <c r="B43" s="34" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C43" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="35"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
+      <c r="D43" s="35">
+        <v>3</v>
+      </c>
+      <c r="E43" s="33">
+        <v>3</v>
+      </c>
+      <c r="F43" s="33">
+        <v>3</v>
+      </c>
       <c r="G43" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I43" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" s="33">
         <f t="shared" si="2"/>
@@ -4875,25 +5134,31 @@
     <row r="44" spans="1:13" ht="18.5" thickBot="1">
       <c r="A44" s="65"/>
       <c r="B44" s="34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C44" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D44" s="35"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
+      <c r="D44" s="35">
+        <v>6</v>
+      </c>
+      <c r="E44" s="33">
+        <v>6</v>
+      </c>
+      <c r="F44" s="33">
+        <v>6</v>
+      </c>
       <c r="G44" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I44" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J44" s="33">
         <f t="shared" si="2"/>
@@ -4906,25 +5171,31 @@
     <row r="45" spans="1:13" ht="18.5" thickBot="1">
       <c r="A45" s="65"/>
       <c r="B45" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C45" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="35"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
+      <c r="D45" s="35">
+        <v>160</v>
+      </c>
+      <c r="E45" s="33">
+        <v>160</v>
+      </c>
+      <c r="F45" s="33">
+        <v>160</v>
+      </c>
       <c r="G45" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I45" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="J45" s="33">
         <f t="shared" si="2"/>
@@ -4937,25 +5208,31 @@
     <row r="46" spans="1:13" ht="18.5" thickBot="1">
       <c r="A46" s="65"/>
       <c r="B46" s="34" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" s="35"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
+        <v>50</v>
+      </c>
+      <c r="D46" s="35">
+        <v>22</v>
+      </c>
+      <c r="E46" s="33">
+        <v>22</v>
+      </c>
+      <c r="F46" s="33">
+        <v>22</v>
+      </c>
       <c r="G46" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I46" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J46" s="33">
         <f t="shared" si="2"/>
@@ -4966,29 +5243,33 @@
       <c r="M46" s="31"/>
     </row>
     <row r="47" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A47" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>94</v>
+      <c r="A47" s="68"/>
+      <c r="B47" s="34" t="s">
+        <v>5</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" s="35"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
+        <v>104</v>
+      </c>
+      <c r="D47" s="35">
+        <v>693</v>
+      </c>
+      <c r="E47" s="33">
+        <v>693</v>
+      </c>
+      <c r="F47" s="33">
+        <v>693</v>
+      </c>
       <c r="G47" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="I47" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="J47" s="33">
         <f t="shared" si="2"/>
@@ -4998,330 +5279,20 @@
       <c r="L47" s="31"/>
       <c r="M47" s="31"/>
     </row>
-    <row r="48" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A48" s="72"/>
-      <c r="B48" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="35"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="33">
-        <f t="shared" ref="I48:I57" si="4">D48</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="33">
-        <f t="shared" ref="J48:J57" si="5">D48-E48</f>
-        <v>0</v>
-      </c>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
-    </row>
-    <row r="49" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A49" s="72"/>
-      <c r="B49" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="35"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J49" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
-    </row>
-    <row r="50" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A50" s="72"/>
-      <c r="B50" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D50" s="35"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-    </row>
-    <row r="51" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A51" s="72"/>
-      <c r="B51" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="35"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
-    </row>
-    <row r="52" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A52" s="72"/>
-      <c r="B52" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52" s="35"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="31"/>
-    </row>
-    <row r="53" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A53" s="72"/>
-      <c r="B53" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D53" s="35"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-    </row>
-    <row r="54" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A54" s="72"/>
-      <c r="B54" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D54" s="35"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
-    </row>
-    <row r="55" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A55" s="72"/>
-      <c r="B55" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C55" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-    </row>
-    <row r="56" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A56" s="72"/>
-      <c r="B56" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C56" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D56" s="35"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="33"/>
-      <c r="G56" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="31"/>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
-    </row>
-    <row r="57" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A57" s="72"/>
-      <c r="B57" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="33">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C1:C2"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A14:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A46"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A47:A57"/>
+    <mergeCell ref="A14:A23"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="A41:A47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74659D99-1B8D-49EA-8BDE-700D4EB0781C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630977E8-0F2D-4260-90D4-0864A000466D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="132">
   <si>
     <t>TỔ CHỨC BIÊN CHẾ, TRANG BỊ HƯỚNG CHỦ YẾU</t>
   </si>
@@ -404,12 +415,63 @@
   <si>
     <t>Cối 100mm</t>
   </si>
+  <si>
+    <t>Gạo, thực phẩm</t>
+  </si>
+  <si>
+    <t>Ngày ăn</t>
+  </si>
+  <si>
+    <t>Lương khô</t>
+  </si>
+  <si>
+    <t>,,</t>
+  </si>
+  <si>
+    <t>Đường sữa thương binh</t>
+  </si>
+  <si>
+    <t>%QS</t>
+  </si>
+  <si>
+    <t>Quân lương chiến đấu</t>
+  </si>
+  <si>
+    <t>Quân trang chiến đấu</t>
+  </si>
+  <si>
+    <t>Túi y sỹ</t>
+  </si>
+  <si>
+    <t>Túi</t>
+  </si>
+  <si>
+    <t>Túi y tá</t>
+  </si>
+  <si>
+    <t>Túi cứu thương</t>
+  </si>
+  <si>
+    <t>Băng cá nhân</t>
+  </si>
+  <si>
+    <t>C/người</t>
+  </si>
+  <si>
+    <t>Dầu thắp</t>
+  </si>
+  <si>
+    <t>Ngày</t>
+  </si>
+  <si>
+    <t>Quân trang thương binh</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,6 +608,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -832,8 +902,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -948,6 +1019,45 @@
     <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -990,78 +1100,40 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường 2" xfId="1" xr:uid="{E2A62A3F-70A5-4DC5-A358-9BA0F56286C7}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1077,9 +1149,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1117,7 +1189,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1223,7 +1295,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1365,7 +1437,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1374,79 +1446,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D56173A-C175-4526-B966-989AD58BFBEE}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="53"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="43"/>
-    </row>
-    <row r="3" spans="1:13" ht="14" customHeight="1">
-      <c r="A3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="44" t="s">
+      <c r="A2" s="54"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="56"/>
+    </row>
+    <row r="3" spans="1:13" ht="13.95" customHeight="1">
+      <c r="A3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1455,8 +1527,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1472,7 +1544,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="57"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1489,7 +1561,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21">
+    <row r="6" spans="1:13" ht="20.399999999999999">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1544,7 +1616,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="20.399999999999999">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1631,7 +1703,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="21">
+    <row r="11" spans="1:13" ht="20.399999999999999">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -1682,7 +1754,7 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" ht="21">
+    <row r="14" spans="1:13" ht="20.399999999999999">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -1699,7 +1771,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" ht="21">
+    <row r="15" spans="1:13" ht="20.399999999999999">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -1803,79 +1875,79 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F16AEE-EEF3-41FC-9011-B3FA05A2337A}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="53"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="43"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="56"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="44" t="s">
+      <c r="A3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1884,8 +1956,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1901,7 +1973,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="57"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1918,7 +1990,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18">
+    <row r="6" spans="1:13" ht="19.2">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -2012,7 +2084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18">
+    <row r="8" spans="1:13" ht="19.2">
       <c r="A8" s="10" t="s">
         <v>29</v>
       </c>
@@ -2119,7 +2191,7 @@
       </c>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="18">
+    <row r="11" spans="1:13" ht="19.2">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -2379,35 +2451,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB776F58-BBC1-4BAD-8576-583DC692D30D}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="45" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="I1" s="58" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
       <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
@@ -2420,8 +2492,8 @@
       <c r="G2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
@@ -2434,23 +2506,23 @@
         <v>36</v>
       </c>
       <c r="D3" s="24">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E3" s="23">
         <f>D3/C3</f>
-        <v>0.97222222222222221</v>
+        <v>2.7777777777777776E-2</v>
       </c>
       <c r="F3" s="23">
         <f>G3/D3</f>
-        <v>0.97142857142857142</v>
+        <v>0</v>
       </c>
       <c r="G3" s="24">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H3" s="24"/>
       <c r="I3" s="23">
         <f>C3-D3</f>
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2464,23 +2536,23 @@
         <v>439</v>
       </c>
       <c r="D4" s="24">
-        <v>439</v>
+        <v>1</v>
       </c>
       <c r="E4" s="23">
         <f>D4/C4</f>
-        <v>1</v>
+        <v>2.2779043280182231E-3</v>
       </c>
       <c r="F4" s="23">
         <f t="shared" ref="F4:F7" si="0">G4/D4</f>
-        <v>0.99772209567198178</v>
+        <v>0</v>
       </c>
       <c r="G4" s="24">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="H4" s="24"/>
       <c r="I4" s="23">
         <f>C4-D4</f>
-        <v>0</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2494,23 +2566,23 @@
         <v>27</v>
       </c>
       <c r="D5" s="24">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E5" s="23">
         <f>D5/C5</f>
-        <v>1</v>
+        <v>3.7037037037037035E-2</v>
       </c>
       <c r="F5" s="23">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="24">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H5" s="24"/>
       <c r="I5" s="23">
         <f t="shared" ref="I5:I7" si="1">C5-D5</f>
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2524,23 +2596,23 @@
         <v>6</v>
       </c>
       <c r="D6" s="24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6" s="23">
         <f>D6/C6</f>
-        <v>1</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="F6" s="23">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>0</v>
       </c>
       <c r="G6" s="24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6" s="24"/>
       <c r="I6" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2554,23 +2626,23 @@
         <v>2073</v>
       </c>
       <c r="D7" s="24">
-        <v>2073</v>
+        <v>1</v>
       </c>
       <c r="E7" s="23">
         <f>D7/C7</f>
-        <v>1</v>
+        <v>4.8239266763145202E-4</v>
       </c>
       <c r="F7" s="23">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="24">
-        <v>2073</v>
+        <v>0</v>
       </c>
       <c r="H7" s="24"/>
       <c r="I7" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2072</v>
       </c>
     </row>
   </sheetData>
@@ -2589,7 +2661,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D657F165-9D3D-496E-8012-68B69501198F}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:5" ht="24">
       <c r="A1" s="25" t="s">
@@ -2681,34 +2753,37 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6AD6F2A-F3DA-482E-A27C-72512E35A6E7}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="59" t="s">
+      <c r="E1" s="46"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="50"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="53"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
       <c r="D2" s="26" t="s">
         <v>65</v>
       </c>
@@ -2732,8 +2807,12 @@
       <c r="A3" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="25"/>
+      <c r="B3" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>116</v>
+      </c>
       <c r="D3" s="27"/>
       <c r="E3" s="27"/>
       <c r="F3" s="27"/>
@@ -2745,8 +2824,12 @@
       <c r="A4" s="24">
         <v>2</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="25"/>
+      <c r="B4" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>118</v>
+      </c>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
       <c r="F4" s="27"/>
@@ -2758,8 +2841,12 @@
       <c r="A5" s="24">
         <v>3</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="25"/>
+      <c r="B5" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>120</v>
+      </c>
       <c r="D5" s="27"/>
       <c r="E5" s="27"/>
       <c r="F5" s="27"/>
@@ -2771,8 +2858,12 @@
       <c r="A6" s="24">
         <v>4</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="25"/>
+      <c r="B6" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>120</v>
+      </c>
       <c r="D6" s="27"/>
       <c r="E6" s="27"/>
       <c r="F6" s="27"/>
@@ -2784,14 +2875,118 @@
       <c r="A7" s="24">
         <v>5</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="25"/>
+      <c r="B7" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>118</v>
+      </c>
       <c r="D7" s="27"/>
       <c r="E7" s="27"/>
       <c r="F7" s="27"/>
       <c r="G7" s="24"/>
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="24">
+        <v>6</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="24">
+        <v>7</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="24">
+        <v>8</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="24">
+        <v>9</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="24">
+        <v>10</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="24">
+        <v>11</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2808,79 +3003,79 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90BB609-02C3-4480-ABA1-81B8EB7FC6E5}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="53"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="43"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="56"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="44" t="s">
+      <c r="A3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2889,8 +3084,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2906,7 +3101,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="57"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2923,7 +3118,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18">
+    <row r="6" spans="1:13" ht="19.2">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -3017,7 +3212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18">
+    <row r="8" spans="1:13" ht="19.2">
       <c r="A8" s="10" t="s">
         <v>29</v>
       </c>
@@ -3124,7 +3319,7 @@
       </c>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="18">
+    <row r="11" spans="1:13" ht="19.2">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -3384,91 +3579,91 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18CCF06B-A044-4E5A-A947-A016657D51E8}">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62" t="s">
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62" t="s">
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="62"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="62" t="s">
+      <c r="F2" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="62" t="s">
+      <c r="I2" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="62"/>
-      <c r="L2" s="63" t="s">
+      <c r="K2" s="65"/>
+      <c r="L2" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="63"/>
+      <c r="M2" s="66"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="62"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
       <c r="J4" s="29" t="s">
         <v>79</v>
       </c>
@@ -3506,46 +3701,46 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9BFD24-F416-4E13-BF3D-CA2831AC61D2}">
   <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="16.6328125" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.5" thickBot="1">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:13" ht="16.2" thickBot="1">
+      <c r="A1" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="66" t="s">
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="J1" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="71"/>
-    </row>
-    <row r="2" spans="1:13" ht="30.5" thickBot="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="69"/>
+    </row>
+    <row r="2" spans="1:13" ht="31.8" thickBot="1">
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
       <c r="E2" s="30" t="s">
         <v>86</v>
       </c>
@@ -3558,7 +3753,7 @@
       <c r="H2" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="67"/>
+      <c r="I2" s="74"/>
       <c r="J2" s="30" t="s">
         <v>89</v>
       </c>
@@ -3572,8 +3767,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A3" s="70" t="s">
         <v>93</v>
       </c>
       <c r="B3" s="31" t="s">
@@ -3611,8 +3806,8 @@
       <c r="L3" s="31"/>
       <c r="M3" s="31"/>
     </row>
-    <row r="4" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A4" s="65"/>
+    <row r="4" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A4" s="71"/>
       <c r="B4" s="34" t="s">
         <v>95</v>
       </c>
@@ -3648,8 +3843,8 @@
       <c r="L4" s="31"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A5" s="65"/>
+    <row r="5" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A5" s="71"/>
       <c r="B5" s="34" t="s">
         <v>96</v>
       </c>
@@ -3685,8 +3880,8 @@
       <c r="L5" s="31"/>
       <c r="M5" s="31"/>
     </row>
-    <row r="6" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A6" s="65"/>
+    <row r="6" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A6" s="71"/>
       <c r="B6" s="34" t="s">
         <v>97</v>
       </c>
@@ -3722,8 +3917,8 @@
       <c r="L6" s="31"/>
       <c r="M6" s="31"/>
     </row>
-    <row r="7" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A7" s="65"/>
+    <row r="7" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A7" s="71"/>
       <c r="B7" s="34" t="s">
         <v>98</v>
       </c>
@@ -3759,8 +3954,8 @@
       <c r="L7" s="31"/>
       <c r="M7" s="31"/>
     </row>
-    <row r="8" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A8" s="65"/>
+    <row r="8" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A8" s="71"/>
       <c r="B8" s="34" t="s">
         <v>99</v>
       </c>
@@ -3780,7 +3975,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H8" s="72">
+      <c r="H8" s="38">
         <f t="shared" si="0"/>
         <v>0.98611111111111116</v>
       </c>
@@ -3802,8 +3997,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A9" s="65"/>
+    <row r="9" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A9" s="71"/>
       <c r="B9" s="34" t="s">
         <v>100</v>
       </c>
@@ -3839,8 +4034,8 @@
       <c r="L9" s="31"/>
       <c r="M9" s="31"/>
     </row>
-    <row r="10" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A10" s="65"/>
+    <row r="10" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A10" s="71"/>
       <c r="B10" s="34" t="s">
         <v>101</v>
       </c>
@@ -3876,8 +4071,8 @@
       <c r="L10" s="31"/>
       <c r="M10" s="31"/>
     </row>
-    <row r="11" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A11" s="65"/>
+    <row r="11" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A11" s="71"/>
       <c r="B11" s="34" t="s">
         <v>102</v>
       </c>
@@ -3897,7 +4092,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H11" s="72">
+      <c r="H11" s="38">
         <f t="shared" si="0"/>
         <v>0.97530864197530864</v>
       </c>
@@ -3919,8 +4114,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A12" s="65"/>
+    <row r="12" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A12" s="71"/>
       <c r="B12" s="34" t="s">
         <v>103</v>
       </c>
@@ -3956,8 +4151,8 @@
       <c r="L12" s="31"/>
       <c r="M12" s="31"/>
     </row>
-    <row r="13" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A13" s="68"/>
+    <row r="13" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A13" s="72"/>
       <c r="B13" s="34" t="s">
         <v>5</v>
       </c>
@@ -3993,8 +4188,8 @@
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
     </row>
-    <row r="14" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A14" s="64" t="s">
+    <row r="14" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A14" s="70" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="31" t="s">
@@ -4032,8 +4227,8 @@
       <c r="L14" s="31"/>
       <c r="M14" s="31"/>
     </row>
-    <row r="15" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A15" s="65"/>
+    <row r="15" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A15" s="71"/>
       <c r="B15" s="34" t="s">
         <v>113</v>
       </c>
@@ -4069,8 +4264,8 @@
       <c r="L15" s="31"/>
       <c r="M15" s="31"/>
     </row>
-    <row r="16" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A16" s="65"/>
+    <row r="16" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A16" s="71"/>
       <c r="B16" s="34" t="s">
         <v>97</v>
       </c>
@@ -4106,8 +4301,8 @@
       <c r="L16" s="31"/>
       <c r="M16" s="31"/>
     </row>
-    <row r="17" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A17" s="65"/>
+    <row r="17" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A17" s="71"/>
       <c r="B17" s="34" t="s">
         <v>98</v>
       </c>
@@ -4143,8 +4338,8 @@
       <c r="L17" s="31"/>
       <c r="M17" s="31"/>
     </row>
-    <row r="18" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A18" s="65"/>
+    <row r="18" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A18" s="71"/>
       <c r="B18" s="34" t="s">
         <v>99</v>
       </c>
@@ -4164,7 +4359,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H18" s="72">
+      <c r="H18" s="38">
         <f t="shared" si="0"/>
         <v>0.96666666666666667</v>
       </c>
@@ -4186,8 +4381,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A19" s="65"/>
+    <row r="19" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A19" s="71"/>
       <c r="B19" s="34" t="s">
         <v>100</v>
       </c>
@@ -4223,8 +4418,8 @@
       <c r="L19" s="31"/>
       <c r="M19" s="31"/>
     </row>
-    <row r="20" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A20" s="65"/>
+    <row r="20" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A20" s="71"/>
       <c r="B20" s="34" t="s">
         <v>101</v>
       </c>
@@ -4260,8 +4455,8 @@
       <c r="L20" s="31"/>
       <c r="M20" s="31"/>
     </row>
-    <row r="21" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A21" s="65"/>
+    <row r="21" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A21" s="71"/>
       <c r="B21" s="34" t="s">
         <v>102</v>
       </c>
@@ -4281,7 +4476,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H21" s="72">
+      <c r="H21" s="38">
         <f t="shared" si="0"/>
         <v>0.96273291925465843</v>
       </c>
@@ -4303,8 +4498,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A22" s="65"/>
+    <row r="22" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A22" s="71"/>
       <c r="B22" s="34" t="s">
         <v>103</v>
       </c>
@@ -4340,8 +4535,8 @@
       <c r="L22" s="31"/>
       <c r="M22" s="31"/>
     </row>
-    <row r="23" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A23" s="68"/>
+    <row r="23" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A23" s="72"/>
       <c r="B23" s="34" t="s">
         <v>5</v>
       </c>
@@ -4377,11 +4572,11 @@
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
     </row>
-    <row r="24" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A24" s="64" t="s">
+    <row r="24" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A24" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="73" t="s">
+      <c r="B24" s="39" t="s">
         <v>94</v>
       </c>
       <c r="C24" s="32" t="s">
@@ -4416,9 +4611,9 @@
       <c r="L24" s="31"/>
       <c r="M24" s="31"/>
     </row>
-    <row r="25" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A25" s="65"/>
-      <c r="B25" s="73" t="s">
+    <row r="25" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A25" s="71"/>
+      <c r="B25" s="39" t="s">
         <v>113</v>
       </c>
       <c r="C25" s="32" t="s">
@@ -4453,9 +4648,9 @@
       <c r="L25" s="31"/>
       <c r="M25" s="31"/>
     </row>
-    <row r="26" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A26" s="65"/>
-      <c r="B26" s="74" t="s">
+    <row r="26" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A26" s="71"/>
+      <c r="B26" s="40" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="32" t="s">
@@ -4490,9 +4685,9 @@
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
     </row>
-    <row r="27" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A27" s="65"/>
-      <c r="B27" s="74" t="s">
+    <row r="27" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A27" s="71"/>
+      <c r="B27" s="40" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="32" t="s">
@@ -4527,9 +4722,9 @@
       <c r="L27" s="31"/>
       <c r="M27" s="31"/>
     </row>
-    <row r="28" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A28" s="65"/>
-      <c r="B28" s="74" t="s">
+    <row r="28" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A28" s="71"/>
+      <c r="B28" s="40" t="s">
         <v>99</v>
       </c>
       <c r="C28" s="32" t="s">
@@ -4564,9 +4759,9 @@
       <c r="L28" s="31"/>
       <c r="M28" s="31"/>
     </row>
-    <row r="29" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="74" t="s">
+    <row r="29" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A29" s="71"/>
+      <c r="B29" s="40" t="s">
         <v>100</v>
       </c>
       <c r="C29" s="32" t="s">
@@ -4601,9 +4796,9 @@
       <c r="L29" s="31"/>
       <c r="M29" s="31"/>
     </row>
-    <row r="30" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A30" s="65"/>
-      <c r="B30" s="74" t="s">
+    <row r="30" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A30" s="71"/>
+      <c r="B30" s="40" t="s">
         <v>101</v>
       </c>
       <c r="C30" s="32" t="s">
@@ -4638,9 +4833,9 @@
       <c r="L30" s="31"/>
       <c r="M30" s="31"/>
     </row>
-    <row r="31" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A31" s="65"/>
-      <c r="B31" s="74" t="s">
+    <row r="31" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A31" s="71"/>
+      <c r="B31" s="40" t="s">
         <v>102</v>
       </c>
       <c r="C31" s="32" t="s">
@@ -4659,7 +4854,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H31" s="72">
+      <c r="H31" s="38">
         <f t="shared" si="0"/>
         <v>0.95833333333333337</v>
       </c>
@@ -4681,9 +4876,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A32" s="65"/>
-      <c r="B32" s="74" t="s">
+    <row r="32" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A32" s="71"/>
+      <c r="B32" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C32" s="32" t="s">
@@ -4718,9 +4913,9 @@
       <c r="L32" s="31"/>
       <c r="M32" s="31"/>
     </row>
-    <row r="33" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A33" s="68"/>
-      <c r="B33" s="74" t="s">
+    <row r="33" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A33" s="72"/>
+      <c r="B33" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="32" t="s">
@@ -4755,8 +4950,8 @@
       <c r="L33" s="31"/>
       <c r="M33" s="31"/>
     </row>
-    <row r="34" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A34" s="64" t="s">
+    <row r="34" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A34" s="70" t="s">
         <v>107</v>
       </c>
       <c r="B34" s="31" t="s">
@@ -4794,8 +4989,8 @@
       <c r="L34" s="31"/>
       <c r="M34" s="31"/>
     </row>
-    <row r="35" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A35" s="65"/>
+    <row r="35" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A35" s="71"/>
       <c r="B35" s="34" t="s">
         <v>99</v>
       </c>
@@ -4831,8 +5026,8 @@
       <c r="L35" s="31"/>
       <c r="M35" s="31"/>
     </row>
-    <row r="36" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A36" s="65"/>
+    <row r="36" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A36" s="71"/>
       <c r="B36" s="34" t="s">
         <v>100</v>
       </c>
@@ -4868,8 +5063,8 @@
       <c r="L36" s="31"/>
       <c r="M36" s="31"/>
     </row>
-    <row r="37" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A37" s="65"/>
+    <row r="37" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A37" s="71"/>
       <c r="B37" s="34" t="s">
         <v>101</v>
       </c>
@@ -4905,8 +5100,8 @@
       <c r="L37" s="31"/>
       <c r="M37" s="31"/>
     </row>
-    <row r="38" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A38" s="65"/>
+    <row r="38" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A38" s="71"/>
       <c r="B38" s="34" t="s">
         <v>102</v>
       </c>
@@ -4926,7 +5121,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H38" s="72">
+      <c r="H38" s="38">
         <f t="shared" si="0"/>
         <v>0.97101449275362317</v>
       </c>
@@ -4942,8 +5137,8 @@
       <c r="L38" s="31"/>
       <c r="M38" s="31"/>
     </row>
-    <row r="39" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A39" s="65"/>
+    <row r="39" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A39" s="71"/>
       <c r="B39" s="34" t="s">
         <v>103</v>
       </c>
@@ -4979,8 +5174,8 @@
       <c r="L39" s="31"/>
       <c r="M39" s="31"/>
     </row>
-    <row r="40" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A40" s="68"/>
+    <row r="40" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A40" s="72"/>
       <c r="B40" s="34" t="s">
         <v>5</v>
       </c>
@@ -5016,8 +5211,8 @@
       <c r="L40" s="31"/>
       <c r="M40" s="31"/>
     </row>
-    <row r="41" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A41" s="64" t="s">
+    <row r="41" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A41" s="70" t="s">
         <v>108</v>
       </c>
       <c r="B41" s="31" t="s">
@@ -5057,8 +5252,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A42" s="65"/>
+    <row r="42" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A42" s="71"/>
       <c r="B42" s="34" t="s">
         <v>114</v>
       </c>
@@ -5094,8 +5289,8 @@
       <c r="L42" s="31"/>
       <c r="M42" s="31"/>
     </row>
-    <row r="43" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A43" s="65"/>
+    <row r="43" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A43" s="71"/>
       <c r="B43" s="34" t="s">
         <v>98</v>
       </c>
@@ -5131,8 +5326,8 @@
       <c r="L43" s="31"/>
       <c r="M43" s="31"/>
     </row>
-    <row r="44" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A44" s="65"/>
+    <row r="44" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A44" s="71"/>
       <c r="B44" s="34" t="s">
         <v>99</v>
       </c>
@@ -5168,8 +5363,8 @@
       <c r="L44" s="31"/>
       <c r="M44" s="31"/>
     </row>
-    <row r="45" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A45" s="65"/>
+    <row r="45" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A45" s="71"/>
       <c r="B45" s="34" t="s">
         <v>102</v>
       </c>
@@ -5205,8 +5400,8 @@
       <c r="L45" s="31"/>
       <c r="M45" s="31"/>
     </row>
-    <row r="46" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A46" s="65"/>
+    <row r="46" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A46" s="71"/>
       <c r="B46" s="34" t="s">
         <v>103</v>
       </c>
@@ -5242,8 +5437,8 @@
       <c r="L46" s="31"/>
       <c r="M46" s="31"/>
     </row>
-    <row r="47" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A47" s="68"/>
+    <row r="47" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A47" s="72"/>
       <c r="B47" s="34" t="s">
         <v>5</v>
       </c>
@@ -5281,6 +5476,10 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A14:A23"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="A41:A47"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="A3:A13"/>
@@ -5289,10 +5488,6 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A14:A23"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="A41:A47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74659D99-1B8D-49EA-8BDE-700D4EB0781C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59008B69-BE59-40FE-A4F4-6F6FE73800F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="128">
   <si>
     <t>TỔ CHỨC BIÊN CHẾ, TRANG BỊ HƯỚNG CHỦ YẾU</t>
   </si>
@@ -404,12 +404,51 @@
   <si>
     <t>Cối 100mm</t>
   </si>
+  <si>
+    <t>Phân đội HC-KT</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>TLHC/d</t>
+  </si>
+  <si>
+    <t>NVQK</t>
+  </si>
+  <si>
+    <t>NVQN</t>
+  </si>
+  <si>
+    <t>NVKT</t>
+  </si>
+  <si>
+    <t>QY/d</t>
+  </si>
+  <si>
+    <t>bVTB/d</t>
+  </si>
+  <si>
+    <t>bPV/d</t>
+  </si>
+  <si>
+    <t>LL tăng cường</t>
+  </si>
+  <si>
+    <t>QY/e</t>
+  </si>
+  <si>
+    <t>bVTB/e</t>
+  </si>
+  <si>
+    <t>Tổ SC/e</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,6 +586,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -598,7 +644,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -831,11 +877,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -948,6 +1005,15 @@
     <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1020,10 +1086,19 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1032,32 +1107,81 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1377,76 +1501,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="43"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="46"/>
     </row>
     <row r="3" spans="1:13" ht="14" customHeight="1">
-      <c r="A3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="44" t="s">
+      <c r="A3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44" t="s">
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44" t="s">
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1455,8 +1579,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="47"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1472,7 +1596,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="47"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1493,31 +1617,52 @@
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="B6" s="2">
+        <f t="shared" ref="B6:H6" si="0">B7</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="I6" s="2">
         <f>I7</f>
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <f t="shared" ref="J6:M6" si="0">J7</f>
+        <f t="shared" ref="J6:M6" si="1">J7</f>
         <v>0</v>
       </c>
       <c r="K6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1549,51 +1694,51 @@
         <v>17</v>
       </c>
       <c r="B8" s="2">
-        <f t="shared" ref="B8:M8" si="1">SUM(B9:B16)</f>
+        <f t="shared" ref="B8:M8" si="2">SUM(B9:B16)</f>
         <v>0</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1738,51 +1883,51 @@
         <v>26</v>
       </c>
       <c r="B17" s="9">
-        <f t="shared" ref="B17:M17" si="2">B7+B8</f>
+        <f t="shared" ref="B17:M17" si="3">B7+B8</f>
         <v>1</v>
       </c>
       <c r="C17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1806,76 +1951,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="43"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="46"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="44" t="s">
+      <c r="A3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44" t="s">
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44" t="s">
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1884,8 +2029,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="47"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1901,7 +2046,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="47"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2382,32 +2527,32 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="45" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="I1" s="48" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
       <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
@@ -2420,8 +2565,8 @@
       <c r="G2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
@@ -2685,30 +2830,30 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="59" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="64"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="53"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="26" t="s">
         <v>65</v>
       </c>
@@ -2811,76 +2956,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="43"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="46"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="44" t="s">
+      <c r="A3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44" t="s">
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44" t="s">
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2889,8 +3034,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="47"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2906,7 +3051,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="44"/>
+      <c r="H5" s="47"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -3383,92 +3528,95 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18CCF06B-A044-4E5A-A947-A016657D51E8}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="17" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62" t="s">
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62" t="s">
+      <c r="H1" s="88"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="62"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62" t="s">
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="89"/>
+    </row>
+    <row r="2" spans="1:13" ht="14.5" customHeight="1">
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="62" t="s">
+      <c r="F2" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="62" t="s">
+      <c r="I2" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="62"/>
-      <c r="L2" s="63" t="s">
+      <c r="K2" s="95"/>
+      <c r="L2" s="90" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="63"/>
+      <c r="M2" s="91"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="93"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="62"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
+      <c r="A4" s="86"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
       <c r="J4" s="29" t="s">
         <v>79</v>
       </c>
@@ -3481,6 +3629,318 @@
       <c r="M4" s="29" t="s">
         <v>80</v>
       </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="29">
+        <v>1</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="29">
+        <f>SUM(C6:C12)</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="29">
+        <f>SUM(D6:D12)</f>
+        <v>5</v>
+      </c>
+      <c r="E5" s="29">
+        <f>SUM(E6:E12)</f>
+        <v>54</v>
+      </c>
+      <c r="F5" s="29">
+        <f>SUM(F6:F12)</f>
+        <v>61</v>
+      </c>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="75" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="29">
+        <v>1</v>
+      </c>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29">
+        <f t="shared" ref="F6:F11" si="0">SUM(C6:E6)</f>
+        <v>1</v>
+      </c>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="75" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29">
+        <v>1</v>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="76" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29">
+        <v>1</v>
+      </c>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="75" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29">
+        <v>1</v>
+      </c>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="75" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29">
+        <v>1</v>
+      </c>
+      <c r="E10" s="29">
+        <v>2</v>
+      </c>
+      <c r="F10" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="75" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="29">
+        <v>1</v>
+      </c>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29">
+        <v>27</v>
+      </c>
+      <c r="F11" s="29">
+        <f>SUM(C11:E11)</f>
+        <v>28</v>
+      </c>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79">
+        <v>1</v>
+      </c>
+      <c r="E12" s="79">
+        <v>25</v>
+      </c>
+      <c r="F12" s="29">
+        <f>SUM(C12:E12)</f>
+        <v>26</v>
+      </c>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="29">
+        <v>2</v>
+      </c>
+      <c r="B13" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="29">
+        <f>C14+C15+C16</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="29">
+        <f>D14+D15+D16</f>
+        <v>4</v>
+      </c>
+      <c r="E13" s="29">
+        <f>E14+E15+E16</f>
+        <v>29</v>
+      </c>
+      <c r="F13" s="29">
+        <f>F14+F15+F16</f>
+        <v>34</v>
+      </c>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="80"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="75" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29">
+        <v>1</v>
+      </c>
+      <c r="E14" s="29">
+        <v>2</v>
+      </c>
+      <c r="F14" s="29">
+        <f>SUM(C14:E14)</f>
+        <v>3</v>
+      </c>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="80"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="82">
+        <v>1</v>
+      </c>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82">
+        <v>27</v>
+      </c>
+      <c r="F15" s="29">
+        <f>SUM(C15:E15)</f>
+        <v>28</v>
+      </c>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="82" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="83" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82">
+        <v>3</v>
+      </c>
+      <c r="E16" s="82"/>
+      <c r="F16" s="29">
+        <f>SUM(C16:E16)</f>
+        <v>3</v>
+      </c>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3513,39 +3973,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.5" thickBot="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="66" t="s">
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="J1" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="71"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="69"/>
     </row>
     <row r="2" spans="1:13" ht="30.5" thickBot="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
       <c r="E2" s="30" t="s">
         <v>86</v>
       </c>
@@ -3558,7 +4018,7 @@
       <c r="H2" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="67"/>
+      <c r="I2" s="66"/>
       <c r="J2" s="30" t="s">
         <v>89</v>
       </c>
@@ -3572,8 +4032,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A3" s="70" t="s">
         <v>93</v>
       </c>
       <c r="B3" s="31" t="s">
@@ -3612,7 +4072,7 @@
       <c r="M3" s="31"/>
     </row>
     <row r="4" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A4" s="65"/>
+      <c r="A4" s="71"/>
       <c r="B4" s="34" t="s">
         <v>95</v>
       </c>
@@ -3649,7 +4109,7 @@
       <c r="M4" s="31"/>
     </row>
     <row r="5" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A5" s="65"/>
+      <c r="A5" s="71"/>
       <c r="B5" s="34" t="s">
         <v>96</v>
       </c>
@@ -3686,7 +4146,7 @@
       <c r="M5" s="31"/>
     </row>
     <row r="6" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A6" s="65"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="34" t="s">
         <v>97</v>
       </c>
@@ -3723,7 +4183,7 @@
       <c r="M6" s="31"/>
     </row>
     <row r="7" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A7" s="65"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="34" t="s">
         <v>98</v>
       </c>
@@ -3760,7 +4220,7 @@
       <c r="M7" s="31"/>
     </row>
     <row r="8" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A8" s="65"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="34" t="s">
         <v>99</v>
       </c>
@@ -3780,7 +4240,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H8" s="72">
+      <c r="H8" s="38">
         <f t="shared" si="0"/>
         <v>0.98611111111111116</v>
       </c>
@@ -3803,7 +4263,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A9" s="65"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="34" t="s">
         <v>100</v>
       </c>
@@ -3840,7 +4300,7 @@
       <c r="M9" s="31"/>
     </row>
     <row r="10" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A10" s="65"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="34" t="s">
         <v>101</v>
       </c>
@@ -3877,7 +4337,7 @@
       <c r="M10" s="31"/>
     </row>
     <row r="11" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A11" s="65"/>
+      <c r="A11" s="71"/>
       <c r="B11" s="34" t="s">
         <v>102</v>
       </c>
@@ -3897,7 +4357,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H11" s="72">
+      <c r="H11" s="38">
         <f t="shared" si="0"/>
         <v>0.97530864197530864</v>
       </c>
@@ -3920,7 +4380,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A12" s="65"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="34" t="s">
         <v>103</v>
       </c>
@@ -3957,7 +4417,7 @@
       <c r="M12" s="31"/>
     </row>
     <row r="13" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A13" s="68"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="34" t="s">
         <v>5</v>
       </c>
@@ -3993,8 +4453,8 @@
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
     </row>
-    <row r="14" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A14" s="64" t="s">
+    <row r="14" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A14" s="70" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="31" t="s">
@@ -4033,7 +4493,7 @@
       <c r="M14" s="31"/>
     </row>
     <row r="15" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A15" s="65"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="34" t="s">
         <v>113</v>
       </c>
@@ -4070,7 +4530,7 @@
       <c r="M15" s="31"/>
     </row>
     <row r="16" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A16" s="65"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="34" t="s">
         <v>97</v>
       </c>
@@ -4107,7 +4567,7 @@
       <c r="M16" s="31"/>
     </row>
     <row r="17" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A17" s="65"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="34" t="s">
         <v>98</v>
       </c>
@@ -4144,7 +4604,7 @@
       <c r="M17" s="31"/>
     </row>
     <row r="18" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A18" s="65"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="34" t="s">
         <v>99</v>
       </c>
@@ -4164,7 +4624,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H18" s="72">
+      <c r="H18" s="38">
         <f t="shared" si="0"/>
         <v>0.96666666666666667</v>
       </c>
@@ -4187,7 +4647,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A19" s="65"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="34" t="s">
         <v>100</v>
       </c>
@@ -4224,7 +4684,7 @@
       <c r="M19" s="31"/>
     </row>
     <row r="20" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A20" s="65"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="34" t="s">
         <v>101</v>
       </c>
@@ -4261,7 +4721,7 @@
       <c r="M20" s="31"/>
     </row>
     <row r="21" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A21" s="65"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="34" t="s">
         <v>102</v>
       </c>
@@ -4281,7 +4741,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H21" s="72">
+      <c r="H21" s="38">
         <f t="shared" si="0"/>
         <v>0.96273291925465843</v>
       </c>
@@ -4304,7 +4764,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A22" s="65"/>
+      <c r="A22" s="71"/>
       <c r="B22" s="34" t="s">
         <v>103</v>
       </c>
@@ -4341,7 +4801,7 @@
       <c r="M22" s="31"/>
     </row>
     <row r="23" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A23" s="68"/>
+      <c r="A23" s="72"/>
       <c r="B23" s="34" t="s">
         <v>5</v>
       </c>
@@ -4377,11 +4837,11 @@
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
     </row>
-    <row r="24" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A24" s="64" t="s">
+    <row r="24" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A24" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="73" t="s">
+      <c r="B24" s="39" t="s">
         <v>94</v>
       </c>
       <c r="C24" s="32" t="s">
@@ -4416,9 +4876,9 @@
       <c r="L24" s="31"/>
       <c r="M24" s="31"/>
     </row>
-    <row r="25" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A25" s="65"/>
-      <c r="B25" s="73" t="s">
+    <row r="25" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A25" s="71"/>
+      <c r="B25" s="39" t="s">
         <v>113</v>
       </c>
       <c r="C25" s="32" t="s">
@@ -4453,9 +4913,9 @@
       <c r="L25" s="31"/>
       <c r="M25" s="31"/>
     </row>
-    <row r="26" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A26" s="65"/>
-      <c r="B26" s="74" t="s">
+    <row r="26" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A26" s="71"/>
+      <c r="B26" s="40" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="32" t="s">
@@ -4490,9 +4950,9 @@
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
     </row>
-    <row r="27" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A27" s="65"/>
-      <c r="B27" s="74" t="s">
+    <row r="27" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A27" s="71"/>
+      <c r="B27" s="40" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="32" t="s">
@@ -4527,9 +4987,9 @@
       <c r="L27" s="31"/>
       <c r="M27" s="31"/>
     </row>
-    <row r="28" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A28" s="65"/>
-      <c r="B28" s="74" t="s">
+    <row r="28" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A28" s="71"/>
+      <c r="B28" s="40" t="s">
         <v>99</v>
       </c>
       <c r="C28" s="32" t="s">
@@ -4564,9 +5024,9 @@
       <c r="L28" s="31"/>
       <c r="M28" s="31"/>
     </row>
-    <row r="29" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="74" t="s">
+    <row r="29" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A29" s="71"/>
+      <c r="B29" s="40" t="s">
         <v>100</v>
       </c>
       <c r="C29" s="32" t="s">
@@ -4601,9 +5061,9 @@
       <c r="L29" s="31"/>
       <c r="M29" s="31"/>
     </row>
-    <row r="30" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A30" s="65"/>
-      <c r="B30" s="74" t="s">
+    <row r="30" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A30" s="71"/>
+      <c r="B30" s="40" t="s">
         <v>101</v>
       </c>
       <c r="C30" s="32" t="s">
@@ -4638,9 +5098,9 @@
       <c r="L30" s="31"/>
       <c r="M30" s="31"/>
     </row>
-    <row r="31" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A31" s="65"/>
-      <c r="B31" s="74" t="s">
+    <row r="31" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A31" s="71"/>
+      <c r="B31" s="40" t="s">
         <v>102</v>
       </c>
       <c r="C31" s="32" t="s">
@@ -4659,7 +5119,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H31" s="72">
+      <c r="H31" s="38">
         <f t="shared" si="0"/>
         <v>0.95833333333333337</v>
       </c>
@@ -4681,9 +5141,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A32" s="65"/>
-      <c r="B32" s="74" t="s">
+    <row r="32" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A32" s="71"/>
+      <c r="B32" s="40" t="s">
         <v>103</v>
       </c>
       <c r="C32" s="32" t="s">
@@ -4718,9 +5178,9 @@
       <c r="L32" s="31"/>
       <c r="M32" s="31"/>
     </row>
-    <row r="33" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A33" s="68"/>
-      <c r="B33" s="74" t="s">
+    <row r="33" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A33" s="72"/>
+      <c r="B33" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="32" t="s">
@@ -4755,8 +5215,8 @@
       <c r="L33" s="31"/>
       <c r="M33" s="31"/>
     </row>
-    <row r="34" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A34" s="64" t="s">
+    <row r="34" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A34" s="70" t="s">
         <v>107</v>
       </c>
       <c r="B34" s="31" t="s">
@@ -4795,7 +5255,7 @@
       <c r="M34" s="31"/>
     </row>
     <row r="35" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A35" s="65"/>
+      <c r="A35" s="71"/>
       <c r="B35" s="34" t="s">
         <v>99</v>
       </c>
@@ -4832,7 +5292,7 @@
       <c r="M35" s="31"/>
     </row>
     <row r="36" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A36" s="65"/>
+      <c r="A36" s="71"/>
       <c r="B36" s="34" t="s">
         <v>100</v>
       </c>
@@ -4869,7 +5329,7 @@
       <c r="M36" s="31"/>
     </row>
     <row r="37" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A37" s="65"/>
+      <c r="A37" s="71"/>
       <c r="B37" s="34" t="s">
         <v>101</v>
       </c>
@@ -4906,7 +5366,7 @@
       <c r="M37" s="31"/>
     </row>
     <row r="38" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A38" s="65"/>
+      <c r="A38" s="71"/>
       <c r="B38" s="34" t="s">
         <v>102</v>
       </c>
@@ -4926,7 +5386,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H38" s="72">
+      <c r="H38" s="38">
         <f t="shared" si="0"/>
         <v>0.97101449275362317</v>
       </c>
@@ -4943,7 +5403,7 @@
       <c r="M38" s="31"/>
     </row>
     <row r="39" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A39" s="65"/>
+      <c r="A39" s="71"/>
       <c r="B39" s="34" t="s">
         <v>103</v>
       </c>
@@ -4980,7 +5440,7 @@
       <c r="M39" s="31"/>
     </row>
     <row r="40" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A40" s="68"/>
+      <c r="A40" s="72"/>
       <c r="B40" s="34" t="s">
         <v>5</v>
       </c>
@@ -5016,8 +5476,8 @@
       <c r="L40" s="31"/>
       <c r="M40" s="31"/>
     </row>
-    <row r="41" spans="1:13" ht="54.5" thickBot="1">
-      <c r="A41" s="64" t="s">
+    <row r="41" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A41" s="70" t="s">
         <v>108</v>
       </c>
       <c r="B41" s="31" t="s">
@@ -5058,7 +5518,7 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A42" s="65"/>
+      <c r="A42" s="71"/>
       <c r="B42" s="34" t="s">
         <v>114</v>
       </c>
@@ -5095,7 +5555,7 @@
       <c r="M42" s="31"/>
     </row>
     <row r="43" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A43" s="65"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="34" t="s">
         <v>98</v>
       </c>
@@ -5132,7 +5592,7 @@
       <c r="M43" s="31"/>
     </row>
     <row r="44" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A44" s="65"/>
+      <c r="A44" s="71"/>
       <c r="B44" s="34" t="s">
         <v>99</v>
       </c>
@@ -5169,7 +5629,7 @@
       <c r="M44" s="31"/>
     </row>
     <row r="45" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A45" s="65"/>
+      <c r="A45" s="71"/>
       <c r="B45" s="34" t="s">
         <v>102</v>
       </c>
@@ -5206,7 +5666,7 @@
       <c r="M45" s="31"/>
     </row>
     <row r="46" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A46" s="65"/>
+      <c r="A46" s="71"/>
       <c r="B46" s="34" t="s">
         <v>103</v>
       </c>
@@ -5243,7 +5703,7 @@
       <c r="M46" s="31"/>
     </row>
     <row r="47" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A47" s="68"/>
+      <c r="A47" s="72"/>
       <c r="B47" s="34" t="s">
         <v>5</v>
       </c>
@@ -5281,6 +5741,10 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A14:A23"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="A41:A47"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="A3:A13"/>
@@ -5289,10 +5753,6 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A14:A23"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="A41:A47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59008B69-BE59-40FE-A4F4-6F6FE73800F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D003EAF7-35B2-4A1D-849B-3DF2EF9888E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="133">
   <si>
     <t>TỔ CHỨC BIÊN CHẾ, TRANG BỊ HƯỚNG CHỦ YẾU</t>
   </si>
@@ -442,6 +453,21 @@
   </si>
   <si>
     <t>Tổ SC/e</t>
+  </si>
+  <si>
+    <t>Cối 60</t>
+  </si>
+  <si>
+    <t>Cối 82</t>
+  </si>
+  <si>
+    <t>Cối 100</t>
+  </si>
+  <si>
+    <t>Pháo PK</t>
+  </si>
+  <si>
+    <t>B41,M79</t>
   </si>
 </sst>
 </file>
@@ -1014,102 +1040,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1141,6 +1071,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1150,6 +1152,30 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1159,33 +1185,33 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1201,9 +1227,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1241,7 +1267,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1347,7 +1373,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1489,7 +1515,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1498,79 +1524,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D56173A-C175-4526-B966-989AD58BFBEE}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="54"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
-    </row>
-    <row r="3" spans="1:13" ht="14" customHeight="1">
-      <c r="A3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="47" t="s">
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="57"/>
+    </row>
+    <row r="3" spans="1:13" ht="14.1" customHeight="1">
+      <c r="A3" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47" t="s">
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47" t="s">
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1579,8 +1605,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="58"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1596,7 +1622,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="47"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1776,7 +1802,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="21">
+    <row r="11" spans="1:13" ht="22.5">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -1827,7 +1853,7 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" ht="21">
+    <row r="14" spans="1:13" ht="22.5">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -1844,7 +1870,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" ht="21">
+    <row r="15" spans="1:13" ht="33.75">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -1948,79 +1974,79 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F16AEE-EEF3-41FC-9011-B3FA05A2337A}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="54"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="57"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="47" t="s">
+      <c r="A3" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47" t="s">
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47" t="s">
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2029,8 +2055,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="58"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2046,7 +2072,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="47"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2063,7 +2089,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18">
+    <row r="6" spans="1:13" ht="21">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -2157,7 +2183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18">
+    <row r="8" spans="1:13" ht="21">
       <c r="A8" s="10" t="s">
         <v>29</v>
       </c>
@@ -2264,7 +2290,7 @@
       </c>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="18">
+    <row r="11" spans="1:13" ht="21">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -2523,36 +2549,36 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB776F58-BBC1-4BAD-8576-583DC692D30D}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="48" t="s">
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="59" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
       <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
@@ -2565,8 +2591,8 @@
       <c r="G2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
@@ -2576,14 +2602,14 @@
         <v>50</v>
       </c>
       <c r="C3" s="23">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D3" s="24">
         <v>35</v>
       </c>
       <c r="E3" s="23">
         <f>D3/C3</f>
-        <v>0.97222222222222221</v>
+        <v>35</v>
       </c>
       <c r="F3" s="23">
         <f>G3/D3</f>
@@ -2595,7 +2621,7 @@
       <c r="H3" s="24"/>
       <c r="I3" s="23">
         <f>C3-D3</f>
-        <v>1</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2606,17 +2632,17 @@
         <v>50</v>
       </c>
       <c r="C4" s="23">
-        <v>439</v>
+        <v>2</v>
       </c>
       <c r="D4" s="24">
         <v>439</v>
       </c>
       <c r="E4" s="23">
         <f>D4/C4</f>
-        <v>1</v>
+        <v>219.5</v>
       </c>
       <c r="F4" s="23">
-        <f t="shared" ref="F4:F7" si="0">G4/D4</f>
+        <f t="shared" ref="F4:F8" si="0">G4/D4</f>
         <v>0.99772209567198178</v>
       </c>
       <c r="G4" s="24">
@@ -2625,7 +2651,7 @@
       <c r="H4" s="24"/>
       <c r="I4" s="23">
         <f>C4-D4</f>
-        <v>0</v>
+        <v>-437</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2636,14 +2662,14 @@
         <v>50</v>
       </c>
       <c r="C5" s="23">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D5" s="24">
         <v>27</v>
       </c>
       <c r="E5" s="23">
         <f>D5/C5</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F5" s="23">
         <f t="shared" si="0"/>
@@ -2654,8 +2680,8 @@
       </c>
       <c r="H5" s="24"/>
       <c r="I5" s="23">
-        <f t="shared" ref="I5:I7" si="1">C5-D5</f>
-        <v>0</v>
+        <f t="shared" ref="I5:I8" si="1">C5-D5</f>
+        <v>-24</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2666,14 +2692,14 @@
         <v>50</v>
       </c>
       <c r="C6" s="23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="24">
         <v>6</v>
       </c>
       <c r="E6" s="23">
         <f>D6/C6</f>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F6" s="23">
         <f t="shared" si="0"/>
@@ -2685,37 +2711,217 @@
       <c r="H6" s="24"/>
       <c r="I6" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="23">
         <v>5</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="23">
-        <v>2073</v>
-      </c>
       <c r="D7" s="24">
-        <v>2073</v>
+        <v>6</v>
       </c>
       <c r="E7" s="23">
         <f>D7/C7</f>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F7" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F7" si="2">G7/D7</f>
         <v>1</v>
       </c>
       <c r="G7" s="24">
-        <v>2073</v>
+        <v>6</v>
       </c>
       <c r="H7" s="24"/>
       <c r="I7" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="I7" si="3">C7-D7</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="23">
+        <v>6</v>
+      </c>
+      <c r="D8" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E8" s="23">
+        <f>D8/C8</f>
+        <v>345.5</v>
+      </c>
+      <c r="F8" s="23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="24">
+        <v>2073</v>
+      </c>
+      <c r="H8" s="24"/>
+      <c r="I8" s="23">
+        <f t="shared" si="1"/>
+        <v>-2067</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="23">
+        <v>7</v>
+      </c>
+      <c r="D9" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E9" s="23">
+        <f t="shared" ref="E9:E13" si="4">D9/C9</f>
+        <v>296.14285714285717</v>
+      </c>
+      <c r="F9" s="23">
+        <f t="shared" ref="F9:F13" si="5">G9/D9</f>
+        <v>1.0004823926676314</v>
+      </c>
+      <c r="G9" s="24">
+        <v>2074</v>
+      </c>
+      <c r="H9" s="24"/>
+      <c r="I9" s="23">
+        <f t="shared" ref="I9:I13" si="6">C9-D9</f>
+        <v>-2066</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="23">
+        <v>8</v>
+      </c>
+      <c r="D10" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E10" s="23">
+        <f t="shared" si="4"/>
+        <v>259.125</v>
+      </c>
+      <c r="F10" s="23">
+        <f t="shared" si="5"/>
+        <v>1.000964785335263</v>
+      </c>
+      <c r="G10" s="24">
+        <v>2075</v>
+      </c>
+      <c r="H10" s="24"/>
+      <c r="I10" s="23">
+        <f t="shared" si="6"/>
+        <v>-2065</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="23">
+        <v>9</v>
+      </c>
+      <c r="D11" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E11" s="23">
+        <f t="shared" si="4"/>
+        <v>230.33333333333334</v>
+      </c>
+      <c r="F11" s="23">
+        <f t="shared" si="5"/>
+        <v>1.0014471780028944</v>
+      </c>
+      <c r="G11" s="24">
+        <v>2076</v>
+      </c>
+      <c r="H11" s="24"/>
+      <c r="I11" s="23">
+        <f t="shared" si="6"/>
+        <v>-2064</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="23">
+        <v>10</v>
+      </c>
+      <c r="D12" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E12" s="23">
+        <f t="shared" si="4"/>
+        <v>207.3</v>
+      </c>
+      <c r="F12" s="23">
+        <f t="shared" si="5"/>
+        <v>1.0019295706705258</v>
+      </c>
+      <c r="G12" s="24">
+        <v>2077</v>
+      </c>
+      <c r="H12" s="24"/>
+      <c r="I12" s="23">
+        <f t="shared" si="6"/>
+        <v>-2063</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="23">
+        <v>11</v>
+      </c>
+      <c r="D13" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E13" s="23">
+        <f t="shared" si="4"/>
+        <v>188.45454545454547</v>
+      </c>
+      <c r="F13" s="23">
+        <f t="shared" si="5"/>
+        <v>1.0024119633381572</v>
+      </c>
+      <c r="G13" s="24">
+        <v>2078</v>
+      </c>
+      <c r="H13" s="24"/>
+      <c r="I13" s="23">
+        <f t="shared" si="6"/>
+        <v>-2062</v>
       </c>
     </row>
   </sheetData>
@@ -2734,7 +2940,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D657F165-9D3D-496E-8012-68B69501198F}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" ht="24">
       <c r="A1" s="25" t="s">
@@ -2827,33 +3033,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6AD6F2A-F3DA-482E-A27C-72512E35A6E7}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="62" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="63"/>
-      <c r="I1" s="64"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="56"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
       <c r="D2" s="26" t="s">
         <v>65</v>
       </c>
@@ -2953,79 +3159,79 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90BB609-02C3-4480-ABA1-81B8EB7FC6E5}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="54"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="57"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="47" t="s">
+      <c r="A3" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47" t="s">
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47" t="s">
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -3034,8 +3240,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="58"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3051,7 +3257,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="47"/>
+      <c r="H5" s="58"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -3068,7 +3274,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18">
+    <row r="6" spans="1:13" ht="21">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -3162,7 +3368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18">
+    <row r="8" spans="1:13" ht="21">
       <c r="A8" s="10" t="s">
         <v>29</v>
       </c>
@@ -3269,7 +3475,7 @@
       </c>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="18">
+    <row r="11" spans="1:13" ht="21">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -3529,16 +3735,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18CCF06B-A044-4E5A-A947-A016657D51E8}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="76" t="s">
         <v>67</v>
       </c>
       <c r="C1" s="87" t="s">
@@ -3559,64 +3765,64 @@
       <c r="L1" s="88"/>
       <c r="M1" s="89"/>
     </row>
-    <row r="2" spans="1:13" ht="14.5" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="84" t="s">
+    <row r="2" spans="1:13" ht="14.45" customHeight="1">
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="84" t="s">
+      <c r="D2" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="84" t="s">
+      <c r="E2" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="76" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="I2" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="94" t="s">
+      <c r="J2" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="95"/>
-      <c r="L2" s="90" t="s">
+      <c r="K2" s="80"/>
+      <c r="L2" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="91"/>
+      <c r="M2" s="84"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="93"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="86"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="86"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
       <c r="J4" s="29" t="s">
         <v>79</v>
       </c>
@@ -3634,7 +3840,7 @@
       <c r="A5" s="29">
         <v>1</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="42" t="s">
         <v>115</v>
       </c>
       <c r="C5" s="29">
@@ -3665,7 +3871,7 @@
       <c r="A6" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="43" t="s">
         <v>117</v>
       </c>
       <c r="C6" s="29">
@@ -3674,7 +3880,7 @@
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29">
-        <f t="shared" ref="F6:F11" si="0">SUM(C6:E6)</f>
+        <f t="shared" ref="F6:F10" si="0">SUM(C6:E6)</f>
         <v>1</v>
       </c>
       <c r="G6" s="29"/>
@@ -3689,7 +3895,7 @@
       <c r="A7" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="43" t="s">
         <v>118</v>
       </c>
       <c r="C7" s="29"/>
@@ -3713,7 +3919,7 @@
       <c r="A8" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="76" t="s">
+      <c r="B8" s="44" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="29"/>
@@ -3737,7 +3943,7 @@
       <c r="A9" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="43" t="s">
         <v>120</v>
       </c>
       <c r="C9" s="29"/>
@@ -3761,7 +3967,7 @@
       <c r="A10" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="43" t="s">
         <v>121</v>
       </c>
       <c r="C10" s="29"/>
@@ -3787,7 +3993,7 @@
       <c r="A11" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="43" t="s">
         <v>122</v>
       </c>
       <c r="C11" s="29">
@@ -3810,36 +4016,36 @@
       <c r="M11" s="29"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79">
-        <v>1</v>
-      </c>
-      <c r="E12" s="79">
+      <c r="C12" s="47"/>
+      <c r="D12" s="47">
+        <v>1</v>
+      </c>
+      <c r="E12" s="47">
         <v>25</v>
       </c>
       <c r="F12" s="29">
         <f>SUM(C12:E12)</f>
         <v>26</v>
       </c>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="29">
         <v>2</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="48" t="s">
         <v>124</v>
       </c>
       <c r="C13" s="29">
@@ -3858,19 +4064,19 @@
         <f>F14+F15+F16</f>
         <v>34</v>
       </c>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="80"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="43" t="s">
         <v>125</v>
       </c>
       <c r="C14" s="29"/>
@@ -3884,63 +4090,63 @@
         <f>SUM(C14:E14)</f>
         <v>3</v>
       </c>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="82">
-        <v>1</v>
-      </c>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82">
+      <c r="C15" s="50">
+        <v>1</v>
+      </c>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50">
         <v>27</v>
       </c>
       <c r="F15" s="29">
         <f>SUM(C15:E15)</f>
         <v>28</v>
       </c>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="73"/>
-      <c r="M15" s="73"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="82" t="s">
+      <c r="A16" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82">
+      <c r="C16" s="50"/>
+      <c r="D16" s="50">
         <v>3</v>
       </c>
-      <c r="E16" s="82"/>
+      <c r="E16" s="50"/>
       <c r="F16" s="29">
         <f>SUM(C16:E16)</f>
         <v>3</v>
       </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73"/>
-      <c r="K16" s="73"/>
-      <c r="L16" s="73"/>
-      <c r="M16" s="73"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3966,46 +4172,46 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9BFD24-F416-4E13-BF3D-CA2831AC61D2}">
   <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.6328125" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.5" thickBot="1">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:13" ht="16.5" thickBot="1">
+      <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="65" t="s">
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="69"/>
-    </row>
-    <row r="2" spans="1:13" ht="30.5" thickBot="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="97"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" thickBot="1">
+      <c r="A2" s="94"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
       <c r="E2" s="30" t="s">
         <v>86</v>
       </c>
@@ -4018,7 +4224,7 @@
       <c r="H2" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="66"/>
+      <c r="I2" s="94"/>
       <c r="J2" s="30" t="s">
         <v>89</v>
       </c>
@@ -4032,8 +4238,8 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A3" s="70" t="s">
+    <row r="3" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A3" s="90" t="s">
         <v>93</v>
       </c>
       <c r="B3" s="31" t="s">
@@ -4071,8 +4277,8 @@
       <c r="L3" s="31"/>
       <c r="M3" s="31"/>
     </row>
-    <row r="4" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A4" s="71"/>
+    <row r="4" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A4" s="91"/>
       <c r="B4" s="34" t="s">
         <v>95</v>
       </c>
@@ -4108,8 +4314,8 @@
       <c r="L4" s="31"/>
       <c r="M4" s="31"/>
     </row>
-    <row r="5" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A5" s="71"/>
+    <row r="5" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A5" s="91"/>
       <c r="B5" s="34" t="s">
         <v>96</v>
       </c>
@@ -4145,8 +4351,8 @@
       <c r="L5" s="31"/>
       <c r="M5" s="31"/>
     </row>
-    <row r="6" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A6" s="71"/>
+    <row r="6" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A6" s="91"/>
       <c r="B6" s="34" t="s">
         <v>97</v>
       </c>
@@ -4182,8 +4388,8 @@
       <c r="L6" s="31"/>
       <c r="M6" s="31"/>
     </row>
-    <row r="7" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A7" s="71"/>
+    <row r="7" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A7" s="91"/>
       <c r="B7" s="34" t="s">
         <v>98</v>
       </c>
@@ -4219,8 +4425,8 @@
       <c r="L7" s="31"/>
       <c r="M7" s="31"/>
     </row>
-    <row r="8" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A8" s="71"/>
+    <row r="8" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A8" s="91"/>
       <c r="B8" s="34" t="s">
         <v>99</v>
       </c>
@@ -4262,8 +4468,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A9" s="71"/>
+    <row r="9" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A9" s="91"/>
       <c r="B9" s="34" t="s">
         <v>100</v>
       </c>
@@ -4299,8 +4505,8 @@
       <c r="L9" s="31"/>
       <c r="M9" s="31"/>
     </row>
-    <row r="10" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A10" s="71"/>
+    <row r="10" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A10" s="91"/>
       <c r="B10" s="34" t="s">
         <v>101</v>
       </c>
@@ -4336,8 +4542,8 @@
       <c r="L10" s="31"/>
       <c r="M10" s="31"/>
     </row>
-    <row r="11" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A11" s="71"/>
+    <row r="11" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A11" s="91"/>
       <c r="B11" s="34" t="s">
         <v>102</v>
       </c>
@@ -4379,8 +4585,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A12" s="71"/>
+    <row r="12" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A12" s="91"/>
       <c r="B12" s="34" t="s">
         <v>103</v>
       </c>
@@ -4416,8 +4622,8 @@
       <c r="L12" s="31"/>
       <c r="M12" s="31"/>
     </row>
-    <row r="13" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A13" s="72"/>
+    <row r="13" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A13" s="92"/>
       <c r="B13" s="34" t="s">
         <v>5</v>
       </c>
@@ -4453,8 +4659,8 @@
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
     </row>
-    <row r="14" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A14" s="70" t="s">
+    <row r="14" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A14" s="90" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="31" t="s">
@@ -4492,8 +4698,8 @@
       <c r="L14" s="31"/>
       <c r="M14" s="31"/>
     </row>
-    <row r="15" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A15" s="71"/>
+    <row r="15" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A15" s="91"/>
       <c r="B15" s="34" t="s">
         <v>113</v>
       </c>
@@ -4529,8 +4735,8 @@
       <c r="L15" s="31"/>
       <c r="M15" s="31"/>
     </row>
-    <row r="16" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A16" s="71"/>
+    <row r="16" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A16" s="91"/>
       <c r="B16" s="34" t="s">
         <v>97</v>
       </c>
@@ -4566,8 +4772,8 @@
       <c r="L16" s="31"/>
       <c r="M16" s="31"/>
     </row>
-    <row r="17" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A17" s="71"/>
+    <row r="17" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A17" s="91"/>
       <c r="B17" s="34" t="s">
         <v>98</v>
       </c>
@@ -4603,8 +4809,8 @@
       <c r="L17" s="31"/>
       <c r="M17" s="31"/>
     </row>
-    <row r="18" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A18" s="71"/>
+    <row r="18" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A18" s="91"/>
       <c r="B18" s="34" t="s">
         <v>99</v>
       </c>
@@ -4646,8 +4852,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A19" s="71"/>
+    <row r="19" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A19" s="91"/>
       <c r="B19" s="34" t="s">
         <v>100</v>
       </c>
@@ -4683,8 +4889,8 @@
       <c r="L19" s="31"/>
       <c r="M19" s="31"/>
     </row>
-    <row r="20" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A20" s="71"/>
+    <row r="20" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A20" s="91"/>
       <c r="B20" s="34" t="s">
         <v>101</v>
       </c>
@@ -4720,8 +4926,8 @@
       <c r="L20" s="31"/>
       <c r="M20" s="31"/>
     </row>
-    <row r="21" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A21" s="71"/>
+    <row r="21" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A21" s="91"/>
       <c r="B21" s="34" t="s">
         <v>102</v>
       </c>
@@ -4763,8 +4969,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A22" s="71"/>
+    <row r="22" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A22" s="91"/>
       <c r="B22" s="34" t="s">
         <v>103</v>
       </c>
@@ -4800,8 +5006,8 @@
       <c r="L22" s="31"/>
       <c r="M22" s="31"/>
     </row>
-    <row r="23" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A23" s="72"/>
+    <row r="23" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A23" s="92"/>
       <c r="B23" s="34" t="s">
         <v>5</v>
       </c>
@@ -4837,8 +5043,8 @@
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
     </row>
-    <row r="24" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A24" s="70" t="s">
+    <row r="24" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A24" s="90" t="s">
         <v>106</v>
       </c>
       <c r="B24" s="39" t="s">
@@ -4876,8 +5082,8 @@
       <c r="L24" s="31"/>
       <c r="M24" s="31"/>
     </row>
-    <row r="25" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A25" s="71"/>
+    <row r="25" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A25" s="91"/>
       <c r="B25" s="39" t="s">
         <v>113</v>
       </c>
@@ -4913,8 +5119,8 @@
       <c r="L25" s="31"/>
       <c r="M25" s="31"/>
     </row>
-    <row r="26" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A26" s="71"/>
+    <row r="26" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A26" s="91"/>
       <c r="B26" s="40" t="s">
         <v>97</v>
       </c>
@@ -4950,8 +5156,8 @@
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
     </row>
-    <row r="27" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A27" s="71"/>
+    <row r="27" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A27" s="91"/>
       <c r="B27" s="40" t="s">
         <v>98</v>
       </c>
@@ -4987,8 +5193,8 @@
       <c r="L27" s="31"/>
       <c r="M27" s="31"/>
     </row>
-    <row r="28" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A28" s="71"/>
+    <row r="28" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A28" s="91"/>
       <c r="B28" s="40" t="s">
         <v>99</v>
       </c>
@@ -5024,8 +5230,8 @@
       <c r="L28" s="31"/>
       <c r="M28" s="31"/>
     </row>
-    <row r="29" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A29" s="71"/>
+    <row r="29" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A29" s="91"/>
       <c r="B29" s="40" t="s">
         <v>100</v>
       </c>
@@ -5061,8 +5267,8 @@
       <c r="L29" s="31"/>
       <c r="M29" s="31"/>
     </row>
-    <row r="30" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A30" s="71"/>
+    <row r="30" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A30" s="91"/>
       <c r="B30" s="40" t="s">
         <v>101</v>
       </c>
@@ -5098,8 +5304,8 @@
       <c r="L30" s="31"/>
       <c r="M30" s="31"/>
     </row>
-    <row r="31" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A31" s="71"/>
+    <row r="31" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A31" s="91"/>
       <c r="B31" s="40" t="s">
         <v>102</v>
       </c>
@@ -5141,8 +5347,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A32" s="71"/>
+    <row r="32" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A32" s="91"/>
       <c r="B32" s="40" t="s">
         <v>103</v>
       </c>
@@ -5178,8 +5384,8 @@
       <c r="L32" s="31"/>
       <c r="M32" s="31"/>
     </row>
-    <row r="33" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A33" s="72"/>
+    <row r="33" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A33" s="92"/>
       <c r="B33" s="40" t="s">
         <v>5</v>
       </c>
@@ -5215,8 +5421,8 @@
       <c r="L33" s="31"/>
       <c r="M33" s="31"/>
     </row>
-    <row r="34" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A34" s="70" t="s">
+    <row r="34" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A34" s="90" t="s">
         <v>107</v>
       </c>
       <c r="B34" s="31" t="s">
@@ -5254,8 +5460,8 @@
       <c r="L34" s="31"/>
       <c r="M34" s="31"/>
     </row>
-    <row r="35" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A35" s="71"/>
+    <row r="35" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A35" s="91"/>
       <c r="B35" s="34" t="s">
         <v>99</v>
       </c>
@@ -5291,8 +5497,8 @@
       <c r="L35" s="31"/>
       <c r="M35" s="31"/>
     </row>
-    <row r="36" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A36" s="71"/>
+    <row r="36" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A36" s="91"/>
       <c r="B36" s="34" t="s">
         <v>100</v>
       </c>
@@ -5328,8 +5534,8 @@
       <c r="L36" s="31"/>
       <c r="M36" s="31"/>
     </row>
-    <row r="37" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A37" s="71"/>
+    <row r="37" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A37" s="91"/>
       <c r="B37" s="34" t="s">
         <v>101</v>
       </c>
@@ -5365,8 +5571,8 @@
       <c r="L37" s="31"/>
       <c r="M37" s="31"/>
     </row>
-    <row r="38" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A38" s="71"/>
+    <row r="38" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A38" s="91"/>
       <c r="B38" s="34" t="s">
         <v>102</v>
       </c>
@@ -5402,8 +5608,8 @@
       <c r="L38" s="31"/>
       <c r="M38" s="31"/>
     </row>
-    <row r="39" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A39" s="71"/>
+    <row r="39" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A39" s="91"/>
       <c r="B39" s="34" t="s">
         <v>103</v>
       </c>
@@ -5439,8 +5645,8 @@
       <c r="L39" s="31"/>
       <c r="M39" s="31"/>
     </row>
-    <row r="40" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A40" s="72"/>
+    <row r="40" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A40" s="92"/>
       <c r="B40" s="34" t="s">
         <v>5</v>
       </c>
@@ -5476,8 +5682,8 @@
       <c r="L40" s="31"/>
       <c r="M40" s="31"/>
     </row>
-    <row r="41" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A41" s="70" t="s">
+    <row r="41" spans="1:13" ht="38.25" thickBot="1">
+      <c r="A41" s="90" t="s">
         <v>108</v>
       </c>
       <c r="B41" s="31" t="s">
@@ -5517,8 +5723,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A42" s="71"/>
+    <row r="42" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A42" s="91"/>
       <c r="B42" s="34" t="s">
         <v>114</v>
       </c>
@@ -5554,8 +5760,8 @@
       <c r="L42" s="31"/>
       <c r="M42" s="31"/>
     </row>
-    <row r="43" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A43" s="71"/>
+    <row r="43" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A43" s="91"/>
       <c r="B43" s="34" t="s">
         <v>98</v>
       </c>
@@ -5591,8 +5797,8 @@
       <c r="L43" s="31"/>
       <c r="M43" s="31"/>
     </row>
-    <row r="44" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A44" s="71"/>
+    <row r="44" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A44" s="91"/>
       <c r="B44" s="34" t="s">
         <v>99</v>
       </c>
@@ -5628,8 +5834,8 @@
       <c r="L44" s="31"/>
       <c r="M44" s="31"/>
     </row>
-    <row r="45" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A45" s="71"/>
+    <row r="45" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A45" s="91"/>
       <c r="B45" s="34" t="s">
         <v>102</v>
       </c>
@@ -5665,8 +5871,8 @@
       <c r="L45" s="31"/>
       <c r="M45" s="31"/>
     </row>
-    <row r="46" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A46" s="71"/>
+    <row r="46" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A46" s="91"/>
       <c r="B46" s="34" t="s">
         <v>103</v>
       </c>
@@ -5702,8 +5908,8 @@
       <c r="L46" s="31"/>
       <c r="M46" s="31"/>
     </row>
-    <row r="47" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A47" s="72"/>
+    <row r="47" spans="1:13" ht="19.5" thickBot="1">
+      <c r="A47" s="92"/>
       <c r="B47" s="34" t="s">
         <v>5</v>
       </c>
@@ -5741,11 +5947,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A14:A23"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="C1:C2"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="E1:H1"/>
@@ -5753,6 +5954,11 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A14:A23"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59008B69-BE59-40FE-A4F4-6F6FE73800F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965E3334-9BB4-416B-97A5-5C7D799FD981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
     <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="126">
   <si>
     <t>TỔ CHỨC BIÊN CHẾ, TRANG BỊ HƯỚNG CHỦ YẾU</t>
   </si>
@@ -397,12 +400,6 @@
   </si>
   <si>
     <t>  </t>
-  </si>
-  <si>
-    <t>Cối 82mm</t>
-  </si>
-  <si>
-    <t>Cối 100mm</t>
   </si>
   <si>
     <t>Phân đội HC-KT</t>
@@ -639,7 +636,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -892,7 +889,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -981,134 +978,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1141,6 +1012,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1150,6 +1093,30 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1159,29 +1126,56 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="18" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1198,6 +1192,222 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Giao diện"/>
+      <sheetName val="QUÂN SỐ"/>
+      <sheetName val="1. QS, TBKT"/>
+      <sheetName val="BaoDamVKTBKT"/>
+      <sheetName val="Đạn"/>
+      <sheetName val="TinhHinhVC"/>
+      <sheetName val="ChiLenhHCKT"/>
+      <sheetName val="PhanCapVCHC"/>
+      <sheetName val="VCHC, VTKT"/>
+      <sheetName val="DuKienKLVatChat"/>
+      <sheetName val="KeHoachVanChuyen"/>
+      <sheetName val="KhoiLuongVanTai"/>
+      <sheetName val="DuKienTiLeTBBB"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="19">
+          <cell r="C19">
+            <v>36</v>
+          </cell>
+          <cell r="D19">
+            <v>439</v>
+          </cell>
+          <cell r="E19">
+            <v>27</v>
+          </cell>
+          <cell r="F19">
+            <v>6</v>
+          </cell>
+          <cell r="G19">
+            <v>54</v>
+          </cell>
+          <cell r="H19">
+            <v>2073</v>
+          </cell>
+          <cell r="I19">
+            <v>6</v>
+          </cell>
+          <cell r="J19">
+            <v>4</v>
+          </cell>
+          <cell r="K19">
+            <v>4</v>
+          </cell>
+          <cell r="L19">
+            <v>9</v>
+          </cell>
+          <cell r="M19">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36">
+            <v>12</v>
+          </cell>
+          <cell r="D36">
+            <v>157</v>
+          </cell>
+          <cell r="E36">
+            <v>15</v>
+          </cell>
+          <cell r="F36">
+            <v>4</v>
+          </cell>
+          <cell r="G36">
+            <v>30</v>
+          </cell>
+          <cell r="H36">
+            <v>822</v>
+          </cell>
+          <cell r="I36">
+            <v>4</v>
+          </cell>
+          <cell r="J36">
+            <v>3</v>
+          </cell>
+          <cell r="K36">
+            <v>0</v>
+          </cell>
+          <cell r="L36">
+            <v>3</v>
+          </cell>
+          <cell r="M36">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="C48">
+            <v>4</v>
+          </cell>
+          <cell r="D48">
+            <v>75</v>
+          </cell>
+          <cell r="E48">
+            <v>9</v>
+          </cell>
+          <cell r="F48">
+            <v>2</v>
+          </cell>
+          <cell r="G48">
+            <v>18</v>
+          </cell>
+          <cell r="H48">
+            <v>390</v>
+          </cell>
+          <cell r="I48">
+            <v>2</v>
+          </cell>
+          <cell r="J48">
+            <v>1</v>
+          </cell>
+          <cell r="K48">
+            <v>0</v>
+          </cell>
+          <cell r="L48">
+            <v>0</v>
+          </cell>
+          <cell r="M48">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="C59">
+            <v>0</v>
+          </cell>
+          <cell r="D59">
+            <v>20</v>
+          </cell>
+          <cell r="E59">
+            <v>3</v>
+          </cell>
+          <cell r="F59">
+            <v>0</v>
+          </cell>
+          <cell r="G59">
+            <v>6</v>
+          </cell>
+          <cell r="H59">
+            <v>102</v>
+          </cell>
+          <cell r="I59">
+            <v>0</v>
+          </cell>
+          <cell r="J59">
+            <v>0</v>
+          </cell>
+          <cell r="K59">
+            <v>0</v>
+          </cell>
+          <cell r="L59">
+            <v>0</v>
+          </cell>
+          <cell r="M59">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="C78">
+            <v>20</v>
+          </cell>
+          <cell r="D78">
+            <v>187</v>
+          </cell>
+          <cell r="E78">
+            <v>0</v>
+          </cell>
+          <cell r="F78">
+            <v>0</v>
+          </cell>
+          <cell r="G78">
+            <v>0</v>
+          </cell>
+          <cell r="H78">
+            <v>759</v>
+          </cell>
+          <cell r="I78">
+            <v>0</v>
+          </cell>
+          <cell r="J78">
+            <v>0</v>
+          </cell>
+          <cell r="K78">
+            <v>4</v>
+          </cell>
+          <cell r="L78">
+            <v>6</v>
+          </cell>
+          <cell r="M78">
+            <v>6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1501,76 +1711,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
+      <c r="A1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="44"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="14" customHeight="1">
-      <c r="A3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="47" t="s">
+      <c r="A3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47" t="s">
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47" t="s">
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1579,8 +1789,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
+      <c r="A5" s="48"/>
+      <c r="B5" s="48"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1596,7 +1806,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="47"/>
+      <c r="H5" s="48"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1951,76 +2161,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="44"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="47"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="47" t="s">
+      <c r="A3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47" t="s">
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47" t="s">
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2029,8 +2239,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
+      <c r="A5" s="48"/>
+      <c r="B5" s="48"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2046,7 +2256,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="47"/>
+      <c r="H5" s="48"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2527,32 +2737,32 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="48" t="s">
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="49" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
       <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
@@ -2565,8 +2775,8 @@
       <c r="G2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
@@ -2830,30 +3040,30 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="62" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="63"/>
-      <c r="I1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="65"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="56"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="26" t="s">
         <v>65</v>
       </c>
@@ -2956,76 +3166,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="44"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="47"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="47" t="s">
+      <c r="A3" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47" t="s">
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47" t="s">
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -3034,8 +3244,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
+      <c r="A5" s="48"/>
+      <c r="B5" s="48"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3051,7 +3261,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="47"/>
+      <c r="H5" s="48"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -3535,88 +3745,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="87" t="s">
+      <c r="C1" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="87" t="s">
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="88"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="87" t="s">
+      <c r="H1" s="78"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="89"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="79"/>
     </row>
     <row r="2" spans="1:13" ht="14.5" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="84" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="84" t="s">
+      <c r="D2" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="84" t="s">
+      <c r="E2" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="I2" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="94" t="s">
+      <c r="J2" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="95"/>
-      <c r="L2" s="90" t="s">
+      <c r="K2" s="70"/>
+      <c r="L2" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="91"/>
+      <c r="M2" s="74"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="93"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="76"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="86"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
       <c r="J4" s="29" t="s">
         <v>79</v>
       </c>
@@ -3634,8 +3844,8 @@
       <c r="A5" s="29">
         <v>1</v>
       </c>
-      <c r="B5" s="74" t="s">
-        <v>115</v>
+      <c r="B5" s="32" t="s">
+        <v>113</v>
       </c>
       <c r="C5" s="29">
         <f>SUM(C6:C12)</f>
@@ -3663,10 +3873,10 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="75" t="s">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>115</v>
       </c>
       <c r="C6" s="29">
         <v>1</v>
@@ -3674,7 +3884,7 @@
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29">
-        <f t="shared" ref="F6:F11" si="0">SUM(C6:E6)</f>
+        <f t="shared" ref="F6:F10" si="0">SUM(C6:E6)</f>
         <v>1</v>
       </c>
       <c r="G6" s="29"/>
@@ -3687,10 +3897,10 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="33" t="s">
         <v>116</v>
-      </c>
-      <c r="B7" s="75" t="s">
-        <v>118</v>
       </c>
       <c r="C7" s="29"/>
       <c r="D7" s="29">
@@ -3711,10 +3921,10 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="76" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>117</v>
       </c>
       <c r="C8" s="29"/>
       <c r="D8" s="29">
@@ -3735,10 +3945,10 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="75" t="s">
-        <v>120</v>
+        <v>114</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>118</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="29">
@@ -3759,10 +3969,10 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="75" t="s">
-        <v>121</v>
+        <v>114</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="C10" s="29"/>
       <c r="D10" s="29">
@@ -3785,10 +3995,10 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" s="75" t="s">
-        <v>122</v>
+        <v>114</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>120</v>
       </c>
       <c r="C11" s="29">
         <v>1</v>
@@ -3810,37 +4020,37 @@
       <c r="M11" s="29"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="78" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79">
-        <v>1</v>
-      </c>
-      <c r="E12" s="79">
+      <c r="A12" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37">
+        <v>1</v>
+      </c>
+      <c r="E12" s="37">
         <v>25</v>
       </c>
       <c r="F12" s="29">
         <f>SUM(C12:E12)</f>
         <v>26</v>
       </c>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="29">
         <v>2</v>
       </c>
-      <c r="B13" s="80" t="s">
-        <v>124</v>
+      <c r="B13" s="38" t="s">
+        <v>122</v>
       </c>
       <c r="C13" s="29">
         <f>C14+C15+C16</f>
@@ -3858,20 +4068,20 @@
         <f>F14+F15+F16</f>
         <v>34</v>
       </c>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="80"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="75" t="s">
-        <v>125</v>
+        <v>114</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>123</v>
       </c>
       <c r="C14" s="29"/>
       <c r="D14" s="29">
@@ -3884,63 +4094,63 @@
         <f>SUM(C14:E14)</f>
         <v>3</v>
       </c>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="82">
-        <v>1</v>
-      </c>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82">
+        <v>114</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="40">
+        <v>1</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40">
         <v>27</v>
       </c>
       <c r="F15" s="29">
         <f>SUM(C15:E15)</f>
         <v>28</v>
       </c>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="73"/>
-      <c r="M15" s="73"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="82" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="83" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82">
+      <c r="A16" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40">
         <v>3</v>
       </c>
-      <c r="E16" s="82"/>
+      <c r="E16" s="40"/>
       <c r="F16" s="29">
         <f>SUM(C16:E16)</f>
         <v>3</v>
       </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73"/>
-      <c r="K16" s="73"/>
-      <c r="L16" s="73"/>
-      <c r="M16" s="73"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3965,1787 +4175,2207 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9BFD24-F416-4E13-BF3D-CA2831AC61D2}">
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="16.6328125" customWidth="1"/>
     <col min="3" max="3" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.5" thickBot="1">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:13" ht="15.5" customHeight="1" thickBot="1">
+      <c r="A1" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="80" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="65" t="s">
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="69"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="83"/>
     </row>
     <row r="2" spans="1:13" ht="30.5" thickBot="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="30" t="s">
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="85" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="66"/>
-      <c r="J2" s="30" t="s">
+      <c r="I2" s="84"/>
+      <c r="J2" s="85" t="s">
         <v>89</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="M2" s="30" t="s">
+      <c r="M2" s="85" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A3" s="70" t="s">
+    <row r="3" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
+      <c r="A3" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="88">
+        <f>'[1]1. QS, TBKT'!M19</f>
         <v>9</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="89">
         <v>9</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="89">
         <v>9</v>
       </c>
-      <c r="G3" s="33">
-        <f>E3/D3</f>
-        <v>1</v>
-      </c>
-      <c r="H3" s="33">
-        <f>F3/E3</f>
-        <v>1</v>
-      </c>
-      <c r="I3" s="33">
+      <c r="G3" s="88">
+        <f>IFERROR(E3/D3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="88">
+        <f>IFERROR(F3/E3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="88">
         <f>D3</f>
         <v>9</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="88">
         <f>D3-E3</f>
         <v>0</v>
       </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
     </row>
     <row r="4" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="34" t="s">
+      <c r="A4" s="90"/>
+      <c r="B4" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="92">
+        <f>'[1]1. QS, TBKT'!K19</f>
         <v>4</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="89">
         <v>4</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="89">
         <v>4</v>
       </c>
-      <c r="G4" s="33">
-        <f t="shared" ref="G4:H47" si="0">E4/D4</f>
-        <v>1</v>
-      </c>
-      <c r="H4" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I4" s="33">
-        <f t="shared" ref="I4:I47" si="1">D4</f>
+      <c r="G4" s="88">
+        <f t="shared" ref="G4:H57" si="0">IFERROR(E4/D4,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I4" s="88">
+        <f t="shared" ref="I4:I57" si="1">D4</f>
         <v>4</v>
       </c>
-      <c r="J4" s="33">
-        <f t="shared" ref="J4:J47" si="2">D4-E4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
+      <c r="J4" s="88">
+        <f t="shared" ref="J4:J57" si="2">D4-E4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
     </row>
     <row r="5" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A5" s="71"/>
-      <c r="B5" s="34" t="s">
+      <c r="A5" s="90"/>
+      <c r="B5" s="91" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="92">
+        <f>'[1]1. QS, TBKT'!J19</f>
         <v>4</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="89">
         <v>4</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="89">
         <v>4</v>
       </c>
-      <c r="G5" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H5" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I5" s="33">
+      <c r="G5" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H5" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I5" s="88">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="88">
         <f>D5-E5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A6" s="71"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="90"/>
+      <c r="B6" s="91" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="35">
-        <v>8</v>
-      </c>
-      <c r="E6" s="33">
-        <v>8</v>
-      </c>
-      <c r="F6" s="33">
-        <v>8</v>
-      </c>
-      <c r="G6" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H6" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I6" s="33">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="J6" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
+      <c r="D6" s="92">
+        <f>'[1]1. QS, TBKT'!I19</f>
+        <v>6</v>
+      </c>
+      <c r="E6" s="89">
+        <v>6</v>
+      </c>
+      <c r="F6" s="89">
+        <v>6</v>
+      </c>
+      <c r="G6" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="88">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J6" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
     </row>
     <row r="7" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A7" s="71"/>
-      <c r="B7" s="34" t="s">
+      <c r="A7" s="90"/>
+      <c r="B7" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="92">
+        <f>'[1]1. QS, TBKT'!L19</f>
         <v>9</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="89">
         <v>9</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="89">
         <v>9</v>
       </c>
-      <c r="G7" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H7" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I7" s="33">
+      <c r="G7" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H7" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="88">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J7" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
+      <c r="J7" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
     </row>
     <row r="8" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A8" s="71"/>
-      <c r="B8" s="34" t="s">
+      <c r="A8" s="90"/>
+      <c r="B8" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="35">
-        <v>72</v>
-      </c>
-      <c r="E8" s="33">
-        <v>72</v>
-      </c>
-      <c r="F8" s="33">
-        <v>71</v>
-      </c>
-      <c r="G8" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="38">
-        <f t="shared" si="0"/>
-        <v>0.98611111111111116</v>
-      </c>
-      <c r="I8" s="33">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
-      <c r="J8" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="31" t="s">
+      <c r="D8" s="92">
+        <f>'[1]1. QS, TBKT'!G19</f>
+        <v>54</v>
+      </c>
+      <c r="E8" s="89">
+        <v>54</v>
+      </c>
+      <c r="F8" s="89">
+        <v>54</v>
+      </c>
+      <c r="G8" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="88">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="J8" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="L8" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="M8" s="31" t="s">
+      <c r="M8" s="30" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A9" s="71"/>
-      <c r="B9" s="34" t="s">
+      <c r="A9" s="90"/>
+      <c r="B9" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="35">
-        <v>8</v>
-      </c>
-      <c r="E9" s="33">
-        <v>8</v>
-      </c>
-      <c r="F9" s="33">
-        <v>8</v>
-      </c>
-      <c r="G9" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H9" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I9" s="33">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="J9" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
+      <c r="D9" s="92">
+        <f>'[1]1. QS, TBKT'!F19</f>
+        <v>6</v>
+      </c>
+      <c r="E9" s="89">
+        <v>6</v>
+      </c>
+      <c r="F9" s="89">
+        <v>6</v>
+      </c>
+      <c r="G9" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="88">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J9" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
     </row>
     <row r="10" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="90"/>
+      <c r="B10" s="91" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="92">
+        <f>'[1]1. QS, TBKT'!E19</f>
+        <v>27</v>
+      </c>
+      <c r="E10" s="89">
+        <v>27</v>
+      </c>
+      <c r="F10" s="89">
+        <v>27</v>
+      </c>
+      <c r="G10" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H10" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I10" s="88">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="J10" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+    </row>
+    <row r="11" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A11" s="90"/>
+      <c r="B11" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="92">
+        <f>'[1]1. QS, TBKT'!D19</f>
+        <v>439</v>
+      </c>
+      <c r="E11" s="89">
+        <v>439</v>
+      </c>
+      <c r="F11" s="89">
+        <v>439</v>
+      </c>
+      <c r="G11" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="88">
+        <f t="shared" si="1"/>
+        <v>439</v>
+      </c>
+      <c r="J11" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="M11" s="30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A12" s="90"/>
+      <c r="B12" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="92">
+        <f>'[1]1. QS, TBKT'!C19</f>
         <v>36</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E12" s="89">
         <v>36</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F12" s="89">
         <v>36</v>
       </c>
-      <c r="G10" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H10" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I10" s="33">
+      <c r="G12" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H12" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="88">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="J10" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-    </row>
-    <row r="11" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="34" t="s">
+      <c r="J12" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+    </row>
+    <row r="13" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A13" s="93"/>
+      <c r="B13" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="94">
+        <f>'[1]1. QS, TBKT'!H19</f>
+        <v>2073</v>
+      </c>
+      <c r="E13" s="95">
+        <v>2073</v>
+      </c>
+      <c r="F13" s="95">
+        <v>2073</v>
+      </c>
+      <c r="G13" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H13" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="88">
+        <f t="shared" si="1"/>
+        <v>2073</v>
+      </c>
+      <c r="J13" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+    </row>
+    <row r="14" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
+      <c r="A14" s="86" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="88">
+        <f>'[1]1. QS, TBKT'!M36</f>
+        <v>3</v>
+      </c>
+      <c r="E14" s="89">
+        <v>3</v>
+      </c>
+      <c r="F14" s="89">
+        <v>3</v>
+      </c>
+      <c r="G14" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H14" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="88">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J14" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+    </row>
+    <row r="15" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A15" s="90"/>
+      <c r="B15" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="92">
+        <f>'[1]1. QS, TBKT'!K36</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="89">
+        <v>0</v>
+      </c>
+      <c r="F15" s="89">
+        <v>0</v>
+      </c>
+      <c r="G15" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+    </row>
+    <row r="16" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A16" s="90"/>
+      <c r="B16" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="92">
+        <f>'[1]1. QS, TBKT'!J36</f>
+        <v>3</v>
+      </c>
+      <c r="E16" s="89">
+        <v>3</v>
+      </c>
+      <c r="F16" s="89">
+        <v>3</v>
+      </c>
+      <c r="G16" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H16" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I16" s="88">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J16" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+    </row>
+    <row r="17" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A17" s="90"/>
+      <c r="B17" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="92">
+        <f>'[1]1. QS, TBKT'!I36</f>
+        <v>4</v>
+      </c>
+      <c r="E17" s="89">
+        <v>4</v>
+      </c>
+      <c r="F17" s="89">
+        <v>4</v>
+      </c>
+      <c r="G17" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H17" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I17" s="88">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J17" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+    </row>
+    <row r="18" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A18" s="90"/>
+      <c r="B18" s="91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="92">
+        <f>'[1]1. QS, TBKT'!L36</f>
+        <v>3</v>
+      </c>
+      <c r="E18" s="89">
+        <v>3</v>
+      </c>
+      <c r="F18" s="89">
+        <v>3</v>
+      </c>
+      <c r="G18" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I18" s="88">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J18" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="M18" s="30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A19" s="90"/>
+      <c r="B19" s="91" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="92">
+        <f>'[1]1. QS, TBKT'!G36</f>
+        <v>30</v>
+      </c>
+      <c r="E19" s="89">
+        <v>30</v>
+      </c>
+      <c r="F19" s="89">
+        <v>30</v>
+      </c>
+      <c r="G19" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="88">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="J19" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+    </row>
+    <row r="20" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A20" s="90"/>
+      <c r="B20" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="92">
+        <f>'[1]1. QS, TBKT'!F36</f>
+        <v>4</v>
+      </c>
+      <c r="E20" s="89">
+        <v>4</v>
+      </c>
+      <c r="F20" s="89">
+        <v>4</v>
+      </c>
+      <c r="G20" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I20" s="88">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J20" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+    </row>
+    <row r="21" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A21" s="90"/>
+      <c r="B21" s="91" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="92">
+        <f>'[1]1. QS, TBKT'!E36</f>
+        <v>15</v>
+      </c>
+      <c r="E21" s="89">
+        <v>15</v>
+      </c>
+      <c r="F21" s="89">
+        <v>15</v>
+      </c>
+      <c r="G21" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H21" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I21" s="88">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="J21" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="M21" s="30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A22" s="90"/>
+      <c r="B22" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C22" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="35">
-        <v>486</v>
-      </c>
-      <c r="E11" s="33">
-        <v>486</v>
-      </c>
-      <c r="F11" s="33">
-        <v>474</v>
-      </c>
-      <c r="G11" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H11" s="38">
-        <f t="shared" si="0"/>
-        <v>0.97530864197530864</v>
-      </c>
-      <c r="I11" s="33">
-        <f t="shared" si="1"/>
-        <v>486</v>
-      </c>
-      <c r="J11" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="31" t="s">
+      <c r="D22" s="92">
+        <f>'[1]1. QS, TBKT'!D36</f>
+        <v>157</v>
+      </c>
+      <c r="E22" s="89">
+        <v>157</v>
+      </c>
+      <c r="F22" s="89">
+        <v>157</v>
+      </c>
+      <c r="G22" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H22" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I22" s="88">
+        <f t="shared" si="1"/>
+        <v>157</v>
+      </c>
+      <c r="J22" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+    </row>
+    <row r="23" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A23" s="90"/>
+      <c r="B23" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="92">
+        <f>'[1]1. QS, TBKT'!C36</f>
+        <v>12</v>
+      </c>
+      <c r="E23" s="89">
+        <v>12</v>
+      </c>
+      <c r="F23" s="89">
+        <v>12</v>
+      </c>
+      <c r="G23" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I23" s="88">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="J23" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+    </row>
+    <row r="24" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
+      <c r="A24" s="93"/>
+      <c r="B24" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="88">
+        <f>'[1]1. QS, TBKT'!H36</f>
+        <v>822</v>
+      </c>
+      <c r="E24" s="89">
+        <v>822</v>
+      </c>
+      <c r="F24" s="89">
+        <v>822</v>
+      </c>
+      <c r="G24" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I24" s="88">
+        <f t="shared" si="1"/>
+        <v>822</v>
+      </c>
+      <c r="J24" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+    </row>
+    <row r="25" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A25" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="88">
+        <f>'[1]1. QS, TBKT'!M48</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="89">
+        <v>0</v>
+      </c>
+      <c r="F25" s="89">
+        <v>0</v>
+      </c>
+      <c r="G25" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+    </row>
+    <row r="26" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A26" s="90"/>
+      <c r="B26" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="92">
+        <f>'[1]1. QS, TBKT'!K48</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="89">
+        <v>0</v>
+      </c>
+      <c r="F26" s="89">
+        <v>0</v>
+      </c>
+      <c r="G26" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+    </row>
+    <row r="27" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A27" s="90"/>
+      <c r="B27" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="92">
+        <f>'[1]1. QS, TBKT'!J48</f>
+        <v>1</v>
+      </c>
+      <c r="E27" s="89">
+        <v>1</v>
+      </c>
+      <c r="F27" s="89">
+        <v>1</v>
+      </c>
+      <c r="G27" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H27" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I27" s="88">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+    </row>
+    <row r="28" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A28" s="90"/>
+      <c r="B28" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="92">
+        <f>'[1]1. QS, TBKT'!I48</f>
+        <v>2</v>
+      </c>
+      <c r="E28" s="89">
+        <v>2</v>
+      </c>
+      <c r="F28" s="89">
+        <v>2</v>
+      </c>
+      <c r="G28" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H28" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I28" s="88">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+    </row>
+    <row r="29" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A29" s="90"/>
+      <c r="B29" s="91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="92">
+        <f>'[1]1. QS, TBKT'!L48</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="89">
+        <v>0</v>
+      </c>
+      <c r="F29" s="89">
+        <v>0</v>
+      </c>
+      <c r="G29" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+    </row>
+    <row r="30" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
+      <c r="A30" s="90"/>
+      <c r="B30" s="91" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="92">
+        <f>'[1]1. QS, TBKT'!G48</f>
+        <v>18</v>
+      </c>
+      <c r="E30" s="89">
+        <v>18</v>
+      </c>
+      <c r="F30" s="89">
+        <v>18</v>
+      </c>
+      <c r="G30" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H30" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I30" s="88">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="J30" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+    </row>
+    <row r="31" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A31" s="90"/>
+      <c r="B31" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="92">
+        <f>'[1]1. QS, TBKT'!F48</f>
+        <v>2</v>
+      </c>
+      <c r="E31" s="89">
+        <v>2</v>
+      </c>
+      <c r="F31" s="89">
+        <v>2</v>
+      </c>
+      <c r="G31" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H31" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I31" s="88">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J31" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="L11" s="31" t="s">
+      <c r="L31" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="M11" s="31" t="s">
+      <c r="M31" s="30" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="34" t="s">
+    <row r="32" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A32" s="90"/>
+      <c r="B32" s="91" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="92">
+        <f>'[1]1. QS, TBKT'!E48</f>
+        <v>9</v>
+      </c>
+      <c r="E32" s="89">
+        <v>9</v>
+      </c>
+      <c r="F32" s="89">
+        <v>9</v>
+      </c>
+      <c r="G32" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H32" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I32" s="88">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="J32" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+    </row>
+    <row r="33" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A33" s="90"/>
+      <c r="B33" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="92">
+        <f>'[1]1. QS, TBKT'!D48</f>
+        <v>75</v>
+      </c>
+      <c r="E33" s="89">
+        <v>75</v>
+      </c>
+      <c r="F33" s="89">
+        <v>75</v>
+      </c>
+      <c r="G33" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H33" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I33" s="88">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="J33" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+    </row>
+    <row r="34" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
+      <c r="A34" s="90"/>
+      <c r="B34" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C34" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="35">
-        <v>42</v>
-      </c>
-      <c r="E12" s="33">
-        <v>42</v>
-      </c>
-      <c r="F12" s="33">
-        <v>42</v>
-      </c>
-      <c r="G12" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I12" s="33">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-      <c r="J12" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-    </row>
-    <row r="13" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A13" s="72"/>
-      <c r="B13" s="34" t="s">
+      <c r="D34" s="88">
+        <f>'[1]1. QS, TBKT'!C48</f>
+        <v>4</v>
+      </c>
+      <c r="E34" s="89">
+        <v>4</v>
+      </c>
+      <c r="F34" s="89">
+        <v>4</v>
+      </c>
+      <c r="G34" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H34" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I34" s="88">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J34" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+    </row>
+    <row r="35" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A35" s="93"/>
+      <c r="B35" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C35" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="92">
+        <f>'[1]1. QS, TBKT'!H48</f>
+        <v>390</v>
+      </c>
+      <c r="E35" s="89">
+        <v>390</v>
+      </c>
+      <c r="F35" s="89">
+        <v>390</v>
+      </c>
+      <c r="G35" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I35" s="88">
+        <f t="shared" si="1"/>
+        <v>390</v>
+      </c>
+      <c r="J35" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+    </row>
+    <row r="36" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A36" s="86" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="92">
+        <f>'[1]1. QS, TBKT'!M59</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="89">
+        <v>0</v>
+      </c>
+      <c r="F36" s="89">
+        <v>0</v>
+      </c>
+      <c r="G36" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+    </row>
+    <row r="37" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A37" s="90"/>
+      <c r="B37" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="92">
+        <f>'[1]1. QS, TBKT'!K59</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="89">
+        <v>0</v>
+      </c>
+      <c r="F37" s="89">
+        <v>0</v>
+      </c>
+      <c r="G37" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+    </row>
+    <row r="38" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A38" s="90"/>
+      <c r="B38" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="92">
+        <f>'[1]1. QS, TBKT'!J59</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="89">
+        <v>0</v>
+      </c>
+      <c r="F38" s="89">
+        <v>0</v>
+      </c>
+      <c r="G38" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+    </row>
+    <row r="39" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A39" s="90"/>
+      <c r="B39" s="91" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="92">
+        <f>'[1]1. QS, TBKT'!I59</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="89">
+        <v>0</v>
+      </c>
+      <c r="F39" s="89">
+        <v>0</v>
+      </c>
+      <c r="G39" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+    </row>
+    <row r="40" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A40" s="90"/>
+      <c r="B40" s="91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" s="92">
+        <f>'[1]1. QS, TBKT'!L59</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="89">
+        <v>0</v>
+      </c>
+      <c r="F40" s="89">
+        <v>0</v>
+      </c>
+      <c r="G40" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+    </row>
+    <row r="41" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
+      <c r="A41" s="90"/>
+      <c r="B41" s="91" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="88">
+        <f>'[1]1. QS, TBKT'!G59</f>
+        <v>6</v>
+      </c>
+      <c r="E41" s="89">
+        <v>6</v>
+      </c>
+      <c r="F41" s="89">
+        <v>6</v>
+      </c>
+      <c r="G41" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H41" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I41" s="88">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J41" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A42" s="90"/>
+      <c r="B42" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="92">
+        <f>'[1]1. QS, TBKT'!F59</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="89">
+        <v>0</v>
+      </c>
+      <c r="F42" s="89">
+        <v>0</v>
+      </c>
+      <c r="G42" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+    </row>
+    <row r="43" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A43" s="90"/>
+      <c r="B43" s="91" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="92">
+        <f>'[1]1. QS, TBKT'!E59</f>
+        <v>3</v>
+      </c>
+      <c r="E43" s="89">
+        <v>3</v>
+      </c>
+      <c r="F43" s="89">
+        <v>3</v>
+      </c>
+      <c r="G43" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H43" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I43" s="88">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J43" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+    </row>
+    <row r="44" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A44" s="90"/>
+      <c r="B44" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44" s="92">
+        <f>'[1]1. QS, TBKT'!D59</f>
+        <v>20</v>
+      </c>
+      <c r="E44" s="89">
+        <v>20</v>
+      </c>
+      <c r="F44" s="89">
+        <v>20</v>
+      </c>
+      <c r="G44" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H44" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I44" s="88">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J44" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+    </row>
+    <row r="45" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A45" s="90"/>
+      <c r="B45" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="92">
+        <f>'[1]1. QS, TBKT'!C59</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="89">
+        <v>0</v>
+      </c>
+      <c r="F45" s="89">
+        <v>0</v>
+      </c>
+      <c r="G45" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+    </row>
+    <row r="46" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A46" s="90"/>
+      <c r="B46" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="88" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="37">
-        <v>2403</v>
-      </c>
-      <c r="E13" s="36">
-        <v>2403</v>
-      </c>
-      <c r="F13" s="36">
-        <v>2403</v>
-      </c>
-      <c r="G13" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H13" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I13" s="33">
-        <f t="shared" si="1"/>
-        <v>2403</v>
-      </c>
-      <c r="J13" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-    </row>
-    <row r="14" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A14" s="70" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="31" t="s">
+      <c r="D46" s="92">
+        <f>'[1]1. QS, TBKT'!H59</f>
+        <v>102</v>
+      </c>
+      <c r="E46" s="89">
+        <v>102</v>
+      </c>
+      <c r="F46" s="89">
+        <v>102</v>
+      </c>
+      <c r="G46" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H46" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I46" s="88">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="J46" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+    </row>
+    <row r="47" spans="1:13" ht="36.5" thickBot="1">
+      <c r="A47" s="96" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C47" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="33">
-        <v>3</v>
-      </c>
-      <c r="E14" s="33">
-        <v>3</v>
-      </c>
-      <c r="F14" s="33">
-        <v>3</v>
-      </c>
-      <c r="G14" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H14" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I14" s="33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J14" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-    </row>
-    <row r="15" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A15" s="71"/>
-      <c r="B15" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="32" t="s">
+      <c r="D47" s="92">
+        <f>'[1]1. QS, TBKT'!M78</f>
+        <v>6</v>
+      </c>
+      <c r="E47" s="89">
+        <v>6</v>
+      </c>
+      <c r="F47" s="89">
+        <v>6</v>
+      </c>
+      <c r="G47" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H47" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I47" s="88">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J47" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+    </row>
+    <row r="48" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A48" s="96"/>
+      <c r="B48" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="35">
-        <v>3</v>
-      </c>
-      <c r="E15" s="33">
-        <v>3</v>
-      </c>
-      <c r="F15" s="33">
-        <v>3</v>
-      </c>
-      <c r="G15" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H15" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I15" s="33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J15" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-    </row>
-    <row r="16" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A16" s="71"/>
-      <c r="B16" s="34" t="s">
+      <c r="D48" s="92">
+        <f>'[1]1. QS, TBKT'!K78</f>
+        <v>4</v>
+      </c>
+      <c r="E48" s="89">
+        <v>4</v>
+      </c>
+      <c r="F48" s="89">
+        <v>4</v>
+      </c>
+      <c r="G48" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H48" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I48" s="88">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J48" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+    </row>
+    <row r="49" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A49" s="96"/>
+      <c r="B49" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="92">
+        <f>'[1]1. QS, TBKT'!J78</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="89">
+        <v>0</v>
+      </c>
+      <c r="F49" s="89">
+        <v>0</v>
+      </c>
+      <c r="G49" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+    </row>
+    <row r="50" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A50" s="96"/>
+      <c r="B50" s="91" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C50" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="35">
-        <v>4</v>
-      </c>
-      <c r="E16" s="33">
-        <v>4</v>
-      </c>
-      <c r="F16" s="33">
-        <v>4</v>
-      </c>
-      <c r="G16" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H16" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I16" s="33">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="J16" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-    </row>
-    <row r="17" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="34" t="s">
+      <c r="D50" s="92">
+        <f>'[1]1. QS, TBKT'!I78</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="89">
+        <v>0</v>
+      </c>
+      <c r="F50" s="89">
+        <v>0</v>
+      </c>
+      <c r="G50" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+    </row>
+    <row r="51" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A51" s="96"/>
+      <c r="B51" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C51" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="35">
-        <v>3</v>
-      </c>
-      <c r="E17" s="33">
-        <v>3</v>
-      </c>
-      <c r="F17" s="33">
-        <v>3</v>
-      </c>
-      <c r="G17" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H17" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I17" s="33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J17" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-    </row>
-    <row r="18" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A18" s="71"/>
-      <c r="B18" s="34" t="s">
+      <c r="D51" s="92">
+        <f>'[1]1. QS, TBKT'!L78</f>
+        <v>6</v>
+      </c>
+      <c r="E51" s="89">
+        <v>6</v>
+      </c>
+      <c r="F51" s="89">
+        <v>6</v>
+      </c>
+      <c r="G51" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H51" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I51" s="88">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J51" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+    </row>
+    <row r="52" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A52" s="96"/>
+      <c r="B52" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C52" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="35">
-        <v>30</v>
-      </c>
-      <c r="E18" s="33">
-        <v>30</v>
-      </c>
-      <c r="F18" s="33">
-        <v>29</v>
-      </c>
-      <c r="G18" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="38">
-        <f t="shared" si="0"/>
-        <v>0.96666666666666667</v>
-      </c>
-      <c r="I18" s="33">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="J18" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="L18" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="M18" s="31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A19" s="71"/>
-      <c r="B19" s="34" t="s">
+      <c r="D52" s="92">
+        <f>'[1]1. QS, TBKT'!G78</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="89">
+        <v>0</v>
+      </c>
+      <c r="F52" s="89">
+        <v>0</v>
+      </c>
+      <c r="G52" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+    </row>
+    <row r="53" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A53" s="96"/>
+      <c r="B53" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C53" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="35">
-        <v>4</v>
-      </c>
-      <c r="E19" s="33">
-        <v>4</v>
-      </c>
-      <c r="F19" s="33">
-        <v>4</v>
-      </c>
-      <c r="G19" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H19" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I19" s="33">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="J19" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-    </row>
-    <row r="20" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A20" s="71"/>
-      <c r="B20" s="34" t="s">
+      <c r="D53" s="92">
+        <f>'[1]1. QS, TBKT'!F78</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="89">
+        <v>0</v>
+      </c>
+      <c r="F53" s="89">
+        <v>0</v>
+      </c>
+      <c r="G53" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+    </row>
+    <row r="54" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A54" s="96"/>
+      <c r="B54" s="91" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C54" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="35">
-        <v>18</v>
-      </c>
-      <c r="E20" s="33">
-        <v>18</v>
-      </c>
-      <c r="F20" s="33">
-        <v>18</v>
-      </c>
-      <c r="G20" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H20" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I20" s="33">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="J20" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-    </row>
-    <row r="21" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A21" s="71"/>
-      <c r="B21" s="34" t="s">
+      <c r="D54" s="92">
+        <f>'[1]1. QS, TBKT'!E78</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="89">
+        <v>0</v>
+      </c>
+      <c r="F54" s="89">
+        <v>0</v>
+      </c>
+      <c r="G54" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="88">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="88">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+    </row>
+    <row r="55" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A55" s="96"/>
+      <c r="B55" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C55" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="35">
-        <v>161</v>
-      </c>
-      <c r="E21" s="33">
-        <v>161</v>
-      </c>
-      <c r="F21" s="33">
-        <v>155</v>
-      </c>
-      <c r="G21" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H21" s="38">
-        <f t="shared" si="0"/>
-        <v>0.96273291925465843</v>
-      </c>
-      <c r="I21" s="33">
-        <f t="shared" si="1"/>
-        <v>161</v>
-      </c>
-      <c r="J21" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="L21" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="M21" s="31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A22" s="71"/>
-      <c r="B22" s="34" t="s">
+      <c r="D55" s="92">
+        <f>'[1]1. QS, TBKT'!D78</f>
+        <v>187</v>
+      </c>
+      <c r="E55" s="89">
+        <v>187</v>
+      </c>
+      <c r="F55" s="89">
+        <v>187</v>
+      </c>
+      <c r="G55" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H55" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I55" s="88">
+        <f t="shared" si="1"/>
+        <v>187</v>
+      </c>
+      <c r="J55" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+    </row>
+    <row r="56" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A56" s="96"/>
+      <c r="B56" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C56" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="35">
-        <v>12</v>
-      </c>
-      <c r="E22" s="33">
-        <v>12</v>
-      </c>
-      <c r="F22" s="33">
-        <v>12</v>
-      </c>
-      <c r="G22" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H22" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I22" s="33">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="J22" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-    </row>
-    <row r="23" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A23" s="72"/>
-      <c r="B23" s="34" t="s">
+      <c r="D56" s="92">
+        <f>'[1]1. QS, TBKT'!C78</f>
+        <v>20</v>
+      </c>
+      <c r="E56" s="89">
+        <v>20</v>
+      </c>
+      <c r="F56" s="89">
+        <v>20</v>
+      </c>
+      <c r="G56" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H56" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I56" s="88">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J56" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
+    </row>
+    <row r="57" spans="1:13" ht="18.5" thickBot="1">
+      <c r="A57" s="96"/>
+      <c r="B57" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C57" s="88" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="35">
-        <v>846</v>
-      </c>
-      <c r="E23" s="33">
-        <v>846</v>
-      </c>
-      <c r="F23" s="33">
-        <v>846</v>
-      </c>
-      <c r="G23" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H23" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I23" s="33">
-        <f t="shared" si="1"/>
-        <v>846</v>
-      </c>
-      <c r="J23" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-    </row>
-    <row r="24" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A24" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="33">
-        <v>3</v>
-      </c>
-      <c r="E24" s="33">
-        <v>3</v>
-      </c>
-      <c r="F24" s="33">
-        <v>3</v>
-      </c>
-      <c r="G24" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H24" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I24" s="33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J24" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-    </row>
-    <row r="25" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A25" s="71"/>
-      <c r="B25" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="33">
-        <v>1</v>
-      </c>
-      <c r="E25" s="33">
-        <v>1</v>
-      </c>
-      <c r="F25" s="33">
-        <v>1</v>
-      </c>
-      <c r="G25" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H25" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I25" s="33">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J25" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-    </row>
-    <row r="26" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A26" s="71"/>
-      <c r="B26" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="35">
-        <v>2</v>
-      </c>
-      <c r="E26" s="33">
-        <v>2</v>
-      </c>
-      <c r="F26" s="33">
-        <v>2</v>
-      </c>
-      <c r="G26" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H26" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I26" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="J26" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-    </row>
-    <row r="27" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A27" s="71"/>
-      <c r="B27" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="35">
-        <v>3</v>
-      </c>
-      <c r="E27" s="33">
-        <v>3</v>
-      </c>
-      <c r="F27" s="33">
-        <v>3</v>
-      </c>
-      <c r="G27" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H27" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I27" s="33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J27" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-    </row>
-    <row r="28" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A28" s="71"/>
-      <c r="B28" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="35">
-        <v>18</v>
-      </c>
-      <c r="E28" s="33">
-        <v>18</v>
-      </c>
-      <c r="F28" s="33">
-        <v>18</v>
-      </c>
-      <c r="G28" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H28" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I28" s="33">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="J28" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-    </row>
-    <row r="29" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A29" s="71"/>
-      <c r="B29" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="35">
-        <v>2</v>
-      </c>
-      <c r="E29" s="33">
-        <v>2</v>
-      </c>
-      <c r="F29" s="33">
-        <v>2</v>
-      </c>
-      <c r="G29" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H29" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I29" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="J29" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-    </row>
-    <row r="30" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A30" s="71"/>
-      <c r="B30" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="35">
-        <v>9</v>
-      </c>
-      <c r="E30" s="33">
-        <v>9</v>
-      </c>
-      <c r="F30" s="33">
-        <v>9</v>
-      </c>
-      <c r="G30" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H30" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I30" s="33">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="J30" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-    </row>
-    <row r="31" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A31" s="71"/>
-      <c r="B31" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="35">
-        <v>96</v>
-      </c>
-      <c r="E31" s="33">
-        <v>96</v>
-      </c>
-      <c r="F31" s="33">
-        <v>92</v>
-      </c>
-      <c r="G31" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H31" s="38">
-        <f t="shared" si="0"/>
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="I31" s="33">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="J31" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="L31" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="M31" s="31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A32" s="71"/>
-      <c r="B32" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="35">
-        <v>4</v>
-      </c>
-      <c r="E32" s="33">
-        <v>4</v>
-      </c>
-      <c r="F32" s="33">
-        <v>4</v>
-      </c>
-      <c r="G32" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H32" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I32" s="33">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="J32" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-    </row>
-    <row r="33" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A33" s="72"/>
-      <c r="B33" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="35">
-        <v>514</v>
-      </c>
-      <c r="E33" s="33">
-        <v>514</v>
-      </c>
-      <c r="F33" s="33">
-        <v>514</v>
-      </c>
-      <c r="G33" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H33" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I33" s="33">
-        <f t="shared" si="1"/>
-        <v>514</v>
-      </c>
-      <c r="J33" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-    </row>
-    <row r="34" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A34" s="70" t="s">
-        <v>107</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="33">
-        <v>2</v>
-      </c>
-      <c r="E34" s="33">
-        <v>2</v>
-      </c>
-      <c r="F34" s="33">
-        <v>2</v>
-      </c>
-      <c r="G34" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H34" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I34" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="J34" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-    </row>
-    <row r="35" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A35" s="71"/>
-      <c r="B35" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="35">
-        <v>18</v>
-      </c>
-      <c r="E35" s="33">
-        <v>18</v>
-      </c>
-      <c r="F35" s="33">
-        <v>18</v>
-      </c>
-      <c r="G35" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H35" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I35" s="33">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="J35" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-    </row>
-    <row r="36" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A36" s="71"/>
-      <c r="B36" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="35">
-        <v>2</v>
-      </c>
-      <c r="E36" s="33">
-        <v>2</v>
-      </c>
-      <c r="F36" s="33">
-        <v>2</v>
-      </c>
-      <c r="G36" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H36" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I36" s="33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="J36" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-    </row>
-    <row r="37" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A37" s="71"/>
-      <c r="B37" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="35">
-        <v>9</v>
-      </c>
-      <c r="E37" s="33">
-        <v>9</v>
-      </c>
-      <c r="F37" s="33">
-        <v>9</v>
-      </c>
-      <c r="G37" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H37" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I37" s="33">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="J37" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-    </row>
-    <row r="38" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A38" s="71"/>
-      <c r="B38" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="35">
-        <v>69</v>
-      </c>
-      <c r="E38" s="33">
-        <v>69</v>
-      </c>
-      <c r="F38" s="33">
-        <v>67</v>
-      </c>
-      <c r="G38" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H38" s="38">
-        <f t="shared" si="0"/>
-        <v>0.97101449275362317</v>
-      </c>
-      <c r="I38" s="33">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="J38" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-    </row>
-    <row r="39" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A39" s="71"/>
-      <c r="B39" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" s="35">
-        <v>4</v>
-      </c>
-      <c r="E39" s="33">
-        <v>4</v>
-      </c>
-      <c r="F39" s="33">
-        <v>4</v>
-      </c>
-      <c r="G39" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H39" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I39" s="33">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="J39" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-    </row>
-    <row r="40" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A40" s="72"/>
-      <c r="B40" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" s="35">
-        <v>350</v>
-      </c>
-      <c r="E40" s="33">
-        <v>350</v>
-      </c>
-      <c r="F40" s="33">
-        <v>350</v>
-      </c>
-      <c r="G40" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H40" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I40" s="33">
-        <f t="shared" si="1"/>
-        <v>350</v>
-      </c>
-      <c r="J40" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-    </row>
-    <row r="41" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A41" s="70" t="s">
-        <v>108</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="33">
-        <v>3</v>
-      </c>
-      <c r="E41" s="33">
-        <v>3</v>
-      </c>
-      <c r="F41" s="33">
-        <v>3</v>
-      </c>
-      <c r="G41" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H41" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I41" s="33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J41" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A42" s="71"/>
-      <c r="B42" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" s="35">
-        <v>4</v>
-      </c>
-      <c r="E42" s="33">
-        <v>4</v>
-      </c>
-      <c r="F42" s="33">
-        <v>4</v>
-      </c>
-      <c r="G42" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H42" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I42" s="33">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="J42" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-    </row>
-    <row r="43" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A43" s="71"/>
-      <c r="B43" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" s="35">
-        <v>3</v>
-      </c>
-      <c r="E43" s="33">
-        <v>3</v>
-      </c>
-      <c r="F43" s="33">
-        <v>3</v>
-      </c>
-      <c r="G43" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H43" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I43" s="33">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="J43" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="31"/>
-    </row>
-    <row r="44" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A44" s="71"/>
-      <c r="B44" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="35">
-        <v>6</v>
-      </c>
-      <c r="E44" s="33">
-        <v>6</v>
-      </c>
-      <c r="F44" s="33">
-        <v>6</v>
-      </c>
-      <c r="G44" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H44" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I44" s="33">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="J44" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="31"/>
-    </row>
-    <row r="45" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A45" s="71"/>
-      <c r="B45" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C45" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="35">
-        <v>160</v>
-      </c>
-      <c r="E45" s="33">
-        <v>160</v>
-      </c>
-      <c r="F45" s="33">
-        <v>160</v>
-      </c>
-      <c r="G45" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H45" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I45" s="33">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="J45" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
-    </row>
-    <row r="46" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A46" s="71"/>
-      <c r="B46" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C46" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="35">
-        <v>22</v>
-      </c>
-      <c r="E46" s="33">
-        <v>22</v>
-      </c>
-      <c r="F46" s="33">
-        <v>22</v>
-      </c>
-      <c r="G46" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H46" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I46" s="33">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="J46" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
-    </row>
-    <row r="47" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A47" s="72"/>
-      <c r="B47" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" s="35">
-        <v>693</v>
-      </c>
-      <c r="E47" s="33">
-        <v>693</v>
-      </c>
-      <c r="F47" s="33">
-        <v>693</v>
-      </c>
-      <c r="G47" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H47" s="33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I47" s="33">
-        <f t="shared" si="1"/>
-        <v>693</v>
-      </c>
-      <c r="J47" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
+      <c r="D57" s="92">
+        <f>'[1]1. QS, TBKT'!H78</f>
+        <v>759</v>
+      </c>
+      <c r="E57" s="89">
+        <v>759</v>
+      </c>
+      <c r="F57" s="89">
+        <v>759</v>
+      </c>
+      <c r="G57" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H57" s="88">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I57" s="88">
+        <f t="shared" si="1"/>
+        <v>759</v>
+      </c>
+      <c r="J57" s="88">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A14:A23"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="C1:C2"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="E1:H1"/>
@@ -5753,6 +6383,11 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="A14:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A46"/>
+    <mergeCell ref="A47:A57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965E3334-9BB4-416B-97A5-5C7D799FD981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF55E933-7CB6-4383-92D1-7147401DA585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
@@ -1012,6 +1012,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1126,52 +1150,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1711,76 +1711,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="44"/>
+      <c r="A1" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="52"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="47"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="55"/>
     </row>
     <row r="3" spans="1:13" ht="14" customHeight="1">
-      <c r="A3" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="48" t="s">
+      <c r="A3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48" t="s">
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48" t="s">
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1789,8 +1789,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="48"/>
-      <c r="B5" s="48"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="48"/>
+      <c r="H5" s="56"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2161,76 +2161,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="44"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="52"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="47"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="55"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="48" t="s">
+      <c r="A3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48" t="s">
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48" t="s">
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2239,8 +2239,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="48"/>
-      <c r="B5" s="48"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="48"/>
+      <c r="H5" s="56"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2737,32 +2737,32 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="49" t="s">
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="57" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
+      <c r="A2" s="60"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
       <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
@@ -2775,8 +2775,8 @@
       <c r="G2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
@@ -3040,30 +3040,30 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="63" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="65"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="73"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="57"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
       <c r="D2" s="26" t="s">
         <v>65</v>
       </c>
@@ -3166,76 +3166,76 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="44"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="52"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="47"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="55"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="48" t="s">
+      <c r="A3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48" t="s">
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48" t="s">
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -3244,8 +3244,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="48"/>
-      <c r="B5" s="48"/>
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3261,7 +3261,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="48"/>
+      <c r="H5" s="56"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -3745,88 +3745,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="77" t="s">
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="77" t="s">
+      <c r="H1" s="86"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="79"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="87"/>
     </row>
     <row r="2" spans="1:13" ht="14.5" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="66" t="s">
+      <c r="A2" s="75"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="66" t="s">
+      <c r="G2" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="69" t="s">
+      <c r="J2" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="70"/>
-      <c r="L2" s="73" t="s">
+      <c r="K2" s="78"/>
+      <c r="L2" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="74"/>
+      <c r="M2" s="82"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="76"/>
+      <c r="A3" s="75"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="84"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
       <c r="J4" s="29" t="s">
         <v>79</v>
       </c>
@@ -4183,98 +4183,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.5" customHeight="1" thickBot="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C1" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="80" t="s">
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="81" t="s">
+      <c r="J1" s="88" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="83"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="90"/>
     </row>
     <row r="2" spans="1:13" ht="30.5" thickBot="1">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="85" t="s">
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="85" t="s">
+      <c r="H2" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="84"/>
-      <c r="J2" s="85" t="s">
+      <c r="I2" s="95"/>
+      <c r="J2" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="K2" s="85" t="s">
+      <c r="K2" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="85" t="s">
+      <c r="L2" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="M2" s="85" t="s">
+      <c r="M2" s="42" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="88">
+      <c r="D3" s="44">
         <f>'[1]1. QS, TBKT'!M19</f>
         <v>9</v>
       </c>
-      <c r="E3" s="89">
+      <c r="E3" s="45">
         <v>9</v>
       </c>
-      <c r="F3" s="89">
+      <c r="F3" s="45">
         <v>9</v>
       </c>
-      <c r="G3" s="88">
+      <c r="G3" s="44">
         <f>IFERROR(E3/D3,0)</f>
         <v>1</v>
       </c>
-      <c r="H3" s="88">
+      <c r="H3" s="44">
         <f>IFERROR(F3/E3,0)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="88">
+      <c r="I3" s="44">
         <f>D3</f>
         <v>9</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="44">
         <f>D3-E3</f>
         <v>0</v>
       </c>
@@ -4283,36 +4283,36 @@
       <c r="M3" s="30"/>
     </row>
     <row r="4" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91" t="s">
+      <c r="A4" s="92"/>
+      <c r="B4" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="92">
+      <c r="D4" s="47">
         <f>'[1]1. QS, TBKT'!K19</f>
         <v>4</v>
       </c>
-      <c r="E4" s="89">
+      <c r="E4" s="45">
         <v>4</v>
       </c>
-      <c r="F4" s="89">
+      <c r="F4" s="45">
         <v>4</v>
       </c>
-      <c r="G4" s="88">
+      <c r="G4" s="44">
         <f t="shared" ref="G4:H57" si="0">IFERROR(E4/D4,0)</f>
         <v>1</v>
       </c>
-      <c r="H4" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I4" s="88">
+      <c r="H4" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I4" s="44">
         <f t="shared" ref="I4:I57" si="1">D4</f>
         <v>4</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="44">
         <f t="shared" ref="J4:J57" si="2">D4-E4</f>
         <v>0</v>
       </c>
@@ -4321,36 +4321,36 @@
       <c r="M4" s="30"/>
     </row>
     <row r="5" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A5" s="90"/>
-      <c r="B5" s="91" t="s">
+      <c r="A5" s="92"/>
+      <c r="B5" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="92">
+      <c r="D5" s="47">
         <f>'[1]1. QS, TBKT'!J19</f>
         <v>4</v>
       </c>
-      <c r="E5" s="89">
+      <c r="E5" s="45">
         <v>4</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="45">
         <v>4</v>
       </c>
-      <c r="G5" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H5" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I5" s="88">
+      <c r="G5" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H5" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I5" s="44">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="44">
         <f>D5-E5</f>
         <v>0</v>
       </c>
@@ -4359,36 +4359,36 @@
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A6" s="90"/>
-      <c r="B6" s="91" t="s">
+      <c r="A6" s="92"/>
+      <c r="B6" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="88" t="s">
+      <c r="C6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="47">
         <f>'[1]1. QS, TBKT'!I19</f>
         <v>6</v>
       </c>
-      <c r="E6" s="89">
+      <c r="E6" s="45">
         <v>6</v>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="45">
         <v>6</v>
       </c>
-      <c r="G6" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H6" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I6" s="88">
+      <c r="G6" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="44">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4397,36 +4397,36 @@
       <c r="M6" s="30"/>
     </row>
     <row r="7" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A7" s="90"/>
-      <c r="B7" s="91" t="s">
+      <c r="A7" s="92"/>
+      <c r="B7" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="88" t="s">
+      <c r="C7" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="47">
         <f>'[1]1. QS, TBKT'!L19</f>
         <v>9</v>
       </c>
-      <c r="E7" s="89">
+      <c r="E7" s="45">
         <v>9</v>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="45">
         <v>9</v>
       </c>
-      <c r="G7" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H7" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I7" s="88">
+      <c r="G7" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H7" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="44">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4435,36 +4435,36 @@
       <c r="M7" s="30"/>
     </row>
     <row r="8" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A8" s="90"/>
-      <c r="B8" s="91" t="s">
+      <c r="A8" s="92"/>
+      <c r="B8" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="88" t="s">
+      <c r="C8" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="92">
+      <c r="D8" s="47">
         <f>'[1]1. QS, TBKT'!G19</f>
         <v>54</v>
       </c>
-      <c r="E8" s="89">
+      <c r="E8" s="45">
         <v>54</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="45">
         <v>54</v>
       </c>
-      <c r="G8" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I8" s="88">
+      <c r="G8" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="44">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4479,36 +4479,36 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91" t="s">
+      <c r="A9" s="92"/>
+      <c r="B9" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="88" t="s">
+      <c r="C9" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="92">
+      <c r="D9" s="47">
         <f>'[1]1. QS, TBKT'!F19</f>
         <v>6</v>
       </c>
-      <c r="E9" s="89">
+      <c r="E9" s="45">
         <v>6</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="45">
         <v>6</v>
       </c>
-      <c r="G9" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H9" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I9" s="88">
+      <c r="G9" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="44">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4517,36 +4517,36 @@
       <c r="M9" s="30"/>
     </row>
     <row r="10" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A10" s="90"/>
-      <c r="B10" s="91" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="47">
         <f>'[1]1. QS, TBKT'!E19</f>
         <v>27</v>
       </c>
-      <c r="E10" s="89">
+      <c r="E10" s="45">
         <v>27</v>
       </c>
-      <c r="F10" s="89">
+      <c r="F10" s="45">
         <v>27</v>
       </c>
-      <c r="G10" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H10" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I10" s="88">
+      <c r="G10" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H10" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I10" s="44">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J10" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4555,36 +4555,36 @@
       <c r="M10" s="30"/>
     </row>
     <row r="11" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91" t="s">
+      <c r="A11" s="92"/>
+      <c r="B11" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="92">
+      <c r="D11" s="47">
         <f>'[1]1. QS, TBKT'!D19</f>
         <v>439</v>
       </c>
-      <c r="E11" s="89">
+      <c r="E11" s="45">
         <v>439</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="45">
         <v>439</v>
       </c>
-      <c r="G11" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H11" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I11" s="88">
+      <c r="G11" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="44">
         <f t="shared" si="1"/>
         <v>439</v>
       </c>
-      <c r="J11" s="88">
+      <c r="J11" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4599,36 +4599,36 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91" t="s">
+      <c r="A12" s="92"/>
+      <c r="B12" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="47">
         <f>'[1]1. QS, TBKT'!C19</f>
         <v>36</v>
       </c>
-      <c r="E12" s="89">
+      <c r="E12" s="45">
         <v>36</v>
       </c>
-      <c r="F12" s="89">
+      <c r="F12" s="45">
         <v>36</v>
       </c>
-      <c r="G12" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I12" s="88">
+      <c r="G12" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H12" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="44">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="J12" s="88">
+      <c r="J12" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4638,35 +4638,35 @@
     </row>
     <row r="13" spans="1:13" ht="18.5" thickBot="1">
       <c r="A13" s="93"/>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="94">
+      <c r="D13" s="48">
         <f>'[1]1. QS, TBKT'!H19</f>
         <v>2073</v>
       </c>
-      <c r="E13" s="95">
+      <c r="E13" s="49">
         <v>2073</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="49">
         <v>2073</v>
       </c>
-      <c r="G13" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H13" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I13" s="88">
+      <c r="G13" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H13" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="44">
         <f t="shared" si="1"/>
         <v>2073</v>
       </c>
-      <c r="J13" s="88">
+      <c r="J13" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4675,38 +4675,38 @@
       <c r="M13" s="30"/>
     </row>
     <row r="14" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="88">
+      <c r="D14" s="44">
         <f>'[1]1. QS, TBKT'!M36</f>
         <v>3</v>
       </c>
-      <c r="E14" s="89">
+      <c r="E14" s="45">
         <v>3</v>
       </c>
-      <c r="F14" s="89">
+      <c r="F14" s="45">
         <v>3</v>
       </c>
-      <c r="G14" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H14" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I14" s="88">
+      <c r="G14" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H14" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="44">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J14" s="88">
+      <c r="J14" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4715,36 +4715,36 @@
       <c r="M14" s="30"/>
     </row>
     <row r="15" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A15" s="90"/>
-      <c r="B15" s="91" t="s">
+      <c r="A15" s="92"/>
+      <c r="B15" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="92">
+      <c r="D15" s="47">
         <f>'[1]1. QS, TBKT'!K36</f>
         <v>0</v>
       </c>
-      <c r="E15" s="89">
-        <v>0</v>
-      </c>
-      <c r="F15" s="89">
-        <v>0</v>
-      </c>
-      <c r="G15" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="88">
+      <c r="E15" s="45">
+        <v>0</v>
+      </c>
+      <c r="F15" s="45">
+        <v>0</v>
+      </c>
+      <c r="G15" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4753,36 +4753,36 @@
       <c r="M15" s="30"/>
     </row>
     <row r="16" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A16" s="90"/>
-      <c r="B16" s="91" t="s">
+      <c r="A16" s="92"/>
+      <c r="B16" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="92">
+      <c r="D16" s="47">
         <f>'[1]1. QS, TBKT'!J36</f>
         <v>3</v>
       </c>
-      <c r="E16" s="89">
+      <c r="E16" s="45">
         <v>3</v>
       </c>
-      <c r="F16" s="89">
+      <c r="F16" s="45">
         <v>3</v>
       </c>
-      <c r="G16" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H16" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I16" s="88">
+      <c r="G16" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H16" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I16" s="44">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J16" s="88">
+      <c r="J16" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4791,36 +4791,36 @@
       <c r="M16" s="30"/>
     </row>
     <row r="17" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A17" s="90"/>
-      <c r="B17" s="91" t="s">
+      <c r="A17" s="92"/>
+      <c r="B17" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="88" t="s">
+      <c r="C17" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="92">
+      <c r="D17" s="47">
         <f>'[1]1. QS, TBKT'!I36</f>
         <v>4</v>
       </c>
-      <c r="E17" s="89">
+      <c r="E17" s="45">
         <v>4</v>
       </c>
-      <c r="F17" s="89">
+      <c r="F17" s="45">
         <v>4</v>
       </c>
-      <c r="G17" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H17" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I17" s="88">
+      <c r="G17" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H17" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I17" s="44">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J17" s="88">
+      <c r="J17" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4829,36 +4829,36 @@
       <c r="M17" s="30"/>
     </row>
     <row r="18" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="91" t="s">
+      <c r="A18" s="92"/>
+      <c r="B18" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="92">
+      <c r="D18" s="47">
         <f>'[1]1. QS, TBKT'!L36</f>
         <v>3</v>
       </c>
-      <c r="E18" s="89">
+      <c r="E18" s="45">
         <v>3</v>
       </c>
-      <c r="F18" s="89">
+      <c r="F18" s="45">
         <v>3</v>
       </c>
-      <c r="G18" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I18" s="88">
+      <c r="G18" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I18" s="44">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J18" s="88">
+      <c r="J18" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4873,36 +4873,36 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="91" t="s">
+      <c r="A19" s="92"/>
+      <c r="B19" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="92">
+      <c r="D19" s="47">
         <f>'[1]1. QS, TBKT'!G36</f>
         <v>30</v>
       </c>
-      <c r="E19" s="89">
+      <c r="E19" s="45">
         <v>30</v>
       </c>
-      <c r="F19" s="89">
+      <c r="F19" s="45">
         <v>30</v>
       </c>
-      <c r="G19" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H19" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I19" s="88">
+      <c r="G19" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="44">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="J19" s="88">
+      <c r="J19" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4911,36 +4911,36 @@
       <c r="M19" s="30"/>
     </row>
     <row r="20" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A20" s="90"/>
-      <c r="B20" s="91" t="s">
+      <c r="A20" s="92"/>
+      <c r="B20" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="88" t="s">
+      <c r="C20" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="92">
+      <c r="D20" s="47">
         <f>'[1]1. QS, TBKT'!F36</f>
         <v>4</v>
       </c>
-      <c r="E20" s="89">
+      <c r="E20" s="45">
         <v>4</v>
       </c>
-      <c r="F20" s="89">
+      <c r="F20" s="45">
         <v>4</v>
       </c>
-      <c r="G20" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H20" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I20" s="88">
+      <c r="G20" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I20" s="44">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J20" s="88">
+      <c r="J20" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4949,36 +4949,36 @@
       <c r="M20" s="30"/>
     </row>
     <row r="21" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A21" s="90"/>
-      <c r="B21" s="91" t="s">
+      <c r="A21" s="92"/>
+      <c r="B21" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="88" t="s">
+      <c r="C21" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="92">
+      <c r="D21" s="47">
         <f>'[1]1. QS, TBKT'!E36</f>
         <v>15</v>
       </c>
-      <c r="E21" s="89">
+      <c r="E21" s="45">
         <v>15</v>
       </c>
-      <c r="F21" s="89">
+      <c r="F21" s="45">
         <v>15</v>
       </c>
-      <c r="G21" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H21" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I21" s="88">
+      <c r="G21" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H21" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I21" s="44">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="J21" s="88">
+      <c r="J21" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4993,36 +4993,36 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A22" s="90"/>
-      <c r="B22" s="91" t="s">
+      <c r="A22" s="92"/>
+      <c r="B22" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="88" t="s">
+      <c r="C22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="92">
+      <c r="D22" s="47">
         <f>'[1]1. QS, TBKT'!D36</f>
         <v>157</v>
       </c>
-      <c r="E22" s="89">
+      <c r="E22" s="45">
         <v>157</v>
       </c>
-      <c r="F22" s="89">
+      <c r="F22" s="45">
         <v>157</v>
       </c>
-      <c r="G22" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H22" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I22" s="88">
+      <c r="G22" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H22" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I22" s="44">
         <f t="shared" si="1"/>
         <v>157</v>
       </c>
-      <c r="J22" s="88">
+      <c r="J22" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5031,36 +5031,36 @@
       <c r="M22" s="30"/>
     </row>
     <row r="23" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A23" s="90"/>
-      <c r="B23" s="91" t="s">
+      <c r="A23" s="92"/>
+      <c r="B23" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="92">
+      <c r="D23" s="47">
         <f>'[1]1. QS, TBKT'!C36</f>
         <v>12</v>
       </c>
-      <c r="E23" s="89">
+      <c r="E23" s="45">
         <v>12</v>
       </c>
-      <c r="F23" s="89">
+      <c r="F23" s="45">
         <v>12</v>
       </c>
-      <c r="G23" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H23" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I23" s="88">
+      <c r="G23" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I23" s="44">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="J23" s="88">
+      <c r="J23" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5070,35 +5070,35 @@
     </row>
     <row r="24" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
       <c r="A24" s="93"/>
-      <c r="B24" s="91" t="s">
+      <c r="B24" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="88">
+      <c r="D24" s="44">
         <f>'[1]1. QS, TBKT'!H36</f>
         <v>822</v>
       </c>
-      <c r="E24" s="89">
+      <c r="E24" s="45">
         <v>822</v>
       </c>
-      <c r="F24" s="89">
+      <c r="F24" s="45">
         <v>822</v>
       </c>
-      <c r="G24" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H24" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I24" s="88">
+      <c r="G24" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I24" s="44">
         <f t="shared" si="1"/>
         <v>822</v>
       </c>
-      <c r="J24" s="88">
+      <c r="J24" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5107,38 +5107,38 @@
       <c r="M24" s="30"/>
     </row>
     <row r="25" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="87" t="s">
+      <c r="B25" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="88">
+      <c r="D25" s="44">
         <f>'[1]1. QS, TBKT'!M48</f>
         <v>0</v>
       </c>
-      <c r="E25" s="89">
-        <v>0</v>
-      </c>
-      <c r="F25" s="89">
-        <v>0</v>
-      </c>
-      <c r="G25" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="88">
+      <c r="E25" s="45">
+        <v>0</v>
+      </c>
+      <c r="F25" s="45">
+        <v>0</v>
+      </c>
+      <c r="G25" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5147,36 +5147,36 @@
       <c r="M25" s="30"/>
     </row>
     <row r="26" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A26" s="90"/>
-      <c r="B26" s="91" t="s">
+      <c r="A26" s="92"/>
+      <c r="B26" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="88" t="s">
+      <c r="C26" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="92">
+      <c r="D26" s="47">
         <f>'[1]1. QS, TBKT'!K48</f>
         <v>0</v>
       </c>
-      <c r="E26" s="89">
-        <v>0</v>
-      </c>
-      <c r="F26" s="89">
-        <v>0</v>
-      </c>
-      <c r="G26" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="88">
+      <c r="E26" s="45">
+        <v>0</v>
+      </c>
+      <c r="F26" s="45">
+        <v>0</v>
+      </c>
+      <c r="G26" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5185,36 +5185,36 @@
       <c r="M26" s="30"/>
     </row>
     <row r="27" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A27" s="90"/>
-      <c r="B27" s="91" t="s">
+      <c r="A27" s="92"/>
+      <c r="B27" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="92">
+      <c r="D27" s="47">
         <f>'[1]1. QS, TBKT'!J48</f>
         <v>1</v>
       </c>
-      <c r="E27" s="89">
-        <v>1</v>
-      </c>
-      <c r="F27" s="89">
-        <v>1</v>
-      </c>
-      <c r="G27" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H27" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I27" s="88">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J27" s="88">
+      <c r="E27" s="45">
+        <v>1</v>
+      </c>
+      <c r="F27" s="45">
+        <v>1</v>
+      </c>
+      <c r="G27" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H27" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I27" s="44">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5223,36 +5223,36 @@
       <c r="M27" s="30"/>
     </row>
     <row r="28" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A28" s="90"/>
-      <c r="B28" s="91" t="s">
+      <c r="A28" s="92"/>
+      <c r="B28" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="88" t="s">
+      <c r="C28" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="92">
+      <c r="D28" s="47">
         <f>'[1]1. QS, TBKT'!I48</f>
         <v>2</v>
       </c>
-      <c r="E28" s="89">
+      <c r="E28" s="45">
         <v>2</v>
       </c>
-      <c r="F28" s="89">
+      <c r="F28" s="45">
         <v>2</v>
       </c>
-      <c r="G28" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H28" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I28" s="88">
+      <c r="G28" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H28" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I28" s="44">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J28" s="88">
+      <c r="J28" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5261,36 +5261,36 @@
       <c r="M28" s="30"/>
     </row>
     <row r="29" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A29" s="90"/>
-      <c r="B29" s="91" t="s">
+      <c r="A29" s="92"/>
+      <c r="B29" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="88" t="s">
+      <c r="C29" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="92">
+      <c r="D29" s="47">
         <f>'[1]1. QS, TBKT'!L48</f>
         <v>0</v>
       </c>
-      <c r="E29" s="89">
-        <v>0</v>
-      </c>
-      <c r="F29" s="89">
-        <v>0</v>
-      </c>
-      <c r="G29" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="88">
+      <c r="E29" s="45">
+        <v>0</v>
+      </c>
+      <c r="F29" s="45">
+        <v>0</v>
+      </c>
+      <c r="G29" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5299,36 +5299,36 @@
       <c r="M29" s="30"/>
     </row>
     <row r="30" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A30" s="90"/>
-      <c r="B30" s="91" t="s">
+      <c r="A30" s="92"/>
+      <c r="B30" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="88" t="s">
+      <c r="C30" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="92">
+      <c r="D30" s="47">
         <f>'[1]1. QS, TBKT'!G48</f>
         <v>18</v>
       </c>
-      <c r="E30" s="89">
+      <c r="E30" s="45">
         <v>18</v>
       </c>
-      <c r="F30" s="89">
+      <c r="F30" s="45">
         <v>18</v>
       </c>
-      <c r="G30" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H30" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I30" s="88">
+      <c r="G30" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H30" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I30" s="44">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="J30" s="88">
+      <c r="J30" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5337,36 +5337,36 @@
       <c r="M30" s="30"/>
     </row>
     <row r="31" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A31" s="90"/>
-      <c r="B31" s="91" t="s">
+      <c r="A31" s="92"/>
+      <c r="B31" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="C31" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="92">
+      <c r="D31" s="47">
         <f>'[1]1. QS, TBKT'!F48</f>
         <v>2</v>
       </c>
-      <c r="E31" s="89">
+      <c r="E31" s="45">
         <v>2</v>
       </c>
-      <c r="F31" s="89">
+      <c r="F31" s="45">
         <v>2</v>
       </c>
-      <c r="G31" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H31" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I31" s="88">
+      <c r="G31" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H31" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I31" s="44">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J31" s="88">
+      <c r="J31" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5381,36 +5381,36 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A32" s="90"/>
-      <c r="B32" s="91" t="s">
+      <c r="A32" s="92"/>
+      <c r="B32" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="88" t="s">
+      <c r="C32" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="92">
+      <c r="D32" s="47">
         <f>'[1]1. QS, TBKT'!E48</f>
         <v>9</v>
       </c>
-      <c r="E32" s="89">
+      <c r="E32" s="45">
         <v>9</v>
       </c>
-      <c r="F32" s="89">
+      <c r="F32" s="45">
         <v>9</v>
       </c>
-      <c r="G32" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H32" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I32" s="88">
+      <c r="G32" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H32" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I32" s="44">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J32" s="88">
+      <c r="J32" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5419,36 +5419,36 @@
       <c r="M32" s="30"/>
     </row>
     <row r="33" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A33" s="90"/>
-      <c r="B33" s="91" t="s">
+      <c r="A33" s="92"/>
+      <c r="B33" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="92">
+      <c r="D33" s="47">
         <f>'[1]1. QS, TBKT'!D48</f>
         <v>75</v>
       </c>
-      <c r="E33" s="89">
+      <c r="E33" s="45">
         <v>75</v>
       </c>
-      <c r="F33" s="89">
+      <c r="F33" s="45">
         <v>75</v>
       </c>
-      <c r="G33" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H33" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I33" s="88">
+      <c r="G33" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H33" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I33" s="44">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="J33" s="88">
+      <c r="J33" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5457,36 +5457,36 @@
       <c r="M33" s="30"/>
     </row>
     <row r="34" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A34" s="90"/>
-      <c r="B34" s="91" t="s">
+      <c r="A34" s="92"/>
+      <c r="B34" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="88">
+      <c r="D34" s="44">
         <f>'[1]1. QS, TBKT'!C48</f>
         <v>4</v>
       </c>
-      <c r="E34" s="89">
+      <c r="E34" s="45">
         <v>4</v>
       </c>
-      <c r="F34" s="89">
+      <c r="F34" s="45">
         <v>4</v>
       </c>
-      <c r="G34" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H34" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I34" s="88">
+      <c r="G34" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H34" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I34" s="44">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J34" s="88">
+      <c r="J34" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5496,35 +5496,35 @@
     </row>
     <row r="35" spans="1:13" ht="18.5" thickBot="1">
       <c r="A35" s="93"/>
-      <c r="B35" s="91" t="s">
+      <c r="B35" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="88" t="s">
+      <c r="C35" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="92">
+      <c r="D35" s="47">
         <f>'[1]1. QS, TBKT'!H48</f>
         <v>390</v>
       </c>
-      <c r="E35" s="89">
+      <c r="E35" s="45">
         <v>390</v>
       </c>
-      <c r="F35" s="89">
+      <c r="F35" s="45">
         <v>390</v>
       </c>
-      <c r="G35" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H35" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I35" s="88">
+      <c r="G35" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I35" s="44">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="J35" s="88">
+      <c r="J35" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5533,38 +5533,38 @@
       <c r="M35" s="30"/>
     </row>
     <row r="36" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A36" s="86" t="s">
+      <c r="A36" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="87" t="s">
+      <c r="B36" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="88" t="s">
+      <c r="C36" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="92">
+      <c r="D36" s="47">
         <f>'[1]1. QS, TBKT'!M59</f>
         <v>0</v>
       </c>
-      <c r="E36" s="89">
-        <v>0</v>
-      </c>
-      <c r="F36" s="89">
-        <v>0</v>
-      </c>
-      <c r="G36" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="88">
+      <c r="E36" s="45">
+        <v>0</v>
+      </c>
+      <c r="F36" s="45">
+        <v>0</v>
+      </c>
+      <c r="G36" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5573,36 +5573,36 @@
       <c r="M36" s="30"/>
     </row>
     <row r="37" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A37" s="90"/>
-      <c r="B37" s="91" t="s">
+      <c r="A37" s="92"/>
+      <c r="B37" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="88" t="s">
+      <c r="C37" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="92">
+      <c r="D37" s="47">
         <f>'[1]1. QS, TBKT'!K59</f>
         <v>0</v>
       </c>
-      <c r="E37" s="89">
-        <v>0</v>
-      </c>
-      <c r="F37" s="89">
-        <v>0</v>
-      </c>
-      <c r="G37" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="88">
+      <c r="E37" s="45">
+        <v>0</v>
+      </c>
+      <c r="F37" s="45">
+        <v>0</v>
+      </c>
+      <c r="G37" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5611,36 +5611,36 @@
       <c r="M37" s="30"/>
     </row>
     <row r="38" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A38" s="90"/>
-      <c r="B38" s="91" t="s">
+      <c r="A38" s="92"/>
+      <c r="B38" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="88" t="s">
+      <c r="C38" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="92">
+      <c r="D38" s="47">
         <f>'[1]1. QS, TBKT'!J59</f>
         <v>0</v>
       </c>
-      <c r="E38" s="89">
-        <v>0</v>
-      </c>
-      <c r="F38" s="89">
-        <v>0</v>
-      </c>
-      <c r="G38" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="88">
+      <c r="E38" s="45">
+        <v>0</v>
+      </c>
+      <c r="F38" s="45">
+        <v>0</v>
+      </c>
+      <c r="G38" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5649,36 +5649,36 @@
       <c r="M38" s="30"/>
     </row>
     <row r="39" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A39" s="90"/>
-      <c r="B39" s="91" t="s">
+      <c r="A39" s="92"/>
+      <c r="B39" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="88" t="s">
+      <c r="C39" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="92">
+      <c r="D39" s="47">
         <f>'[1]1. QS, TBKT'!I59</f>
         <v>0</v>
       </c>
-      <c r="E39" s="89">
-        <v>0</v>
-      </c>
-      <c r="F39" s="89">
-        <v>0</v>
-      </c>
-      <c r="G39" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J39" s="88">
+      <c r="E39" s="45">
+        <v>0</v>
+      </c>
+      <c r="F39" s="45">
+        <v>0</v>
+      </c>
+      <c r="G39" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5687,36 +5687,36 @@
       <c r="M39" s="30"/>
     </row>
     <row r="40" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A40" s="90"/>
-      <c r="B40" s="91" t="s">
+      <c r="A40" s="92"/>
+      <c r="B40" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="88" t="s">
+      <c r="C40" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D40" s="92">
+      <c r="D40" s="47">
         <f>'[1]1. QS, TBKT'!L59</f>
         <v>0</v>
       </c>
-      <c r="E40" s="89">
-        <v>0</v>
-      </c>
-      <c r="F40" s="89">
-        <v>0</v>
-      </c>
-      <c r="G40" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="88">
+      <c r="E40" s="45">
+        <v>0</v>
+      </c>
+      <c r="F40" s="45">
+        <v>0</v>
+      </c>
+      <c r="G40" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5725,36 +5725,36 @@
       <c r="M40" s="30"/>
     </row>
     <row r="41" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
-      <c r="A41" s="90"/>
-      <c r="B41" s="91" t="s">
+      <c r="A41" s="92"/>
+      <c r="B41" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="88" t="s">
+      <c r="C41" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="88">
+      <c r="D41" s="44">
         <f>'[1]1. QS, TBKT'!G59</f>
         <v>6</v>
       </c>
-      <c r="E41" s="89">
+      <c r="E41" s="45">
         <v>6</v>
       </c>
-      <c r="F41" s="89">
+      <c r="F41" s="45">
         <v>6</v>
       </c>
-      <c r="G41" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H41" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I41" s="88">
+      <c r="G41" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H41" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I41" s="44">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J41" s="88">
+      <c r="J41" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5765,36 +5765,36 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A42" s="90"/>
-      <c r="B42" s="91" t="s">
+      <c r="A42" s="92"/>
+      <c r="B42" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="88" t="s">
+      <c r="C42" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="92">
+      <c r="D42" s="47">
         <f>'[1]1. QS, TBKT'!F59</f>
         <v>0</v>
       </c>
-      <c r="E42" s="89">
-        <v>0</v>
-      </c>
-      <c r="F42" s="89">
-        <v>0</v>
-      </c>
-      <c r="G42" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="88">
+      <c r="E42" s="45">
+        <v>0</v>
+      </c>
+      <c r="F42" s="45">
+        <v>0</v>
+      </c>
+      <c r="G42" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5803,36 +5803,36 @@
       <c r="M42" s="30"/>
     </row>
     <row r="43" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A43" s="90"/>
-      <c r="B43" s="91" t="s">
+      <c r="A43" s="92"/>
+      <c r="B43" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="C43" s="88" t="s">
+      <c r="C43" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="92">
+      <c r="D43" s="47">
         <f>'[1]1. QS, TBKT'!E59</f>
         <v>3</v>
       </c>
-      <c r="E43" s="89">
+      <c r="E43" s="45">
         <v>3</v>
       </c>
-      <c r="F43" s="89">
+      <c r="F43" s="45">
         <v>3</v>
       </c>
-      <c r="G43" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H43" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I43" s="88">
+      <c r="G43" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H43" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I43" s="44">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J43" s="88">
+      <c r="J43" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5841,36 +5841,36 @@
       <c r="M43" s="30"/>
     </row>
     <row r="44" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A44" s="90"/>
-      <c r="B44" s="91" t="s">
+      <c r="A44" s="92"/>
+      <c r="B44" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="C44" s="88" t="s">
+      <c r="C44" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D44" s="92">
+      <c r="D44" s="47">
         <f>'[1]1. QS, TBKT'!D59</f>
         <v>20</v>
       </c>
-      <c r="E44" s="89">
+      <c r="E44" s="45">
         <v>20</v>
       </c>
-      <c r="F44" s="89">
+      <c r="F44" s="45">
         <v>20</v>
       </c>
-      <c r="G44" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H44" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I44" s="88">
+      <c r="G44" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H44" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I44" s="44">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="J44" s="88">
+      <c r="J44" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5879,36 +5879,36 @@
       <c r="M44" s="30"/>
     </row>
     <row r="45" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A45" s="90"/>
-      <c r="B45" s="91" t="s">
+      <c r="A45" s="92"/>
+      <c r="B45" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="88" t="s">
+      <c r="C45" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="92">
+      <c r="D45" s="47">
         <f>'[1]1. QS, TBKT'!C59</f>
         <v>0</v>
       </c>
-      <c r="E45" s="89">
-        <v>0</v>
-      </c>
-      <c r="F45" s="89">
-        <v>0</v>
-      </c>
-      <c r="G45" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="88">
+      <c r="E45" s="45">
+        <v>0</v>
+      </c>
+      <c r="F45" s="45">
+        <v>0</v>
+      </c>
+      <c r="G45" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5917,36 +5917,36 @@
       <c r="M45" s="30"/>
     </row>
     <row r="46" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A46" s="90"/>
-      <c r="B46" s="91" t="s">
+      <c r="A46" s="92"/>
+      <c r="B46" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="88" t="s">
+      <c r="C46" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="D46" s="92">
+      <c r="D46" s="47">
         <f>'[1]1. QS, TBKT'!H59</f>
         <v>102</v>
       </c>
-      <c r="E46" s="89">
+      <c r="E46" s="45">
         <v>102</v>
       </c>
-      <c r="F46" s="89">
+      <c r="F46" s="45">
         <v>102</v>
       </c>
-      <c r="G46" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H46" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I46" s="88">
+      <c r="G46" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H46" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I46" s="44">
         <f t="shared" si="1"/>
         <v>102</v>
       </c>
-      <c r="J46" s="88">
+      <c r="J46" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5958,35 +5958,35 @@
       <c r="A47" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="87" t="s">
+      <c r="B47" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="88" t="s">
+      <c r="C47" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D47" s="92">
+      <c r="D47" s="47">
         <f>'[1]1. QS, TBKT'!M78</f>
         <v>6</v>
       </c>
-      <c r="E47" s="89">
+      <c r="E47" s="45">
         <v>6</v>
       </c>
-      <c r="F47" s="89">
+      <c r="F47" s="45">
         <v>6</v>
       </c>
-      <c r="G47" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H47" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I47" s="88">
+      <c r="G47" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H47" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I47" s="44">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J47" s="88">
+      <c r="J47" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5996,35 +5996,35 @@
     </row>
     <row r="48" spans="1:13" ht="18.5" thickBot="1">
       <c r="A48" s="96"/>
-      <c r="B48" s="91" t="s">
+      <c r="B48" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="88" t="s">
+      <c r="C48" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D48" s="92">
+      <c r="D48" s="47">
         <f>'[1]1. QS, TBKT'!K78</f>
         <v>4</v>
       </c>
-      <c r="E48" s="89">
+      <c r="E48" s="45">
         <v>4</v>
       </c>
-      <c r="F48" s="89">
+      <c r="F48" s="45">
         <v>4</v>
       </c>
-      <c r="G48" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H48" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I48" s="88">
+      <c r="G48" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H48" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I48" s="44">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J48" s="88">
+      <c r="J48" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6034,35 +6034,35 @@
     </row>
     <row r="49" spans="1:13" ht="18.5" thickBot="1">
       <c r="A49" s="96"/>
-      <c r="B49" s="91" t="s">
+      <c r="B49" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="88" t="s">
+      <c r="C49" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D49" s="92">
+      <c r="D49" s="47">
         <f>'[1]1. QS, TBKT'!J78</f>
         <v>0</v>
       </c>
-      <c r="E49" s="89">
-        <v>0</v>
-      </c>
-      <c r="F49" s="89">
-        <v>0</v>
-      </c>
-      <c r="G49" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J49" s="88">
+      <c r="E49" s="45">
+        <v>0</v>
+      </c>
+      <c r="F49" s="45">
+        <v>0</v>
+      </c>
+      <c r="G49" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6072,35 +6072,35 @@
     </row>
     <row r="50" spans="1:13" ht="18.5" thickBot="1">
       <c r="A50" s="96"/>
-      <c r="B50" s="91" t="s">
+      <c r="B50" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="88" t="s">
+      <c r="C50" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D50" s="92">
+      <c r="D50" s="47">
         <f>'[1]1. QS, TBKT'!I78</f>
         <v>0</v>
       </c>
-      <c r="E50" s="89">
-        <v>0</v>
-      </c>
-      <c r="F50" s="89">
-        <v>0</v>
-      </c>
-      <c r="G50" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="88">
+      <c r="E50" s="45">
+        <v>0</v>
+      </c>
+      <c r="F50" s="45">
+        <v>0</v>
+      </c>
+      <c r="G50" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I50" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6110,35 +6110,35 @@
     </row>
     <row r="51" spans="1:13" ht="18.5" thickBot="1">
       <c r="A51" s="96"/>
-      <c r="B51" s="91" t="s">
+      <c r="B51" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="88" t="s">
+      <c r="C51" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D51" s="92">
+      <c r="D51" s="47">
         <f>'[1]1. QS, TBKT'!L78</f>
         <v>6</v>
       </c>
-      <c r="E51" s="89">
+      <c r="E51" s="45">
         <v>6</v>
       </c>
-      <c r="F51" s="89">
+      <c r="F51" s="45">
         <v>6</v>
       </c>
-      <c r="G51" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H51" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I51" s="88">
+      <c r="G51" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H51" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I51" s="44">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J51" s="88">
+      <c r="J51" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6148,35 +6148,35 @@
     </row>
     <row r="52" spans="1:13" ht="18.5" thickBot="1">
       <c r="A52" s="96"/>
-      <c r="B52" s="91" t="s">
+      <c r="B52" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="88" t="s">
+      <c r="C52" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D52" s="92">
+      <c r="D52" s="47">
         <f>'[1]1. QS, TBKT'!G78</f>
         <v>0</v>
       </c>
-      <c r="E52" s="89">
-        <v>0</v>
-      </c>
-      <c r="F52" s="89">
-        <v>0</v>
-      </c>
-      <c r="G52" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="88">
+      <c r="E52" s="45">
+        <v>0</v>
+      </c>
+      <c r="F52" s="45">
+        <v>0</v>
+      </c>
+      <c r="G52" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6186,35 +6186,35 @@
     </row>
     <row r="53" spans="1:13" ht="18.5" thickBot="1">
       <c r="A53" s="96"/>
-      <c r="B53" s="91" t="s">
+      <c r="B53" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="88" t="s">
+      <c r="C53" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D53" s="92">
+      <c r="D53" s="47">
         <f>'[1]1. QS, TBKT'!F78</f>
         <v>0</v>
       </c>
-      <c r="E53" s="89">
-        <v>0</v>
-      </c>
-      <c r="F53" s="89">
-        <v>0</v>
-      </c>
-      <c r="G53" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="88">
+      <c r="E53" s="45">
+        <v>0</v>
+      </c>
+      <c r="F53" s="45">
+        <v>0</v>
+      </c>
+      <c r="G53" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6224,35 +6224,35 @@
     </row>
     <row r="54" spans="1:13" ht="18.5" thickBot="1">
       <c r="A54" s="96"/>
-      <c r="B54" s="91" t="s">
+      <c r="B54" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="88" t="s">
+      <c r="C54" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D54" s="92">
+      <c r="D54" s="47">
         <f>'[1]1. QS, TBKT'!E78</f>
         <v>0</v>
       </c>
-      <c r="E54" s="89">
-        <v>0</v>
-      </c>
-      <c r="F54" s="89">
-        <v>0</v>
-      </c>
-      <c r="G54" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="88">
+      <c r="E54" s="45">
+        <v>0</v>
+      </c>
+      <c r="F54" s="45">
+        <v>0</v>
+      </c>
+      <c r="G54" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6262,35 +6262,35 @@
     </row>
     <row r="55" spans="1:13" ht="18.5" thickBot="1">
       <c r="A55" s="96"/>
-      <c r="B55" s="91" t="s">
+      <c r="B55" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="88" t="s">
+      <c r="C55" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D55" s="92">
+      <c r="D55" s="47">
         <f>'[1]1. QS, TBKT'!D78</f>
         <v>187</v>
       </c>
-      <c r="E55" s="89">
+      <c r="E55" s="45">
         <v>187</v>
       </c>
-      <c r="F55" s="89">
+      <c r="F55" s="45">
         <v>187</v>
       </c>
-      <c r="G55" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H55" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I55" s="88">
+      <c r="G55" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H55" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I55" s="44">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
-      <c r="J55" s="88">
+      <c r="J55" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6300,35 +6300,35 @@
     </row>
     <row r="56" spans="1:13" ht="18.5" thickBot="1">
       <c r="A56" s="96"/>
-      <c r="B56" s="91" t="s">
+      <c r="B56" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C56" s="88" t="s">
+      <c r="C56" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D56" s="92">
+      <c r="D56" s="47">
         <f>'[1]1. QS, TBKT'!C78</f>
         <v>20</v>
       </c>
-      <c r="E56" s="89">
+      <c r="E56" s="45">
         <v>20</v>
       </c>
-      <c r="F56" s="89">
+      <c r="F56" s="45">
         <v>20</v>
       </c>
-      <c r="G56" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H56" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I56" s="88">
+      <c r="G56" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H56" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I56" s="44">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="J56" s="88">
+      <c r="J56" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6338,35 +6338,35 @@
     </row>
     <row r="57" spans="1:13" ht="18.5" thickBot="1">
       <c r="A57" s="96"/>
-      <c r="B57" s="91" t="s">
+      <c r="B57" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C57" s="88" t="s">
+      <c r="C57" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="D57" s="92">
+      <c r="D57" s="47">
         <f>'[1]1. QS, TBKT'!H78</f>
         <v>759</v>
       </c>
-      <c r="E57" s="89">
+      <c r="E57" s="45">
         <v>759</v>
       </c>
-      <c r="F57" s="89">
+      <c r="F57" s="45">
         <v>759</v>
       </c>
-      <c r="G57" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H57" s="88">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I57" s="88">
+      <c r="G57" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H57" s="44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I57" s="44">
         <f t="shared" si="1"/>
         <v>759</v>
       </c>
-      <c r="J57" s="88">
+      <c r="J57" s="44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6376,6 +6376,10 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A14:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A46"/>
+    <mergeCell ref="A47:A57"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="E1:H1"/>
@@ -6384,10 +6388,6 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A14:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A46"/>
-    <mergeCell ref="A47:A57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\Thaiha\BoDoiApp\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF55E933-7CB6-4383-92D1-7147401DA585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96BA870-04BC-43A6-8CC3-B9A92F88DA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="7" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -202,12 +213,6 @@
     <t>Loại vật chất</t>
   </si>
   <si>
-    <t>Quy định</t>
-  </si>
-  <si>
-    <t>Đạn</t>
-  </si>
-  <si>
     <t>Tấn</t>
   </si>
   <si>
@@ -218,9 +223,6 @@
   </si>
   <si>
     <t>Doanh trại</t>
-  </si>
-  <si>
-    <t>VTKT</t>
   </si>
   <si>
     <t>Cộng</t>
@@ -439,6 +441,15 @@
   </si>
   <si>
     <t>Tổ SC/e</t>
+  </si>
+  <si>
+    <t>Loại VC</t>
+  </si>
+  <si>
+    <t>Đạn, lựu đạn</t>
+  </si>
+  <si>
+    <t>Vật tư kỹ thuật</t>
   </si>
 </sst>
 </file>
@@ -889,7 +900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1036,6 +1047,33 @@
     <xf numFmtId="3" fontId="18" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1150,36 +1188,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1199,6 +1214,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Giao diện"/>
@@ -1411,9 +1427,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1451,7 +1467,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1557,7 +1573,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1699,7 +1715,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1708,79 +1724,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D56173A-C175-4526-B966-989AD58BFBEE}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="52"/>
+      <c r="A1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="61"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="55"/>
-    </row>
-    <row r="3" spans="1:13" ht="14" customHeight="1">
-      <c r="A3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="56" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="64"/>
+    </row>
+    <row r="3" spans="1:13" ht="13.95" customHeight="1">
+      <c r="A3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56" t="s">
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="I4" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1789,8 +1805,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1806,7 +1822,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="56"/>
+      <c r="H5" s="65"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1823,7 +1839,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21">
+    <row r="6" spans="1:13" ht="20.399999999999999">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1899,7 +1915,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="20.399999999999999">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1986,7 +2002,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="21">
+    <row r="11" spans="1:13" ht="20.399999999999999">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -2037,7 +2053,7 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" ht="21">
+    <row r="14" spans="1:13" ht="20.399999999999999">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -2054,7 +2070,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" ht="21">
+    <row r="15" spans="1:13" ht="20.399999999999999">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -2158,79 +2174,79 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F16AEE-EEF3-41FC-9011-B3FA05A2337A}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="52"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="61"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="55"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="64"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="56" t="s">
+      <c r="A3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56" t="s">
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="I4" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2239,8 +2255,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2256,7 +2272,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="56"/>
+      <c r="H5" s="65"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2273,7 +2289,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18">
+    <row r="6" spans="1:13" ht="19.2">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -2367,7 +2383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18">
+    <row r="8" spans="1:13" ht="19.2">
       <c r="A8" s="10" t="s">
         <v>29</v>
       </c>
@@ -2474,7 +2490,7 @@
       </c>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="18">
+    <row r="11" spans="1:13" ht="19.2">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -2734,35 +2750,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB776F58-BBC1-4BAD-8576-583DC692D30D}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="57" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="I1" s="66" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
       <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
@@ -2775,8 +2791,8 @@
       <c r="G2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
@@ -2944,90 +2960,134 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D657F165-9D3D-496E-8012-68B69501198F}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="24">
-      <c r="A1" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="25" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="97" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="97" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="97" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="97" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="25" t="s">
+      <c r="C2" s="98">
+        <v>0</v>
+      </c>
+      <c r="D2" s="98">
+        <v>0</v>
+      </c>
+      <c r="E2" s="98">
+        <f>D2-C2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B3" s="97" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="98">
+        <v>0</v>
+      </c>
+      <c r="D3" s="98">
+        <v>0</v>
+      </c>
+      <c r="E3" s="99">
+        <f>D3-C3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="26" t="s">
+      <c r="B4" s="97" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="98">
+        <v>0</v>
+      </c>
+      <c r="D4" s="98">
+        <v>0</v>
+      </c>
+      <c r="E4" s="99">
+        <f t="shared" ref="E4:E6" si="0">D4-C4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="26" t="s">
+      <c r="B5" s="97" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="98">
+        <v>0</v>
+      </c>
+      <c r="D5" s="98">
+        <v>0</v>
+      </c>
+      <c r="E5" s="99">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="97" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="98">
+        <v>0</v>
+      </c>
+      <c r="D6" s="98">
+        <v>0</v>
+      </c>
+      <c r="E6" s="99">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="B7" s="97" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="99">
+        <f>C3+C4+C5+C6+C2</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="99">
+        <f t="shared" ref="D7:E7" si="1">D3+D4+D5+D6+D2</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3037,47 +3097,47 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6AD6F2A-F3DA-482E-A27C-72512E35A6E7}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="75" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="78"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="81"/>
+      <c r="I1" s="82"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="74"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>63</v>
-      </c>
-      <c r="B1" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="66" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="68" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="73"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="65"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>66</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>46</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I2" s="28" t="s">
         <v>46</v>
@@ -3163,79 +3223,79 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90BB609-02C3-4480-ABA1-81B8EB7FC6E5}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="52"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="61"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="55"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="64"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="56" t="s">
+      <c r="A3" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56" t="s">
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="I4" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -3244,8 +3304,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3261,7 +3321,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="56"/>
+      <c r="H5" s="65"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -3278,7 +3338,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18">
+    <row r="6" spans="1:13" ht="19.2">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -3372,7 +3432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18">
+    <row r="8" spans="1:13" ht="19.2">
       <c r="A8" s="10" t="s">
         <v>29</v>
       </c>
@@ -3479,7 +3539,7 @@
       </c>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="18">
+    <row r="11" spans="1:13" ht="19.2">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -3739,105 +3799,105 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18CCF06B-A044-4E5A-A947-A016657D51E8}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="74" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="74" t="s">
+      <c r="A1" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="95"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="85" t="s">
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="96"/>
+    </row>
+    <row r="2" spans="1:13" ht="14.55" customHeight="1">
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="85" t="s">
+      <c r="D2" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="86"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="85" t="s">
+      <c r="E2" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="87"/>
-    </row>
-    <row r="2" spans="1:13" ht="14.5" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="74" t="s">
+      <c r="F2" s="83" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="74" t="s">
+      <c r="H2" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="74" t="s">
+      <c r="I2" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="74" t="s">
+      <c r="J2" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="74" t="s">
+      <c r="K2" s="87"/>
+      <c r="L2" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="M2" s="91"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="84"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="93"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="77" t="s">
+      <c r="K4" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="78"/>
-      <c r="L2" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" s="82"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="84"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="76"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="K4" s="29" t="s">
-        <v>80</v>
-      </c>
       <c r="L4" s="29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M4" s="29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3845,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C5" s="29">
         <f>SUM(C6:C12)</f>
@@ -3873,10 +3933,10 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C6" s="29">
         <v>1</v>
@@ -3897,10 +3957,10 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C7" s="29"/>
       <c r="D7" s="29">
@@ -3921,10 +3981,10 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>114</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>117</v>
       </c>
       <c r="C8" s="29"/>
       <c r="D8" s="29">
@@ -3945,10 +4005,10 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="29">
@@ -3969,10 +4029,10 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C10" s="29"/>
       <c r="D10" s="29">
@@ -3995,10 +4055,10 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C11" s="29">
         <v>1</v>
@@ -4021,10 +4081,10 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="35" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C12" s="37"/>
       <c r="D12" s="37">
@@ -4050,7 +4110,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C13" s="29">
         <f>C14+C15+C16</f>
@@ -4078,10 +4138,10 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C14" s="29"/>
       <c r="D14" s="29">
@@ -4104,10 +4164,10 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C15" s="40">
         <v>1</v>
@@ -4130,10 +4190,10 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C16" s="40"/>
       <c r="D16" s="40">
@@ -4176,78 +4236,78 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9BFD24-F416-4E13-BF3D-CA2831AC61D2}">
   <dimension ref="A1:M57"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="16.6328125" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.5" customHeight="1" thickBot="1">
-      <c r="A1" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="94" t="s">
+    <row r="1" spans="1:13" ht="15.45" customHeight="1" thickBot="1">
+      <c r="A1" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="94" t="s">
+      <c r="J1" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="94" t="s">
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="56"/>
+    </row>
+    <row r="2" spans="1:13" ht="31.8" thickBot="1">
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="42" t="s">
         <v>83</v>
-      </c>
-      <c r="E1" s="88" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="94" t="s">
-        <v>84</v>
-      </c>
-      <c r="J1" s="88" t="s">
-        <v>85</v>
-      </c>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="90"/>
-    </row>
-    <row r="2" spans="1:13" ht="30.5" thickBot="1">
-      <c r="A2" s="95"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="42" t="s">
-        <v>86</v>
       </c>
       <c r="F2" s="42" t="s">
         <v>49</v>
       </c>
       <c r="G2" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="58"/>
+      <c r="J2" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="L2" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="I2" s="95"/>
-      <c r="J2" s="42" t="s">
+      <c r="M2" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="K2" s="42" t="s">
+    </row>
+    <row r="3" spans="1:13" ht="36.450000000000003" customHeight="1" thickBot="1">
+      <c r="A3" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="42" t="s">
+      <c r="B3" s="43" t="s">
         <v>91</v>
-      </c>
-      <c r="M2" s="42" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
-      <c r="A3" s="91" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>94</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>50</v>
@@ -4282,10 +4342,10 @@
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="4" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A4" s="92"/>
+    <row r="4" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A4" s="51"/>
       <c r="B4" s="46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>50</v>
@@ -4320,10 +4380,10 @@
       <c r="L4" s="30"/>
       <c r="M4" s="30"/>
     </row>
-    <row r="5" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A5" s="92"/>
+    <row r="5" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A5" s="51"/>
       <c r="B5" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>50</v>
@@ -4358,10 +4418,10 @@
       <c r="L5" s="30"/>
       <c r="M5" s="30"/>
     </row>
-    <row r="6" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A6" s="92"/>
+    <row r="6" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A6" s="51"/>
       <c r="B6" s="46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C6" s="44" t="s">
         <v>50</v>
@@ -4396,10 +4456,10 @@
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
     </row>
-    <row r="7" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A7" s="92"/>
+    <row r="7" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A7" s="51"/>
       <c r="B7" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C7" s="44" t="s">
         <v>50</v>
@@ -4434,10 +4494,10 @@
       <c r="L7" s="30"/>
       <c r="M7" s="30"/>
     </row>
-    <row r="8" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A8" s="92"/>
+    <row r="8" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A8" s="51"/>
       <c r="B8" s="46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C8" s="44" t="s">
         <v>50</v>
@@ -4469,19 +4529,19 @@
         <v>0</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A9" s="92"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A9" s="51"/>
       <c r="B9" s="46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C9" s="44" t="s">
         <v>50</v>
@@ -4516,10 +4576,10 @@
       <c r="L9" s="30"/>
       <c r="M9" s="30"/>
     </row>
-    <row r="10" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A10" s="92"/>
+    <row r="10" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A10" s="51"/>
       <c r="B10" s="46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C10" s="44" t="s">
         <v>50</v>
@@ -4554,10 +4614,10 @@
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
     </row>
-    <row r="11" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A11" s="92"/>
+    <row r="11" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A11" s="51"/>
       <c r="B11" s="46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C11" s="44" t="s">
         <v>50</v>
@@ -4589,19 +4649,19 @@
         <v>0</v>
       </c>
       <c r="K11" s="30" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L11" s="30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M11" s="30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A12" s="92"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A12" s="51"/>
       <c r="B12" s="46" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C12" s="44" t="s">
         <v>50</v>
@@ -4636,13 +4696,13 @@
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
     </row>
-    <row r="13" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A13" s="93"/>
+    <row r="13" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A13" s="52"/>
       <c r="B13" s="46" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D13" s="48">
         <f>'[1]1. QS, TBKT'!H19</f>
@@ -4674,12 +4734,12 @@
       <c r="L13" s="30"/>
       <c r="M13" s="30"/>
     </row>
-    <row r="14" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
-      <c r="A14" s="91" t="s">
-        <v>105</v>
+    <row r="14" spans="1:13" ht="36.450000000000003" customHeight="1" thickBot="1">
+      <c r="A14" s="50" t="s">
+        <v>102</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C14" s="44" t="s">
         <v>50</v>
@@ -4714,10 +4774,10 @@
       <c r="L14" s="30"/>
       <c r="M14" s="30"/>
     </row>
-    <row r="15" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A15" s="92"/>
+    <row r="15" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A15" s="51"/>
       <c r="B15" s="46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C15" s="44" t="s">
         <v>50</v>
@@ -4752,10 +4812,10 @@
       <c r="L15" s="30"/>
       <c r="M15" s="30"/>
     </row>
-    <row r="16" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A16" s="92"/>
+    <row r="16" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A16" s="51"/>
       <c r="B16" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C16" s="44" t="s">
         <v>50</v>
@@ -4790,10 +4850,10 @@
       <c r="L16" s="30"/>
       <c r="M16" s="30"/>
     </row>
-    <row r="17" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A17" s="92"/>
+    <row r="17" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A17" s="51"/>
       <c r="B17" s="46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>50</v>
@@ -4828,10 +4888,10 @@
       <c r="L17" s="30"/>
       <c r="M17" s="30"/>
     </row>
-    <row r="18" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A18" s="92"/>
+    <row r="18" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A18" s="51"/>
       <c r="B18" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>50</v>
@@ -4863,19 +4923,19 @@
         <v>0</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L18" s="30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M18" s="30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A19" s="92"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A19" s="51"/>
       <c r="B19" s="46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C19" s="44" t="s">
         <v>50</v>
@@ -4910,10 +4970,10 @@
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
     </row>
-    <row r="20" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A20" s="92"/>
+    <row r="20" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A20" s="51"/>
       <c r="B20" s="46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C20" s="44" t="s">
         <v>50</v>
@@ -4948,10 +5008,10 @@
       <c r="L20" s="30"/>
       <c r="M20" s="30"/>
     </row>
-    <row r="21" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A21" s="92"/>
+    <row r="21" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A21" s="51"/>
       <c r="B21" s="46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C21" s="44" t="s">
         <v>50</v>
@@ -4983,19 +5043,19 @@
         <v>0</v>
       </c>
       <c r="K21" s="30" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L21" s="30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M21" s="30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A22" s="92"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A22" s="51"/>
       <c r="B22" s="46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C22" s="44" t="s">
         <v>50</v>
@@ -5030,10 +5090,10 @@
       <c r="L22" s="30"/>
       <c r="M22" s="30"/>
     </row>
-    <row r="23" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A23" s="92"/>
+    <row r="23" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A23" s="51"/>
       <c r="B23" s="46" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C23" s="44" t="s">
         <v>50</v>
@@ -5068,13 +5128,13 @@
       <c r="L23" s="30"/>
       <c r="M23" s="30"/>
     </row>
-    <row r="24" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
-      <c r="A24" s="93"/>
+    <row r="24" spans="1:13" ht="36.450000000000003" customHeight="1" thickBot="1">
+      <c r="A24" s="52"/>
       <c r="B24" s="46" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D24" s="44">
         <f>'[1]1. QS, TBKT'!H36</f>
@@ -5106,12 +5166,12 @@
       <c r="L24" s="30"/>
       <c r="M24" s="30"/>
     </row>
-    <row r="25" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A25" s="91" t="s">
-        <v>106</v>
+    <row r="25" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A25" s="50" t="s">
+        <v>103</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C25" s="44" t="s">
         <v>50</v>
@@ -5146,10 +5206,10 @@
       <c r="L25" s="30"/>
       <c r="M25" s="30"/>
     </row>
-    <row r="26" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A26" s="92"/>
+    <row r="26" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A26" s="51"/>
       <c r="B26" s="46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C26" s="44" t="s">
         <v>50</v>
@@ -5184,10 +5244,10 @@
       <c r="L26" s="30"/>
       <c r="M26" s="30"/>
     </row>
-    <row r="27" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A27" s="92"/>
+    <row r="27" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A27" s="51"/>
       <c r="B27" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C27" s="44" t="s">
         <v>50</v>
@@ -5222,10 +5282,10 @@
       <c r="L27" s="30"/>
       <c r="M27" s="30"/>
     </row>
-    <row r="28" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A28" s="92"/>
+    <row r="28" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A28" s="51"/>
       <c r="B28" s="46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C28" s="44" t="s">
         <v>50</v>
@@ -5260,10 +5320,10 @@
       <c r="L28" s="30"/>
       <c r="M28" s="30"/>
     </row>
-    <row r="29" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A29" s="92"/>
+    <row r="29" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A29" s="51"/>
       <c r="B29" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C29" s="44" t="s">
         <v>50</v>
@@ -5298,10 +5358,10 @@
       <c r="L29" s="30"/>
       <c r="M29" s="30"/>
     </row>
-    <row r="30" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A30" s="92"/>
+    <row r="30" spans="1:13" ht="18.45" customHeight="1" thickBot="1">
+      <c r="A30" s="51"/>
       <c r="B30" s="46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C30" s="44" t="s">
         <v>50</v>
@@ -5336,10 +5396,10 @@
       <c r="L30" s="30"/>
       <c r="M30" s="30"/>
     </row>
-    <row r="31" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A31" s="92"/>
+    <row r="31" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A31" s="51"/>
       <c r="B31" s="46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C31" s="44" t="s">
         <v>50</v>
@@ -5371,19 +5431,19 @@
         <v>0</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L31" s="30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M31" s="30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A32" s="92"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A32" s="51"/>
       <c r="B32" s="46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C32" s="44" t="s">
         <v>50</v>
@@ -5418,13 +5478,13 @@
       <c r="L32" s="30"/>
       <c r="M32" s="30"/>
     </row>
-    <row r="33" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A33" s="92"/>
+    <row r="33" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A33" s="51"/>
       <c r="B33" s="46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C33" s="44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D33" s="47">
         <f>'[1]1. QS, TBKT'!D48</f>
@@ -5456,10 +5516,10 @@
       <c r="L33" s="30"/>
       <c r="M33" s="30"/>
     </row>
-    <row r="34" spans="1:13" ht="18.5" customHeight="1" thickBot="1">
-      <c r="A34" s="92"/>
+    <row r="34" spans="1:13" ht="18.45" customHeight="1" thickBot="1">
+      <c r="A34" s="51"/>
       <c r="B34" s="46" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C34" s="44" t="s">
         <v>50</v>
@@ -5494,8 +5554,8 @@
       <c r="L34" s="30"/>
       <c r="M34" s="30"/>
     </row>
-    <row r="35" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A35" s="93"/>
+    <row r="35" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A35" s="52"/>
       <c r="B35" s="46" t="s">
         <v>5</v>
       </c>
@@ -5532,12 +5592,12 @@
       <c r="L35" s="30"/>
       <c r="M35" s="30"/>
     </row>
-    <row r="36" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A36" s="91" t="s">
-        <v>107</v>
+    <row r="36" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A36" s="50" t="s">
+        <v>104</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C36" s="44" t="s">
         <v>50</v>
@@ -5572,10 +5632,10 @@
       <c r="L36" s="30"/>
       <c r="M36" s="30"/>
     </row>
-    <row r="37" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A37" s="92"/>
+    <row r="37" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A37" s="51"/>
       <c r="B37" s="46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C37" s="44" t="s">
         <v>50</v>
@@ -5610,10 +5670,10 @@
       <c r="L37" s="30"/>
       <c r="M37" s="30"/>
     </row>
-    <row r="38" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A38" s="92"/>
+    <row r="38" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A38" s="51"/>
       <c r="B38" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C38" s="44" t="s">
         <v>50</v>
@@ -5648,10 +5708,10 @@
       <c r="L38" s="30"/>
       <c r="M38" s="30"/>
     </row>
-    <row r="39" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A39" s="92"/>
+    <row r="39" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A39" s="51"/>
       <c r="B39" s="46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C39" s="44" t="s">
         <v>50</v>
@@ -5686,10 +5746,10 @@
       <c r="L39" s="30"/>
       <c r="M39" s="30"/>
     </row>
-    <row r="40" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A40" s="92"/>
+    <row r="40" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A40" s="51"/>
       <c r="B40" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C40" s="44" t="s">
         <v>50</v>
@@ -5724,10 +5784,10 @@
       <c r="L40" s="30"/>
       <c r="M40" s="30"/>
     </row>
-    <row r="41" spans="1:13" ht="36.5" customHeight="1" thickBot="1">
-      <c r="A41" s="92"/>
+    <row r="41" spans="1:13" ht="36.450000000000003" customHeight="1" thickBot="1">
+      <c r="A41" s="51"/>
       <c r="B41" s="46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C41" s="44" t="s">
         <v>50</v>
@@ -5761,13 +5821,13 @@
       <c r="K41" s="30"/>
       <c r="L41" s="30"/>
       <c r="M41" s="30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A42" s="92"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A42" s="51"/>
       <c r="B42" s="46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C42" s="44" t="s">
         <v>50</v>
@@ -5802,10 +5862,10 @@
       <c r="L42" s="30"/>
       <c r="M42" s="30"/>
     </row>
-    <row r="43" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A43" s="92"/>
+    <row r="43" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A43" s="51"/>
       <c r="B43" s="46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C43" s="44" t="s">
         <v>50</v>
@@ -5840,10 +5900,10 @@
       <c r="L43" s="30"/>
       <c r="M43" s="30"/>
     </row>
-    <row r="44" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A44" s="92"/>
+    <row r="44" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A44" s="51"/>
       <c r="B44" s="46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C44" s="44" t="s">
         <v>50</v>
@@ -5878,10 +5938,10 @@
       <c r="L44" s="30"/>
       <c r="M44" s="30"/>
     </row>
-    <row r="45" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A45" s="92"/>
+    <row r="45" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A45" s="51"/>
       <c r="B45" s="46" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C45" s="44" t="s">
         <v>50</v>
@@ -5916,13 +5976,13 @@
       <c r="L45" s="30"/>
       <c r="M45" s="30"/>
     </row>
-    <row r="46" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A46" s="92"/>
+    <row r="46" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A46" s="51"/>
       <c r="B46" s="46" t="s">
         <v>5</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D46" s="47">
         <f>'[1]1. QS, TBKT'!H59</f>
@@ -5954,12 +6014,12 @@
       <c r="L46" s="30"/>
       <c r="M46" s="30"/>
     </row>
-    <row r="47" spans="1:13" ht="36.5" thickBot="1">
-      <c r="A47" s="96" t="s">
-        <v>108</v>
+    <row r="47" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A47" s="53" t="s">
+        <v>105</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C47" s="44" t="s">
         <v>50</v>
@@ -5994,10 +6054,10 @@
       <c r="L47" s="30"/>
       <c r="M47" s="30"/>
     </row>
-    <row r="48" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A48" s="96"/>
+    <row r="48" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A48" s="53"/>
       <c r="B48" s="46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C48" s="44" t="s">
         <v>50</v>
@@ -6032,10 +6092,10 @@
       <c r="L48" s="30"/>
       <c r="M48" s="30"/>
     </row>
-    <row r="49" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A49" s="96"/>
+    <row r="49" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A49" s="53"/>
       <c r="B49" s="46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C49" s="44" t="s">
         <v>50</v>
@@ -6070,10 +6130,10 @@
       <c r="L49" s="30"/>
       <c r="M49" s="30"/>
     </row>
-    <row r="50" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A50" s="96"/>
+    <row r="50" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A50" s="53"/>
       <c r="B50" s="46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>50</v>
@@ -6108,10 +6168,10 @@
       <c r="L50" s="30"/>
       <c r="M50" s="30"/>
     </row>
-    <row r="51" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A51" s="96"/>
+    <row r="51" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A51" s="53"/>
       <c r="B51" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C51" s="44" t="s">
         <v>50</v>
@@ -6146,10 +6206,10 @@
       <c r="L51" s="30"/>
       <c r="M51" s="30"/>
     </row>
-    <row r="52" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A52" s="96"/>
+    <row r="52" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A52" s="53"/>
       <c r="B52" s="46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C52" s="44" t="s">
         <v>50</v>
@@ -6184,10 +6244,10 @@
       <c r="L52" s="30"/>
       <c r="M52" s="30"/>
     </row>
-    <row r="53" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A53" s="96"/>
+    <row r="53" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A53" s="53"/>
       <c r="B53" s="46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C53" s="44" t="s">
         <v>50</v>
@@ -6222,10 +6282,10 @@
       <c r="L53" s="30"/>
       <c r="M53" s="30"/>
     </row>
-    <row r="54" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A54" s="96"/>
+    <row r="54" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A54" s="53"/>
       <c r="B54" s="46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C54" s="44" t="s">
         <v>50</v>
@@ -6260,10 +6320,10 @@
       <c r="L54" s="30"/>
       <c r="M54" s="30"/>
     </row>
-    <row r="55" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A55" s="96"/>
+    <row r="55" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A55" s="53"/>
       <c r="B55" s="46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C55" s="44" t="s">
         <v>50</v>
@@ -6298,10 +6358,10 @@
       <c r="L55" s="30"/>
       <c r="M55" s="30"/>
     </row>
-    <row r="56" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A56" s="96"/>
+    <row r="56" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A56" s="53"/>
       <c r="B56" s="46" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C56" s="44" t="s">
         <v>50</v>
@@ -6336,13 +6396,13 @@
       <c r="L56" s="30"/>
       <c r="M56" s="30"/>
     </row>
-    <row r="57" spans="1:13" ht="18.5" thickBot="1">
-      <c r="A57" s="96"/>
+    <row r="57" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A57" s="53"/>
       <c r="B57" s="46" t="s">
         <v>5</v>
       </c>
       <c r="C57" s="44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D57" s="47">
         <f>'[1]1. QS, TBKT'!H78</f>

--- a/Resources/Sheet/Book1.xlsx
+++ b/Resources/Sheet/Book1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Debug (1)\Debug\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8A5611-4765-4084-848A-C83EEDCCE4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355C0D32-4C26-4F00-BA70-63B2203C3CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="6" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FCE59EA9-790B-433B-B511-234C9C16BD72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="126">
   <si>
     <t>TỔ CHỨC BIÊN CHẾ, TRANG BỊ HƯỚNG CHỦ YẾU</t>
   </si>
@@ -324,13 +325,135 @@
   </si>
   <si>
     <t>Vật tư kỹ thuật</t>
+  </si>
+  <si>
+    <t>Tên TBKT</t>
+  </si>
+  <si>
+    <t>Đơn vị tính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhu cầu </t>
+  </si>
+  <si>
+    <t>Phải có trước CĐ</t>
+  </si>
+  <si>
+    <t>Phải bổ sung</t>
+  </si>
+  <si>
+    <t>Tổng số</t>
+  </si>
+  <si>
+    <r>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>bđ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>t</t>
+    </r>
+  </si>
+  <si>
+    <t>Số lượng</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
+  </si>
+  <si>
+    <t>Địa điểm</t>
+  </si>
+  <si>
+    <t>Phương thức</t>
+  </si>
+  <si>
+    <t>dBB1+PT</t>
+  </si>
+  <si>
+    <t>SMPK 12,7mm</t>
+  </si>
+  <si>
+    <t>Cối 100mm/e</t>
+  </si>
+  <si>
+    <t>Cối 82mm/d</t>
+  </si>
+  <si>
+    <t>Cối 60mm</t>
+  </si>
+  <si>
+    <t>Súng SPG-9</t>
+  </si>
+  <si>
+    <t>Súng B41</t>
+  </si>
+  <si>
+    <t>14.00 N-4</t>
+  </si>
+  <si>
+    <t>VTCH/đv</t>
+  </si>
+  <si>
+    <t>Tay ba</t>
+  </si>
+  <si>
+    <t>Súng đại liên</t>
+  </si>
+  <si>
+    <t>Súng trung liên</t>
+  </si>
+  <si>
+    <t>Súng tiểu liên</t>
+  </si>
+  <si>
+    <t>Súng ngắn</t>
+  </si>
+  <si>
+    <t>quả</t>
+  </si>
+  <si>
+    <t>Hướng PN chủ yếu</t>
+  </si>
+  <si>
+    <t>Hướng PN thứ yếu</t>
+  </si>
+  <si>
+    <t>Hướng PN phía sau</t>
+  </si>
+  <si>
+    <t>  </t>
+  </si>
+  <si>
+    <t>Lực lượng còn lại</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +570,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -498,7 +649,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -657,11 +808,96 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -785,6 +1021,60 @@
     <xf numFmtId="4" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -806,27 +1096,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -899,9 +1168,21 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -917,7 +1198,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1214,79 +1495,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D56173A-C175-4526-B966-989AD58BFBEE}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="47"/>
+      <c r="A1" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="65"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="50"/>
-    </row>
-    <row r="3" spans="1:13" ht="13.9" customHeight="1">
-      <c r="A3" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="51" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
+    </row>
+    <row r="3" spans="1:13" ht="13.95" customHeight="1">
+      <c r="A3" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51" t="s">
+      <c r="A4" s="69"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51" t="s">
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1295,8 +1576,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
+      <c r="A5" s="69"/>
+      <c r="B5" s="69"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1312,7 +1593,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="51"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1329,7 +1610,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21">
+    <row r="6" spans="1:13" ht="20.399999999999999">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1405,7 +1686,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="20.399999999999999">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1492,7 +1773,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="22.5">
+    <row r="11" spans="1:13" ht="20.399999999999999">
       <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
@@ -1543,7 +1824,7 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" ht="22.5">
+    <row r="14" spans="1:13" ht="20.399999999999999">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -1560,7 +1841,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" ht="33.75">
+    <row r="15" spans="1:13" ht="20.399999999999999">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -1664,79 +1945,79 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F16AEE-EEF3-41FC-9011-B3FA05A2337A}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="47"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="65"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="50"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="51" t="s">
+      <c r="A3" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51" t="s">
+      <c r="A4" s="69"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51" t="s">
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1745,8 +2026,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
+      <c r="A5" s="69"/>
+      <c r="B5" s="69"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1762,7 +2043,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="51"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -1779,7 +2060,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21">
+    <row r="6" spans="1:13" ht="19.2">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -1873,7 +2154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="19.2">
       <c r="A8" s="10" t="s">
         <v>29</v>
       </c>
@@ -1980,7 +2261,7 @@
       </c>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="21">
+    <row r="11" spans="1:13" ht="19.2">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -2239,36 +2520,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB776F58-BBC1-4BAD-8576-583DC692D30D}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="52" t="s">
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="95" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
       <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
@@ -2281,8 +2565,8 @@
       <c r="G2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="23" t="s">
@@ -2291,15 +2575,13 @@
       <c r="B3" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="23">
-        <v>36</v>
-      </c>
+      <c r="C3" s="23"/>
       <c r="D3" s="24">
         <v>35</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="23" t="e">
         <f>D3/C3</f>
-        <v>0.97222222222222221</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F3" s="23">
         <f>G3/D3</f>
@@ -2311,7 +2593,7 @@
       <c r="H3" s="24"/>
       <c r="I3" s="23">
         <f>C3-D3</f>
-        <v>1</v>
+        <v>-35</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2321,18 +2603,16 @@
       <c r="B4" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="23">
-        <v>439</v>
-      </c>
+      <c r="C4" s="23"/>
       <c r="D4" s="24">
         <v>439</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="23" t="e">
         <f>D4/C4</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F4" s="23">
-        <f t="shared" ref="F4:F7" si="0">G4/D4</f>
+        <f t="shared" ref="F4:F13" si="0">G4/D4</f>
         <v>0.99772209567198178</v>
       </c>
       <c r="G4" s="24">
@@ -2341,7 +2621,7 @@
       <c r="H4" s="24"/>
       <c r="I4" s="23">
         <f>C4-D4</f>
-        <v>0</v>
+        <v>-439</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2351,15 +2631,13 @@
       <c r="B5" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="23">
-        <v>27</v>
-      </c>
+      <c r="C5" s="23"/>
       <c r="D5" s="24">
         <v>27</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="23" t="e">
         <f>D5/C5</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F5" s="23">
         <f t="shared" si="0"/>
@@ -2370,8 +2648,8 @@
       </c>
       <c r="H5" s="24"/>
       <c r="I5" s="23">
-        <f t="shared" ref="I5:I7" si="1">C5-D5</f>
-        <v>0</v>
+        <f t="shared" ref="I5:I13" si="1">C5-D5</f>
+        <v>-27</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2381,15 +2659,13 @@
       <c r="B6" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="23">
-        <v>6</v>
-      </c>
+      <c r="C6" s="23"/>
       <c r="D6" s="24">
         <v>6</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="23" t="e">
         <f>D6/C6</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F6" s="23">
         <f t="shared" si="0"/>
@@ -2401,7 +2677,7 @@
       <c r="H6" s="24"/>
       <c r="I6" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2411,15 +2687,13 @@
       <c r="B7" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="23">
-        <v>2073</v>
-      </c>
+      <c r="C7" s="23"/>
       <c r="D7" s="24">
         <v>2073</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="23" t="e">
         <f>D7/C7</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="F7" s="23">
         <f t="shared" si="0"/>
@@ -2431,7 +2705,175 @@
       <c r="H7" s="24"/>
       <c r="I7" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2073</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="96" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E8" s="23" t="e">
+        <f t="shared" ref="E8:E13" si="2">D8/C8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F8" s="23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="24">
+        <v>2073</v>
+      </c>
+      <c r="H8" s="30"/>
+      <c r="I8" s="23">
+        <f t="shared" si="1"/>
+        <v>-2073</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="97" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E9" s="23" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F9" s="23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="24">
+        <v>2073</v>
+      </c>
+      <c r="H9" s="30"/>
+      <c r="I9" s="23">
+        <f t="shared" si="1"/>
+        <v>-2073</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E10" s="23" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F10" s="23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="24">
+        <v>2073</v>
+      </c>
+      <c r="H10" s="30"/>
+      <c r="I10" s="23">
+        <f t="shared" si="1"/>
+        <v>-2073</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E11" s="23" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F11" s="23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="24">
+        <v>2073</v>
+      </c>
+      <c r="H11" s="30"/>
+      <c r="I11" s="23">
+        <f t="shared" si="1"/>
+        <v>-2073</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="97" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="23"/>
+      <c r="D12" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E12" s="23" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F12" s="23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="24">
+        <v>2073</v>
+      </c>
+      <c r="H12" s="30"/>
+      <c r="I12" s="23">
+        <f t="shared" si="1"/>
+        <v>-2073</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="97" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="24">
+        <v>2073</v>
+      </c>
+      <c r="E13" s="23" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F13" s="23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G13" s="24">
+        <v>2073</v>
+      </c>
+      <c r="H13" s="30"/>
+      <c r="I13" s="23">
+        <f t="shared" si="1"/>
+        <v>-2073</v>
       </c>
     </row>
   </sheetData>
@@ -2450,7 +2892,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D657F165-9D3D-496E-8012-68B69501198F}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="41" t="s">
@@ -2587,33 +3029,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6AD6F2A-F3DA-482E-A27C-72512E35A6E7}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="66" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="67"/>
-      <c r="I1" s="68"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="60"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
+      <c r="A2" s="71"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
       <c r="D2" s="26" t="s">
         <v>62</v>
       </c>
@@ -2713,79 +3155,79 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90BB609-02C3-4480-ABA1-81B8EB7FC6E5}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="47"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="65"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="50"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="68"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="51" t="s">
+      <c r="A3" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51" t="s">
+      <c r="A4" s="69"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51" t="s">
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
       <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2794,8 +3236,8 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
+      <c r="A5" s="69"/>
+      <c r="B5" s="69"/>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2811,7 +3253,7 @@
       <c r="G5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="51"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="1">
         <v>60</v>
       </c>
@@ -2828,7 +3270,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21">
+    <row r="6" spans="1:13" ht="19.2">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -2922,7 +3364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21">
+    <row r="8" spans="1:13" ht="19.2">
       <c r="A8" s="10" t="s">
         <v>29</v>
       </c>
@@ -3029,7 +3471,7 @@
       </c>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="21">
+    <row r="11" spans="1:13" ht="19.2">
       <c r="A11" s="12" t="s">
         <v>32</v>
       </c>
@@ -3289,94 +3731,94 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18CCF06B-A044-4E5A-A947-A016657D51E8}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C1" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="80" t="s">
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="81"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="80" t="s">
+      <c r="H1" s="92"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="82"/>
-    </row>
-    <row r="2" spans="1:13" ht="14.65" customHeight="1">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="69" t="s">
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="93"/>
+    </row>
+    <row r="2" spans="1:13" ht="14.7" customHeight="1">
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="69" t="s">
+      <c r="F2" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="69" t="s">
+      <c r="G2" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="69" t="s">
+      <c r="H2" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="72" t="s">
+      <c r="J2" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="73"/>
-      <c r="L2" s="76" t="s">
+      <c r="K2" s="84"/>
+      <c r="L2" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="77"/>
+      <c r="M2" s="88"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="79"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="90"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="71"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
       <c r="J4" s="29" t="s">
         <v>76</v>
       </c>
@@ -3721,4 +4163,2069 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBBAE9D4-FB38-46C6-8D37-C5F70CA4A32D}">
+  <dimension ref="A1:M57"/>
+  <sheetFormatPr defaultColWidth="7.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" customWidth="1"/>
+    <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="16.2" thickBot="1">
+      <c r="A1" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="56"/>
+    </row>
+    <row r="2" spans="1:13" ht="31.8" thickBot="1">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="61"/>
+      <c r="J2" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="L2" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A3" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48">
+        <v>0</v>
+      </c>
+      <c r="F3" s="48">
+        <v>0</v>
+      </c>
+      <c r="G3" s="47" t="str">
+        <f>IF(OR(D3=0,E3=0),"-",E3/D3)</f>
+        <v>-</v>
+      </c>
+      <c r="H3" s="47" t="str">
+        <f>IF(OR(E3=0, F3=0),"-",F3/E3)</f>
+        <v>-</v>
+      </c>
+      <c r="I3" s="47">
+        <f>D3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="47">
+        <f>D3-E3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+    </row>
+    <row r="4" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A4" s="58"/>
+      <c r="B4" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="48">
+        <v>4</v>
+      </c>
+      <c r="F4" s="48">
+        <v>4</v>
+      </c>
+      <c r="G4" s="47" t="str">
+        <f t="shared" ref="G4:G57" si="0">IF(OR(D4=0,E4=0),"-",E4/D4)</f>
+        <v>-</v>
+      </c>
+      <c r="H4" s="47">
+        <f t="shared" ref="H4:H57" si="1">IF(OR(E4=0, F4=0),"-",F4/E4)</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="47">
+        <f t="shared" ref="I4:I57" si="2">D4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="47">
+        <f t="shared" ref="J4:J57" si="3">D4-E4</f>
+        <v>-4</v>
+      </c>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+    </row>
+    <row r="5" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A5" s="58"/>
+      <c r="B5" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="51"/>
+      <c r="E5" s="48">
+        <v>4</v>
+      </c>
+      <c r="F5" s="48">
+        <v>4</v>
+      </c>
+      <c r="G5" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H5" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I5" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="47">
+        <f>D5-E5</f>
+        <v>-4</v>
+      </c>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+    </row>
+    <row r="6" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A6" s="58"/>
+      <c r="B6" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="51"/>
+      <c r="E6" s="48">
+        <v>6</v>
+      </c>
+      <c r="F6" s="48">
+        <v>6</v>
+      </c>
+      <c r="G6" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H6" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="47">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+    </row>
+    <row r="7" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A7" s="58"/>
+      <c r="B7" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="51"/>
+      <c r="E7" s="48">
+        <v>9</v>
+      </c>
+      <c r="F7" s="48">
+        <v>9</v>
+      </c>
+      <c r="G7" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H7" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="47">
+        <f t="shared" si="3"/>
+        <v>-9</v>
+      </c>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+    </row>
+    <row r="8" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A8" s="58"/>
+      <c r="B8" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="51"/>
+      <c r="E8" s="48">
+        <v>54</v>
+      </c>
+      <c r="F8" s="48">
+        <v>54</v>
+      </c>
+      <c r="G8" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H8" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="47">
+        <f t="shared" si="3"/>
+        <v>-54</v>
+      </c>
+      <c r="K8" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="L8" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="M8" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A9" s="58"/>
+      <c r="B9" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="51"/>
+      <c r="E9" s="48">
+        <v>6</v>
+      </c>
+      <c r="F9" s="48">
+        <v>6</v>
+      </c>
+      <c r="G9" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H9" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="47">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+    </row>
+    <row r="10" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A10" s="58"/>
+      <c r="B10" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="51"/>
+      <c r="E10" s="48">
+        <v>27</v>
+      </c>
+      <c r="F10" s="48">
+        <v>27</v>
+      </c>
+      <c r="G10" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H10" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I10" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="47">
+        <f t="shared" si="3"/>
+        <v>-27</v>
+      </c>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+    </row>
+    <row r="11" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A11" s="58"/>
+      <c r="B11" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="51"/>
+      <c r="E11" s="48">
+        <v>439</v>
+      </c>
+      <c r="F11" s="48">
+        <v>439</v>
+      </c>
+      <c r="G11" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H11" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="47">
+        <f t="shared" si="3"/>
+        <v>-439</v>
+      </c>
+      <c r="K11" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="M11" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A12" s="58"/>
+      <c r="B12" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="48">
+        <v>36</v>
+      </c>
+      <c r="F12" s="48">
+        <v>36</v>
+      </c>
+      <c r="G12" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H12" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="47">
+        <f t="shared" si="3"/>
+        <v>-36</v>
+      </c>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+    </row>
+    <row r="13" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A13" s="59"/>
+      <c r="B13" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="52"/>
+      <c r="E13" s="53">
+        <v>2073</v>
+      </c>
+      <c r="F13" s="53">
+        <v>2073</v>
+      </c>
+      <c r="G13" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H13" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="47">
+        <f t="shared" si="3"/>
+        <v>-2073</v>
+      </c>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+    </row>
+    <row r="14" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A14" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="47"/>
+      <c r="E14" s="48">
+        <v>3</v>
+      </c>
+      <c r="F14" s="48">
+        <v>3</v>
+      </c>
+      <c r="G14" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H14" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="47">
+        <f t="shared" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+    </row>
+    <row r="15" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A15" s="58"/>
+      <c r="B15" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="48">
+        <v>0</v>
+      </c>
+      <c r="F15" s="48">
+        <v>0</v>
+      </c>
+      <c r="G15" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H15" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I15" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+    </row>
+    <row r="16" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A16" s="58"/>
+      <c r="B16" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="51"/>
+      <c r="E16" s="48">
+        <v>3</v>
+      </c>
+      <c r="F16" s="48">
+        <v>3</v>
+      </c>
+      <c r="G16" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H16" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I16" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="47">
+        <f t="shared" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+    </row>
+    <row r="17" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A17" s="58"/>
+      <c r="B17" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="51"/>
+      <c r="E17" s="48">
+        <v>4</v>
+      </c>
+      <c r="F17" s="48">
+        <v>4</v>
+      </c>
+      <c r="G17" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H17" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I17" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="47">
+        <f t="shared" si="3"/>
+        <v>-4</v>
+      </c>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+    </row>
+    <row r="18" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A18" s="58"/>
+      <c r="B18" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="51"/>
+      <c r="E18" s="48">
+        <v>3</v>
+      </c>
+      <c r="F18" s="48">
+        <v>3</v>
+      </c>
+      <c r="G18" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H18" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I18" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="47">
+        <f t="shared" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="K18" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="L18" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="M18" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A19" s="58"/>
+      <c r="B19" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="48">
+        <v>30</v>
+      </c>
+      <c r="F19" s="48">
+        <v>30</v>
+      </c>
+      <c r="G19" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H19" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="47">
+        <f t="shared" si="3"/>
+        <v>-30</v>
+      </c>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+    </row>
+    <row r="20" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A20" s="58"/>
+      <c r="B20" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="51"/>
+      <c r="E20" s="48">
+        <v>4</v>
+      </c>
+      <c r="F20" s="48">
+        <v>4</v>
+      </c>
+      <c r="G20" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H20" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I20" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="47">
+        <f t="shared" si="3"/>
+        <v>-4</v>
+      </c>
+      <c r="K20" s="49"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="49"/>
+    </row>
+    <row r="21" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A21" s="58"/>
+      <c r="B21" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="51"/>
+      <c r="E21" s="48">
+        <v>15</v>
+      </c>
+      <c r="F21" s="48">
+        <v>15</v>
+      </c>
+      <c r="G21" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H21" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I21" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="47">
+        <f t="shared" si="3"/>
+        <v>-15</v>
+      </c>
+      <c r="K21" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="L21" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="M21" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A22" s="58"/>
+      <c r="B22" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="51"/>
+      <c r="E22" s="48">
+        <v>157</v>
+      </c>
+      <c r="F22" s="48">
+        <v>157</v>
+      </c>
+      <c r="G22" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H22" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I22" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="47">
+        <f t="shared" si="3"/>
+        <v>-157</v>
+      </c>
+      <c r="K22" s="49"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="49"/>
+    </row>
+    <row r="23" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A23" s="58"/>
+      <c r="B23" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="51"/>
+      <c r="E23" s="48">
+        <v>12</v>
+      </c>
+      <c r="F23" s="48">
+        <v>12</v>
+      </c>
+      <c r="G23" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H23" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I23" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="47">
+        <f t="shared" si="3"/>
+        <v>-12</v>
+      </c>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+    </row>
+    <row r="24" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A24" s="59"/>
+      <c r="B24" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="47"/>
+      <c r="E24" s="48">
+        <v>822</v>
+      </c>
+      <c r="F24" s="48">
+        <v>822</v>
+      </c>
+      <c r="G24" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H24" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I24" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="47">
+        <f t="shared" si="3"/>
+        <v>-822</v>
+      </c>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+    </row>
+    <row r="25" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A25" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="47"/>
+      <c r="E25" s="48">
+        <v>0</v>
+      </c>
+      <c r="F25" s="48">
+        <v>0</v>
+      </c>
+      <c r="G25" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H25" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I25" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="49"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49"/>
+    </row>
+    <row r="26" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A26" s="58"/>
+      <c r="B26" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="48">
+        <v>0</v>
+      </c>
+      <c r="F26" s="48">
+        <v>0</v>
+      </c>
+      <c r="G26" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H26" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I26" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+    </row>
+    <row r="27" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A27" s="58"/>
+      <c r="B27" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="51"/>
+      <c r="E27" s="48">
+        <v>1</v>
+      </c>
+      <c r="F27" s="48">
+        <v>1</v>
+      </c>
+      <c r="G27" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H27" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I27" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="47">
+        <f t="shared" si="3"/>
+        <v>-1</v>
+      </c>
+      <c r="K27" s="49"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49"/>
+    </row>
+    <row r="28" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A28" s="58"/>
+      <c r="B28" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="51"/>
+      <c r="E28" s="48">
+        <v>2</v>
+      </c>
+      <c r="F28" s="48">
+        <v>2</v>
+      </c>
+      <c r="G28" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H28" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I28" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="47">
+        <f t="shared" si="3"/>
+        <v>-2</v>
+      </c>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+    </row>
+    <row r="29" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A29" s="58"/>
+      <c r="B29" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="51"/>
+      <c r="E29" s="48">
+        <v>0</v>
+      </c>
+      <c r="F29" s="48">
+        <v>0</v>
+      </c>
+      <c r="G29" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H29" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I29" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="49"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="49"/>
+    </row>
+    <row r="30" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A30" s="58"/>
+      <c r="B30" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="51"/>
+      <c r="E30" s="48">
+        <v>18</v>
+      </c>
+      <c r="F30" s="48">
+        <v>18</v>
+      </c>
+      <c r="G30" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H30" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I30" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="47">
+        <f t="shared" si="3"/>
+        <v>-18</v>
+      </c>
+      <c r="K30" s="49"/>
+      <c r="L30" s="49"/>
+      <c r="M30" s="49"/>
+    </row>
+    <row r="31" spans="1:13" ht="36.6" thickBot="1">
+      <c r="A31" s="58"/>
+      <c r="B31" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="51"/>
+      <c r="E31" s="48">
+        <v>2</v>
+      </c>
+      <c r="F31" s="48">
+        <v>2</v>
+      </c>
+      <c r="G31" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H31" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I31" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="47">
+        <f t="shared" si="3"/>
+        <v>-2</v>
+      </c>
+      <c r="K31" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="L31" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="M31" s="49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A32" s="58"/>
+      <c r="B32" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="51"/>
+      <c r="E32" s="48">
+        <v>9</v>
+      </c>
+      <c r="F32" s="48">
+        <v>9</v>
+      </c>
+      <c r="G32" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H32" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I32" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="47">
+        <f t="shared" si="3"/>
+        <v>-9</v>
+      </c>
+      <c r="K32" s="49"/>
+      <c r="L32" s="49"/>
+      <c r="M32" s="49"/>
+    </row>
+    <row r="33" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A33" s="58"/>
+      <c r="B33" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="51"/>
+      <c r="E33" s="48">
+        <v>75</v>
+      </c>
+      <c r="F33" s="48">
+        <v>75</v>
+      </c>
+      <c r="G33" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H33" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I33" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="47">
+        <f t="shared" si="3"/>
+        <v>-75</v>
+      </c>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="49"/>
+    </row>
+    <row r="34" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A34" s="58"/>
+      <c r="B34" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="47"/>
+      <c r="E34" s="48">
+        <v>4</v>
+      </c>
+      <c r="F34" s="48">
+        <v>4</v>
+      </c>
+      <c r="G34" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H34" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I34" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="47">
+        <f t="shared" si="3"/>
+        <v>-4</v>
+      </c>
+      <c r="K34" s="49"/>
+      <c r="L34" s="49"/>
+      <c r="M34" s="49"/>
+    </row>
+    <row r="35" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A35" s="59"/>
+      <c r="B35" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="51"/>
+      <c r="E35" s="48">
+        <v>390</v>
+      </c>
+      <c r="F35" s="48">
+        <v>390</v>
+      </c>
+      <c r="G35" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H35" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I35" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="47">
+        <f t="shared" si="3"/>
+        <v>-390</v>
+      </c>
+      <c r="K35" s="49"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
+    </row>
+    <row r="36" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A36" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="51"/>
+      <c r="E36" s="48">
+        <v>0</v>
+      </c>
+      <c r="F36" s="48">
+        <v>0</v>
+      </c>
+      <c r="G36" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H36" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I36" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="49"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="49"/>
+    </row>
+    <row r="37" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A37" s="58"/>
+      <c r="B37" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="51"/>
+      <c r="E37" s="48">
+        <v>0</v>
+      </c>
+      <c r="F37" s="48">
+        <v>0</v>
+      </c>
+      <c r="G37" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H37" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I37" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
+    </row>
+    <row r="38" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A38" s="58"/>
+      <c r="B38" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="51"/>
+      <c r="E38" s="48">
+        <v>0</v>
+      </c>
+      <c r="F38" s="48">
+        <v>0</v>
+      </c>
+      <c r="G38" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H38" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I38" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="49"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="49"/>
+    </row>
+    <row r="39" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A39" s="58"/>
+      <c r="B39" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="51"/>
+      <c r="E39" s="48">
+        <v>0</v>
+      </c>
+      <c r="F39" s="48">
+        <v>0</v>
+      </c>
+      <c r="G39" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H39" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I39" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="49"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="49"/>
+    </row>
+    <row r="40" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A40" s="58"/>
+      <c r="B40" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" s="51"/>
+      <c r="E40" s="48">
+        <v>0</v>
+      </c>
+      <c r="F40" s="48">
+        <v>0</v>
+      </c>
+      <c r="G40" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H40" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I40" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="49"/>
+      <c r="L40" s="49"/>
+      <c r="M40" s="49"/>
+    </row>
+    <row r="41" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A41" s="58"/>
+      <c r="B41" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="47"/>
+      <c r="E41" s="48">
+        <v>6</v>
+      </c>
+      <c r="F41" s="48">
+        <v>6</v>
+      </c>
+      <c r="G41" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H41" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I41" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="47">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="K41" s="49"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A42" s="58"/>
+      <c r="B42" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="51"/>
+      <c r="E42" s="48">
+        <v>0</v>
+      </c>
+      <c r="F42" s="48">
+        <v>0</v>
+      </c>
+      <c r="G42" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H42" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I42" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+    </row>
+    <row r="43" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A43" s="58"/>
+      <c r="B43" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="51"/>
+      <c r="E43" s="48">
+        <v>3</v>
+      </c>
+      <c r="F43" s="48">
+        <v>3</v>
+      </c>
+      <c r="G43" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H43" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I43" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="47">
+        <f t="shared" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="K43" s="49"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49"/>
+    </row>
+    <row r="44" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A44" s="58"/>
+      <c r="B44" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44" s="51"/>
+      <c r="E44" s="48">
+        <v>20</v>
+      </c>
+      <c r="F44" s="48">
+        <v>20</v>
+      </c>
+      <c r="G44" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H44" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I44" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="47">
+        <f t="shared" si="3"/>
+        <v>-20</v>
+      </c>
+      <c r="K44" s="49"/>
+      <c r="L44" s="49"/>
+      <c r="M44" s="49"/>
+    </row>
+    <row r="45" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A45" s="58"/>
+      <c r="B45" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="51"/>
+      <c r="E45" s="48">
+        <v>0</v>
+      </c>
+      <c r="F45" s="48">
+        <v>0</v>
+      </c>
+      <c r="G45" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H45" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I45" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="49"/>
+      <c r="L45" s="49"/>
+      <c r="M45" s="49"/>
+    </row>
+    <row r="46" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A46" s="58"/>
+      <c r="B46" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46" s="51"/>
+      <c r="E46" s="48">
+        <v>102</v>
+      </c>
+      <c r="F46" s="48">
+        <v>102</v>
+      </c>
+      <c r="G46" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H46" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I46" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="47">
+        <f t="shared" si="3"/>
+        <v>-102</v>
+      </c>
+      <c r="K46" s="49"/>
+      <c r="L46" s="49"/>
+      <c r="M46" s="49"/>
+    </row>
+    <row r="47" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A47" s="62" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="46" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="51"/>
+      <c r="E47" s="48">
+        <v>6</v>
+      </c>
+      <c r="F47" s="48">
+        <v>6</v>
+      </c>
+      <c r="G47" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H47" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I47" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="47">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="K47" s="49"/>
+      <c r="L47" s="49"/>
+      <c r="M47" s="49"/>
+    </row>
+    <row r="48" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A48" s="62"/>
+      <c r="B48" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="51"/>
+      <c r="E48" s="48">
+        <v>4</v>
+      </c>
+      <c r="F48" s="48">
+        <v>4</v>
+      </c>
+      <c r="G48" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H48" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I48" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="47">
+        <f t="shared" si="3"/>
+        <v>-4</v>
+      </c>
+      <c r="K48" s="49"/>
+      <c r="L48" s="49"/>
+      <c r="M48" s="49"/>
+    </row>
+    <row r="49" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A49" s="62"/>
+      <c r="B49" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="51"/>
+      <c r="E49" s="48">
+        <v>0</v>
+      </c>
+      <c r="F49" s="48">
+        <v>0</v>
+      </c>
+      <c r="G49" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H49" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I49" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="49"/>
+      <c r="L49" s="49"/>
+      <c r="M49" s="49"/>
+    </row>
+    <row r="50" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A50" s="62"/>
+      <c r="B50" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" s="51"/>
+      <c r="E50" s="48">
+        <v>0</v>
+      </c>
+      <c r="F50" s="48">
+        <v>0</v>
+      </c>
+      <c r="G50" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H50" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I50" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="49"/>
+      <c r="L50" s="49"/>
+      <c r="M50" s="49"/>
+    </row>
+    <row r="51" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A51" s="62"/>
+      <c r="B51" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="51"/>
+      <c r="E51" s="48">
+        <v>6</v>
+      </c>
+      <c r="F51" s="48">
+        <v>6</v>
+      </c>
+      <c r="G51" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H51" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I51" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="47">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="K51" s="49"/>
+      <c r="L51" s="49"/>
+      <c r="M51" s="49"/>
+    </row>
+    <row r="52" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A52" s="62"/>
+      <c r="B52" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="51"/>
+      <c r="E52" s="48">
+        <v>0</v>
+      </c>
+      <c r="F52" s="48">
+        <v>0</v>
+      </c>
+      <c r="G52" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H52" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I52" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="49"/>
+      <c r="L52" s="49"/>
+      <c r="M52" s="49"/>
+    </row>
+    <row r="53" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A53" s="62"/>
+      <c r="B53" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="51"/>
+      <c r="E53" s="48">
+        <v>0</v>
+      </c>
+      <c r="F53" s="48">
+        <v>0</v>
+      </c>
+      <c r="G53" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H53" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I53" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="49"/>
+      <c r="L53" s="49"/>
+      <c r="M53" s="49"/>
+    </row>
+    <row r="54" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A54" s="62"/>
+      <c r="B54" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="51"/>
+      <c r="E54" s="48">
+        <v>0</v>
+      </c>
+      <c r="F54" s="48">
+        <v>0</v>
+      </c>
+      <c r="G54" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H54" s="47" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
+      <c r="I54" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="49"/>
+      <c r="L54" s="49"/>
+      <c r="M54" s="49"/>
+    </row>
+    <row r="55" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A55" s="62"/>
+      <c r="B55" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55" s="51"/>
+      <c r="E55" s="48">
+        <v>187</v>
+      </c>
+      <c r="F55" s="48">
+        <v>187</v>
+      </c>
+      <c r="G55" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H55" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I55" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="47">
+        <f t="shared" si="3"/>
+        <v>-187</v>
+      </c>
+      <c r="K55" s="49"/>
+      <c r="L55" s="49"/>
+      <c r="M55" s="49"/>
+    </row>
+    <row r="56" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A56" s="62"/>
+      <c r="B56" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="51"/>
+      <c r="E56" s="48">
+        <v>20</v>
+      </c>
+      <c r="F56" s="48">
+        <v>20</v>
+      </c>
+      <c r="G56" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H56" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I56" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="47">
+        <f t="shared" si="3"/>
+        <v>-20</v>
+      </c>
+      <c r="K56" s="49"/>
+      <c r="L56" s="49"/>
+      <c r="M56" s="49"/>
+    </row>
+    <row r="57" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="A57" s="62"/>
+      <c r="B57" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D57" s="51"/>
+      <c r="E57" s="48">
+        <v>759</v>
+      </c>
+      <c r="F57" s="48">
+        <v>759</v>
+      </c>
+      <c r="G57" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="H57" s="47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I57" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="47">
+        <f t="shared" si="3"/>
+        <v>-759</v>
+      </c>
+      <c r="K57" s="49"/>
+      <c r="L57" s="49"/>
+      <c r="M57" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A47:A57"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A3:A13"/>
+    <mergeCell ref="A14:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A46"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I1:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>